--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G19">

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G56">

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G56">

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU70"/>
+  <dimension ref="A1:AU75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00:00</t>
+          <t>2026-11-02 09:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00:00</t>
+          <t>2026-11-02 09:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G6">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00:00</t>
+          <t>2026-11-02 09:00:00</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G7">
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-11-02 12:15:00</t>
+          <t>2026-11-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.22</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>3.05</v>
+        <v>5.02</v>
       </c>
       <c r="P9">
-        <v>2.29</v>
+        <v>1.45</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-11-02 12:30:00</t>
+          <t>2026-11-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-11-02 13:00:00</t>
+          <t>2026-11-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-11-02 13:00:00</t>
+          <t>2026-11-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-11-02 13:00:00</t>
+          <t>2026-11-02 12:15:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G13">
@@ -2424,17 +2424,17 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-11-02 13:45:00</t>
+          <t>2026-11-02 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-11-02 14:00:00</t>
+          <t>2026-11-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-11-02 14:00:00</t>
+          <t>2026-11-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-11-02 14:00:00</t>
+          <t>2026-11-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G17">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-11-02 14:00:00</t>
+          <t>2026-11-02 13:45:00</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G21">
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G22">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,22 +4342,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5152,27 +5152,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G30">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -5967,27 +5967,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6298,22 +6298,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>6.65</v>
+        <v>2.19</v>
       </c>
       <c r="O37">
-        <v>4.7</v>
+        <v>3.56</v>
       </c>
       <c r="P37">
-        <v>1.4</v>
+        <v>2.92</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-11-02 15:05:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -6945,12 +6945,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.6</v>
+        <v>6.65</v>
       </c>
       <c r="O41">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="P41">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7108,27 +7108,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G43">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N43">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:05:00</t>
         </is>
       </c>
     </row>
@@ -7434,27 +7434,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G44">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7760,12 +7760,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G46">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G50">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G51">
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G52">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G53">
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G54">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-11-02 16:45:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-11-02 16:45:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -9965,10 +9965,10 @@
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB59">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10291,10 +10291,10 @@
         <v>0</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -10694,27 +10694,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -10857,27 +10857,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-11-02 19:30:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -11183,27 +11183,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11269,10 +11269,10 @@
         <v>0</v>
       </c>
       <c r="AA67">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-11-02 20:00:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G68">
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-11-02 20:30:00</t>
+          <t>2026-11-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G69">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-11-02 20:30:00</t>
+          <t>2026-11-02 18:00:00</t>
         </is>
       </c>
     </row>
@@ -11672,156 +11672,971 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N70">
+        <v>0</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>0</v>
+      </c>
+      <c r="U70">
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0</v>
+      </c>
+      <c r="X70">
+        <v>0</v>
+      </c>
+      <c r="Y70">
+        <v>0</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+      <c r="AA70">
+        <v>0</v>
+      </c>
+      <c r="AB70">
+        <v>0</v>
+      </c>
+      <c r="AC70">
+        <v>0</v>
+      </c>
+      <c r="AD70">
+        <v>0</v>
+      </c>
+      <c r="AE70">
+        <v>0</v>
+      </c>
+      <c r="AF70">
+        <v>0</v>
+      </c>
+      <c r="AG70">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ70">
+        <v>0</v>
+      </c>
+      <c r="AK70">
+        <v>0</v>
+      </c>
+      <c r="AL70">
+        <v>0</v>
+      </c>
+      <c r="AM70">
+        <v>-1</v>
+      </c>
+      <c r="AN70">
+        <v>-1</v>
+      </c>
+      <c r="AO70">
+        <v>-1</v>
+      </c>
+      <c r="AP70">
+        <v>-1</v>
+      </c>
+      <c r="AQ70">
+        <v>0</v>
+      </c>
+      <c r="AR70">
+        <v>0</v>
+      </c>
+      <c r="AS70">
+        <v>0</v>
+      </c>
+      <c r="AT70">
+        <v>0</v>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
+          <t>2026-11-02 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Molynes United</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>0</v>
+      </c>
+      <c r="U71">
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0</v>
+      </c>
+      <c r="X71">
+        <v>0</v>
+      </c>
+      <c r="Y71">
+        <v>0</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+      <c r="AA71">
+        <v>0</v>
+      </c>
+      <c r="AB71">
+        <v>0</v>
+      </c>
+      <c r="AC71">
+        <v>0</v>
+      </c>
+      <c r="AD71">
+        <v>0</v>
+      </c>
+      <c r="AE71">
+        <v>0</v>
+      </c>
+      <c r="AF71">
+        <v>0</v>
+      </c>
+      <c r="AG71">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ71">
+        <v>0</v>
+      </c>
+      <c r="AK71">
+        <v>0</v>
+      </c>
+      <c r="AL71">
+        <v>0</v>
+      </c>
+      <c r="AM71">
+        <v>-1</v>
+      </c>
+      <c r="AN71">
+        <v>-1</v>
+      </c>
+      <c r="AO71">
+        <v>-1</v>
+      </c>
+      <c r="AP71">
+        <v>-1</v>
+      </c>
+      <c r="AQ71">
+        <v>0</v>
+      </c>
+      <c r="AR71">
+        <v>0</v>
+      </c>
+      <c r="AS71">
+        <v>0</v>
+      </c>
+      <c r="AT71">
+        <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>2026-11-02 19:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N72">
+        <v>2</v>
+      </c>
+      <c r="O72">
+        <v>3.8</v>
+      </c>
+      <c r="P72">
+        <v>3.59</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>0</v>
+      </c>
+      <c r="U72">
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0</v>
+      </c>
+      <c r="X72">
+        <v>0</v>
+      </c>
+      <c r="Y72">
+        <v>0</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+      <c r="AA72">
+        <v>1.68</v>
+      </c>
+      <c r="AB72">
+        <v>2</v>
+      </c>
+      <c r="AC72">
+        <v>0</v>
+      </c>
+      <c r="AD72">
+        <v>0</v>
+      </c>
+      <c r="AE72">
+        <v>0</v>
+      </c>
+      <c r="AF72">
+        <v>0</v>
+      </c>
+      <c r="AG72">
+        <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ72">
+        <v>0</v>
+      </c>
+      <c r="AK72">
+        <v>0</v>
+      </c>
+      <c r="AL72">
+        <v>0</v>
+      </c>
+      <c r="AM72">
+        <v>-1</v>
+      </c>
+      <c r="AN72">
+        <v>-1</v>
+      </c>
+      <c r="AO72">
+        <v>-1</v>
+      </c>
+      <c r="AP72">
+        <v>-1</v>
+      </c>
+      <c r="AQ72">
+        <v>0</v>
+      </c>
+      <c r="AR72">
+        <v>0</v>
+      </c>
+      <c r="AS72">
+        <v>0</v>
+      </c>
+      <c r="AT72">
+        <v>0</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>0</v>
+      </c>
+      <c r="U73">
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0</v>
+      </c>
+      <c r="X73">
+        <v>0</v>
+      </c>
+      <c r="Y73">
+        <v>0</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+      <c r="AA73">
+        <v>0</v>
+      </c>
+      <c r="AB73">
+        <v>0</v>
+      </c>
+      <c r="AC73">
+        <v>0</v>
+      </c>
+      <c r="AD73">
+        <v>0</v>
+      </c>
+      <c r="AE73">
+        <v>0</v>
+      </c>
+      <c r="AF73">
+        <v>0</v>
+      </c>
+      <c r="AG73">
+        <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ73">
+        <v>0</v>
+      </c>
+      <c r="AK73">
+        <v>0</v>
+      </c>
+      <c r="AL73">
+        <v>0</v>
+      </c>
+      <c r="AM73">
+        <v>-1</v>
+      </c>
+      <c r="AN73">
+        <v>-1</v>
+      </c>
+      <c r="AO73">
+        <v>-1</v>
+      </c>
+      <c r="AP73">
+        <v>-1</v>
+      </c>
+      <c r="AQ73">
+        <v>0</v>
+      </c>
+      <c r="AR73">
+        <v>0</v>
+      </c>
+      <c r="AS73">
+        <v>0</v>
+      </c>
+      <c r="AT73">
+        <v>0</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>0</v>
+      </c>
+      <c r="U74">
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0</v>
+      </c>
+      <c r="X74">
+        <v>0</v>
+      </c>
+      <c r="Y74">
+        <v>0</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+      <c r="AA74">
+        <v>0</v>
+      </c>
+      <c r="AB74">
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <v>0</v>
+      </c>
+      <c r="AD74">
+        <v>0</v>
+      </c>
+      <c r="AE74">
+        <v>0</v>
+      </c>
+      <c r="AF74">
+        <v>0</v>
+      </c>
+      <c r="AG74">
+        <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ74">
+        <v>0</v>
+      </c>
+      <c r="AK74">
+        <v>0</v>
+      </c>
+      <c r="AL74">
+        <v>0</v>
+      </c>
+      <c r="AM74">
+        <v>-1</v>
+      </c>
+      <c r="AN74">
+        <v>-1</v>
+      </c>
+      <c r="AO74">
+        <v>-1</v>
+      </c>
+      <c r="AP74">
+        <v>-1</v>
+      </c>
+      <c r="AQ74">
+        <v>0</v>
+      </c>
+      <c r="AR74">
+        <v>0</v>
+      </c>
+      <c r="AS74">
+        <v>0</v>
+      </c>
+      <c r="AT74">
+        <v>0</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Waterhouse</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Cavalier</t>
         </is>
       </c>
-      <c r="G70">
-        <v>0</v>
-      </c>
-      <c r="H70">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>0</v>
-      </c>
-      <c r="M70" t="inlineStr">
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>0</v>
-      </c>
-      <c r="P70">
-        <v>0</v>
-      </c>
-      <c r="Q70">
-        <v>0</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>0</v>
-      </c>
-      <c r="T70">
-        <v>0</v>
-      </c>
-      <c r="U70">
-        <v>0</v>
-      </c>
-      <c r="V70">
-        <v>0</v>
-      </c>
-      <c r="W70">
-        <v>0</v>
-      </c>
-      <c r="X70">
-        <v>0</v>
-      </c>
-      <c r="Y70">
-        <v>0</v>
-      </c>
-      <c r="Z70">
-        <v>0</v>
-      </c>
-      <c r="AA70">
-        <v>0</v>
-      </c>
-      <c r="AB70">
-        <v>0</v>
-      </c>
-      <c r="AC70">
-        <v>0</v>
-      </c>
-      <c r="AD70">
-        <v>0</v>
-      </c>
-      <c r="AE70">
-        <v>0</v>
-      </c>
-      <c r="AF70">
-        <v>0</v>
-      </c>
-      <c r="AG70">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ70">
-        <v>0</v>
-      </c>
-      <c r="AK70">
-        <v>0</v>
-      </c>
-      <c r="AL70">
-        <v>0</v>
-      </c>
-      <c r="AM70">
-        <v>-1</v>
-      </c>
-      <c r="AN70">
-        <v>-1</v>
-      </c>
-      <c r="AO70">
-        <v>-1</v>
-      </c>
-      <c r="AP70">
-        <v>-1</v>
-      </c>
-      <c r="AQ70">
-        <v>0</v>
-      </c>
-      <c r="AR70">
-        <v>0</v>
-      </c>
-      <c r="AS70">
-        <v>0</v>
-      </c>
-      <c r="AT70">
-        <v>0</v>
-      </c>
-      <c r="AU70" t="inlineStr">
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75">
+        <v>0</v>
+      </c>
+      <c r="AE75">
+        <v>0</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+      <c r="AG75">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
+        <v>0</v>
+      </c>
+      <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>-1</v>
+      </c>
+      <c r="AN75">
+        <v>-1</v>
+      </c>
+      <c r="AO75">
+        <v>-1</v>
+      </c>
+      <c r="AP75">
+        <v>-1</v>
+      </c>
+      <c r="AQ75">
+        <v>0</v>
+      </c>
+      <c r="AR75">
+        <v>0</v>
+      </c>
+      <c r="AS75">
+        <v>0</v>
+      </c>
+      <c r="AT75">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
         <is>
           <t>2026-11-02 22:00:00</t>
         </is>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU75"/>
+  <dimension ref="A1:AU77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.19</v>
+        <v>3.7</v>
       </c>
       <c r="O37">
-        <v>3.56</v>
+        <v>2.99</v>
       </c>
       <c r="P37">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.26</v>
+        <v>3.2</v>
       </c>
       <c r="O38">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P38">
-        <v>2.97</v>
+        <v>2.15</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="P39">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>7.65</v>
+        <v>2.26</v>
       </c>
       <c r="O40">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>1.29</v>
+        <v>2.97</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>6.65</v>
+        <v>1.81</v>
       </c>
       <c r="O41">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.1</v>
+        <v>7.65</v>
       </c>
       <c r="O42">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="P42">
-        <v>2.71</v>
+        <v>1.29</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7271,27 +7271,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-11-02 15:05:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7434,27 +7434,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7597,27 +7597,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:05:00</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G46">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G48">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G54">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P55">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9390,27 +9390,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="O57">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P57">
-        <v>2.87</v>
+        <v>2.43</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G60">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10291,10 +10291,10 @@
         <v>0</v>
       </c>
       <c r="AA61">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB61">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-11-02 16:45:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-11-02 16:45:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="O63">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="P63">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AB63">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O64">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P64">
-        <v>8.199999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10943,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC65">
         <v>0</v>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G67">
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -11346,27 +11346,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G68">
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S68">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T68">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U68">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V68">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X68">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y68">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z68">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA68">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD68">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE68">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF68">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG68">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK68">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-11-02 17:30:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -11509,27 +11509,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G69">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G70">
@@ -11728,55 +11728,55 @@
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -11835,27 +11835,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G71">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-11-02 19:05:00</t>
+          <t>2026-11-02 18:00:00</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-11-02 20:00:00</t>
+          <t>2026-11-02 18:00:00</t>
         </is>
       </c>
     </row>
@@ -12161,27 +12161,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G73">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-11-02 20:30:00</t>
+          <t>2026-11-02 19:05:00</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-11-02 20:30:00</t>
+          <t>2026-11-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -12487,156 +12487,482 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>0</v>
+      </c>
+      <c r="U75">
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0</v>
+      </c>
+      <c r="X75">
+        <v>0</v>
+      </c>
+      <c r="Y75">
+        <v>0</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+      <c r="AA75">
+        <v>0</v>
+      </c>
+      <c r="AB75">
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <v>0</v>
+      </c>
+      <c r="AD75">
+        <v>0</v>
+      </c>
+      <c r="AE75">
+        <v>0</v>
+      </c>
+      <c r="AF75">
+        <v>0</v>
+      </c>
+      <c r="AG75">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
+        <v>0</v>
+      </c>
+      <c r="AK75">
+        <v>0</v>
+      </c>
+      <c r="AL75">
+        <v>0</v>
+      </c>
+      <c r="AM75">
+        <v>-1</v>
+      </c>
+      <c r="AN75">
+        <v>-1</v>
+      </c>
+      <c r="AO75">
+        <v>-1</v>
+      </c>
+      <c r="AP75">
+        <v>-1</v>
+      </c>
+      <c r="AQ75">
+        <v>0</v>
+      </c>
+      <c r="AR75">
+        <v>0</v>
+      </c>
+      <c r="AS75">
+        <v>0</v>
+      </c>
+      <c r="AT75">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>0</v>
+      </c>
+      <c r="U76">
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0</v>
+      </c>
+      <c r="X76">
+        <v>0</v>
+      </c>
+      <c r="Y76">
+        <v>0</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+      <c r="AA76">
+        <v>0</v>
+      </c>
+      <c r="AB76">
+        <v>0</v>
+      </c>
+      <c r="AC76">
+        <v>0</v>
+      </c>
+      <c r="AD76">
+        <v>0</v>
+      </c>
+      <c r="AE76">
+        <v>0</v>
+      </c>
+      <c r="AF76">
+        <v>0</v>
+      </c>
+      <c r="AG76">
+        <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
+        <v>0</v>
+      </c>
+      <c r="AK76">
+        <v>0</v>
+      </c>
+      <c r="AL76">
+        <v>0</v>
+      </c>
+      <c r="AM76">
+        <v>-1</v>
+      </c>
+      <c r="AN76">
+        <v>-1</v>
+      </c>
+      <c r="AO76">
+        <v>-1</v>
+      </c>
+      <c r="AP76">
+        <v>-1</v>
+      </c>
+      <c r="AQ76">
+        <v>0</v>
+      </c>
+      <c r="AR76">
+        <v>0</v>
+      </c>
+      <c r="AS76">
+        <v>0</v>
+      </c>
+      <c r="AT76">
+        <v>0</v>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Waterhouse</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Cavalier</t>
         </is>
       </c>
-      <c r="G75">
-        <v>0</v>
-      </c>
-      <c r="H75">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>0</v>
-      </c>
-      <c r="K75">
-        <v>0</v>
-      </c>
-      <c r="L75">
-        <v>0</v>
-      </c>
-      <c r="M75" t="inlineStr">
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75">
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <v>0</v>
-      </c>
-      <c r="S75">
-        <v>0</v>
-      </c>
-      <c r="T75">
-        <v>0</v>
-      </c>
-      <c r="U75">
-        <v>0</v>
-      </c>
-      <c r="V75">
-        <v>0</v>
-      </c>
-      <c r="W75">
-        <v>0</v>
-      </c>
-      <c r="X75">
-        <v>0</v>
-      </c>
-      <c r="Y75">
-        <v>0</v>
-      </c>
-      <c r="Z75">
-        <v>0</v>
-      </c>
-      <c r="AA75">
-        <v>0</v>
-      </c>
-      <c r="AB75">
-        <v>0</v>
-      </c>
-      <c r="AC75">
-        <v>0</v>
-      </c>
-      <c r="AD75">
-        <v>0</v>
-      </c>
-      <c r="AE75">
-        <v>0</v>
-      </c>
-      <c r="AF75">
-        <v>0</v>
-      </c>
-      <c r="AG75">
-        <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>0</v>
-      </c>
-      <c r="AK75">
-        <v>0</v>
-      </c>
-      <c r="AL75">
-        <v>0</v>
-      </c>
-      <c r="AM75">
-        <v>-1</v>
-      </c>
-      <c r="AN75">
-        <v>-1</v>
-      </c>
-      <c r="AO75">
-        <v>-1</v>
-      </c>
-      <c r="AP75">
-        <v>-1</v>
-      </c>
-      <c r="AQ75">
-        <v>0</v>
-      </c>
-      <c r="AR75">
-        <v>0</v>
-      </c>
-      <c r="AS75">
-        <v>0</v>
-      </c>
-      <c r="AT75">
-        <v>0</v>
-      </c>
-      <c r="AU75" t="inlineStr">
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77">
+        <v>0</v>
+      </c>
+      <c r="AE77">
+        <v>0</v>
+      </c>
+      <c r="AF77">
+        <v>0</v>
+      </c>
+      <c r="AG77">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
+        <v>0</v>
+      </c>
+      <c r="AK77">
+        <v>0</v>
+      </c>
+      <c r="AL77">
+        <v>0</v>
+      </c>
+      <c r="AM77">
+        <v>-1</v>
+      </c>
+      <c r="AN77">
+        <v>-1</v>
+      </c>
+      <c r="AO77">
+        <v>-1</v>
+      </c>
+      <c r="AP77">
+        <v>-1</v>
+      </c>
+      <c r="AQ77">
+        <v>0</v>
+      </c>
+      <c r="AR77">
+        <v>0</v>
+      </c>
+      <c r="AS77">
+        <v>0</v>
+      </c>
+      <c r="AT77">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
         <is>
           <t>2026-11-02 22:00:00</t>
         </is>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G6">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O37">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="P37">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB37">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O38">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="P38">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AB38">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC62">
         <v>0</v>
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11438,10 +11438,10 @@
         <v>0</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE68">
         <v>0</v>
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC69">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G23">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O57">
         <v>3.34</v>
       </c>
       <c r="P57">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O58">
         <v>3.34</v>
       </c>
       <c r="P58">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.13</v>
+        <v>2.93</v>
       </c>
       <c r="O68">
-        <v>9.85</v>
+        <v>3.36</v>
       </c>
       <c r="P68">
-        <v>21</v>
+        <v>2.55</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,16 +11432,16 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC68">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD68">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.93</v>
+        <v>1.13</v>
       </c>
       <c r="O69">
-        <v>3.36</v>
+        <v>9.85</v>
       </c>
       <c r="P69">
-        <v>2.55</v>
+        <v>21</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,16 +11595,16 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE69">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU77"/>
+  <dimension ref="A1:AU82"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,12 +588,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bangkok Glass</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G2">
@@ -739,7 +739,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2026-11-02 09:00:00</t>
+          <t>2026-11-02 08:00:00</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ethiopia Nigd Bank</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Bangkok Glass</t>
         </is>
       </c>
       <c r="G3">
@@ -919,7 +919,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Ethiopia Nigd Bank</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G5">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G7">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00:00</t>
+          <t>2026-11-02 09:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00:00</t>
+          <t>2026-11-02 10:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00:00</t>
+          <t>2026-11-02 10:00:00</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2060,22 +2060,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G11">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.76</v>
+        <v>8</v>
       </c>
       <c r="O12">
-        <v>3.86</v>
+        <v>5.02</v>
       </c>
       <c r="P12">
-        <v>4.64</v>
+        <v>1.45</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-11-02 12:15:00</t>
+          <t>2026-11-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.22</v>
+        <v>1.99</v>
       </c>
       <c r="O13">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>2.29</v>
+        <v>3.64</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-11-02 12:30:00</t>
+          <t>2026-11-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-11-02 13:00:00</t>
+          <t>2026-11-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="O15">
-        <v>3.4</v>
+        <v>3.86</v>
       </c>
       <c r="P15">
-        <v>3.7</v>
+        <v>4.64</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AB15">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-11-02 13:00:00</t>
+          <t>2026-11-02 12:15:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-11-02 13:00:00</t>
+          <t>2026-11-02 12:30:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G17">
@@ -3076,68 +3076,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-11-02 13:45:00</t>
+          <t>2026-11-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="AA18">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB18">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-11-02 14:00:00</t>
+          <t>2026-11-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3359,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3445,10 +3445,10 @@
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC19">
         <v>0</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2026-11-02 14:00:00</t>
+          <t>2026-11-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3522,12 +3522,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G20">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2026-11-02 14:00:00</t>
+          <t>2026-11-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G21">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N21">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-11-02 14:00:00</t>
+          <t>2026-11-02 13:45:00</t>
         </is>
       </c>
     </row>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G23">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G24">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G25">
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G26">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,13 +4873,13 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5478,12 +5478,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2</v>
+        <v>2.55</v>
       </c>
       <c r="O32">
-        <v>3.59</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
-        <v>3.8</v>
+        <v>2.65</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5641,27 +5641,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O33">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5804,27 +5804,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="O36">
-        <v>3.36</v>
+        <v>3.59</v>
       </c>
       <c r="P36">
         <v>3.8</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6293,27 +6293,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.2</v>
+        <v>2.47</v>
       </c>
       <c r="O37">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="P37">
-        <v>2.15</v>
+        <v>2.77</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,10 +6379,10 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6456,27 +6456,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,10 +6542,10 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6619,27 +6619,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.19</v>
+        <v>3.04</v>
       </c>
       <c r="O39">
-        <v>3.56</v>
+        <v>3.73</v>
       </c>
       <c r="P39">
-        <v>2.92</v>
+        <v>2.39</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="P40">
-        <v>2.97</v>
+        <v>3.8</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.81</v>
+        <v>3.2</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="P41">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>7.65</v>
+        <v>3.7</v>
       </c>
       <c r="O42">
-        <v>5.9</v>
+        <v>2.99</v>
       </c>
       <c r="P42">
-        <v>1.29</v>
+        <v>2.1</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7276,22 +7276,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>6.65</v>
+        <v>2.19</v>
       </c>
       <c r="O43">
-        <v>4.7</v>
+        <v>3.56</v>
       </c>
       <c r="P43">
-        <v>1.4</v>
+        <v>2.92</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="O44">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="P44">
-        <v>2.71</v>
+        <v>2.97</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7597,12 +7597,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="O45">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="P45">
-        <v>3.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2026-11-02 15:05:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.09</v>
+        <v>7.65</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="P46">
-        <v>3.22</v>
+        <v>1.29</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.6</v>
+        <v>6.65</v>
       </c>
       <c r="O47">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="P47">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8086,27 +8086,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8237,7 +8237,7 @@
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8249,27 +8249,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:05:00</t>
         </is>
       </c>
     </row>
@@ -8412,27 +8412,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8738,12 +8738,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G52">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G53">
@@ -9069,22 +9069,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9476,10 +9476,10 @@
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB56">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC56">
         <v>0</v>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P59">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10042,27 +10042,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="O60">
         <v>3.38</v>
       </c>
       <c r="P60">
-        <v>2.96</v>
+        <v>4.07</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AB60">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="O61">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P61">
-        <v>3.43</v>
+        <v>2.44</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.76</v>
+        <v>2.45</v>
       </c>
       <c r="O62">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P62">
-        <v>3.92</v>
+        <v>2.43</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC62">
         <v>0</v>
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="O63">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-11-02 16:45:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="O64">
-        <v>5</v>
+        <v>3.38</v>
       </c>
       <c r="P64">
-        <v>8.550000000000001</v>
+        <v>2.96</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-11-02 16:45:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="O65">
-        <v>3.78</v>
+        <v>3.2</v>
       </c>
       <c r="P65">
-        <v>3.23</v>
+        <v>3.43</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10943,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB65">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="O66">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
-        <v>8.199999999999999</v>
+        <v>3.92</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AB66">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="O68">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="P68">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AB68">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="O69">
-        <v>9.85</v>
+        <v>5</v>
       </c>
       <c r="P69">
-        <v>21</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11601,10 +11601,10 @@
         <v>0</v>
       </c>
       <c r="AC69">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD69">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -11672,27 +11672,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q70">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S70">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T70">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U70">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V70">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W70">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X70">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y70">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z70">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA70">
-        <v>2.04</v>
+        <v>1.66</v>
       </c>
       <c r="AB70">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AC70">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD70">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE70">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF70">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG70">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK70">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-11-02 17:30:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -11835,27 +11835,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -11998,27 +11998,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G72">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-11-02 19:05:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -12324,27 +12324,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2</v>
+        <v>1.13</v>
       </c>
       <c r="O74">
-        <v>3.8</v>
+        <v>9.85</v>
       </c>
       <c r="P74">
-        <v>3.59</v>
+        <v>21</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,16 +12410,16 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE74">
         <v>0</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-11-02 20:00:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G75">
@@ -12543,55 +12543,55 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-11-02 20:30:00</t>
+          <t>2026-11-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G76">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-11-02 20:30:00</t>
+          <t>2026-11-02 18:00:00</t>
         </is>
       </c>
     </row>
@@ -12813,156 +12813,971 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Ceará</t>
+        </is>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>0</v>
+      </c>
+      <c r="U77">
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0</v>
+      </c>
+      <c r="X77">
+        <v>0</v>
+      </c>
+      <c r="Y77">
+        <v>0</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+      <c r="AA77">
+        <v>0</v>
+      </c>
+      <c r="AB77">
+        <v>0</v>
+      </c>
+      <c r="AC77">
+        <v>0</v>
+      </c>
+      <c r="AD77">
+        <v>0</v>
+      </c>
+      <c r="AE77">
+        <v>0</v>
+      </c>
+      <c r="AF77">
+        <v>0</v>
+      </c>
+      <c r="AG77">
+        <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
+        <v>0</v>
+      </c>
+      <c r="AK77">
+        <v>0</v>
+      </c>
+      <c r="AL77">
+        <v>0</v>
+      </c>
+      <c r="AM77">
+        <v>-1</v>
+      </c>
+      <c r="AN77">
+        <v>-1</v>
+      </c>
+      <c r="AO77">
+        <v>-1</v>
+      </c>
+      <c r="AP77">
+        <v>-1</v>
+      </c>
+      <c r="AQ77">
+        <v>0</v>
+      </c>
+      <c r="AR77">
+        <v>0</v>
+      </c>
+      <c r="AS77">
+        <v>0</v>
+      </c>
+      <c r="AT77">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>2026-11-02 18:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026/2027</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Molynes United</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mount Pleasant Academy FC</t>
+        </is>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>0</v>
+      </c>
+      <c r="U78">
+        <v>0</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0</v>
+      </c>
+      <c r="X78">
+        <v>0</v>
+      </c>
+      <c r="Y78">
+        <v>0</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+      <c r="AA78">
+        <v>0</v>
+      </c>
+      <c r="AB78">
+        <v>0</v>
+      </c>
+      <c r="AC78">
+        <v>0</v>
+      </c>
+      <c r="AD78">
+        <v>0</v>
+      </c>
+      <c r="AE78">
+        <v>0</v>
+      </c>
+      <c r="AF78">
+        <v>0</v>
+      </c>
+      <c r="AG78">
+        <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>0</v>
+      </c>
+      <c r="AK78">
+        <v>0</v>
+      </c>
+      <c r="AL78">
+        <v>0</v>
+      </c>
+      <c r="AM78">
+        <v>-1</v>
+      </c>
+      <c r="AN78">
+        <v>-1</v>
+      </c>
+      <c r="AO78">
+        <v>-1</v>
+      </c>
+      <c r="AP78">
+        <v>-1</v>
+      </c>
+      <c r="AQ78">
+        <v>0</v>
+      </c>
+      <c r="AR78">
+        <v>0</v>
+      </c>
+      <c r="AS78">
+        <v>0</v>
+      </c>
+      <c r="AT78">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>2026-11-02 19:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N79">
+        <v>2</v>
+      </c>
+      <c r="O79">
+        <v>3.8</v>
+      </c>
+      <c r="P79">
+        <v>3.59</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>0</v>
+      </c>
+      <c r="U79">
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0</v>
+      </c>
+      <c r="X79">
+        <v>0</v>
+      </c>
+      <c r="Y79">
+        <v>0</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+      <c r="AA79">
+        <v>1.68</v>
+      </c>
+      <c r="AB79">
+        <v>2</v>
+      </c>
+      <c r="AC79">
+        <v>0</v>
+      </c>
+      <c r="AD79">
+        <v>0</v>
+      </c>
+      <c r="AE79">
+        <v>0</v>
+      </c>
+      <c r="AF79">
+        <v>0</v>
+      </c>
+      <c r="AG79">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
+        <v>0</v>
+      </c>
+      <c r="AK79">
+        <v>0</v>
+      </c>
+      <c r="AL79">
+        <v>0</v>
+      </c>
+      <c r="AM79">
+        <v>-1</v>
+      </c>
+      <c r="AN79">
+        <v>-1</v>
+      </c>
+      <c r="AO79">
+        <v>-1</v>
+      </c>
+      <c r="AP79">
+        <v>-1</v>
+      </c>
+      <c r="AQ79">
+        <v>0</v>
+      </c>
+      <c r="AR79">
+        <v>0</v>
+      </c>
+      <c r="AS79">
+        <v>0</v>
+      </c>
+      <c r="AT79">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>0</v>
+      </c>
+      <c r="U80">
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0</v>
+      </c>
+      <c r="X80">
+        <v>0</v>
+      </c>
+      <c r="Y80">
+        <v>0</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+      <c r="AA80">
+        <v>0</v>
+      </c>
+      <c r="AB80">
+        <v>0</v>
+      </c>
+      <c r="AC80">
+        <v>0</v>
+      </c>
+      <c r="AD80">
+        <v>0</v>
+      </c>
+      <c r="AE80">
+        <v>0</v>
+      </c>
+      <c r="AF80">
+        <v>0</v>
+      </c>
+      <c r="AG80">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ80">
+        <v>0</v>
+      </c>
+      <c r="AK80">
+        <v>0</v>
+      </c>
+      <c r="AL80">
+        <v>0</v>
+      </c>
+      <c r="AM80">
+        <v>-1</v>
+      </c>
+      <c r="AN80">
+        <v>-1</v>
+      </c>
+      <c r="AO80">
+        <v>-1</v>
+      </c>
+      <c r="AP80">
+        <v>-1</v>
+      </c>
+      <c r="AQ80">
+        <v>0</v>
+      </c>
+      <c r="AR80">
+        <v>0</v>
+      </c>
+      <c r="AS80">
+        <v>0</v>
+      </c>
+      <c r="AT80">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81">
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <v>0</v>
+      </c>
+      <c r="U81">
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0</v>
+      </c>
+      <c r="X81">
+        <v>0</v>
+      </c>
+      <c r="Y81">
+        <v>0</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+      <c r="AA81">
+        <v>0</v>
+      </c>
+      <c r="AB81">
+        <v>0</v>
+      </c>
+      <c r="AC81">
+        <v>0</v>
+      </c>
+      <c r="AD81">
+        <v>0</v>
+      </c>
+      <c r="AE81">
+        <v>0</v>
+      </c>
+      <c r="AF81">
+        <v>0</v>
+      </c>
+      <c r="AG81">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
+        <v>0</v>
+      </c>
+      <c r="AK81">
+        <v>0</v>
+      </c>
+      <c r="AL81">
+        <v>0</v>
+      </c>
+      <c r="AM81">
+        <v>-1</v>
+      </c>
+      <c r="AN81">
+        <v>-1</v>
+      </c>
+      <c r="AO81">
+        <v>-1</v>
+      </c>
+      <c r="AP81">
+        <v>-1</v>
+      </c>
+      <c r="AQ81">
+        <v>0</v>
+      </c>
+      <c r="AR81">
+        <v>0</v>
+      </c>
+      <c r="AS81">
+        <v>0</v>
+      </c>
+      <c r="AT81">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Waterhouse</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Cavalier</t>
         </is>
       </c>
-      <c r="G77">
-        <v>0</v>
-      </c>
-      <c r="H77">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>0</v>
-      </c>
-      <c r="J77">
-        <v>0</v>
-      </c>
-      <c r="K77">
-        <v>0</v>
-      </c>
-      <c r="L77">
-        <v>0</v>
-      </c>
-      <c r="M77" t="inlineStr">
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>0</v>
-      </c>
-      <c r="P77">
-        <v>0</v>
-      </c>
-      <c r="Q77">
-        <v>0</v>
-      </c>
-      <c r="R77">
-        <v>0</v>
-      </c>
-      <c r="S77">
-        <v>0</v>
-      </c>
-      <c r="T77">
-        <v>0</v>
-      </c>
-      <c r="U77">
-        <v>0</v>
-      </c>
-      <c r="V77">
-        <v>0</v>
-      </c>
-      <c r="W77">
-        <v>0</v>
-      </c>
-      <c r="X77">
-        <v>0</v>
-      </c>
-      <c r="Y77">
-        <v>0</v>
-      </c>
-      <c r="Z77">
-        <v>0</v>
-      </c>
-      <c r="AA77">
-        <v>0</v>
-      </c>
-      <c r="AB77">
-        <v>0</v>
-      </c>
-      <c r="AC77">
-        <v>0</v>
-      </c>
-      <c r="AD77">
-        <v>0</v>
-      </c>
-      <c r="AE77">
-        <v>0</v>
-      </c>
-      <c r="AF77">
-        <v>0</v>
-      </c>
-      <c r="AG77">
-        <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>0</v>
-      </c>
-      <c r="AK77">
-        <v>0</v>
-      </c>
-      <c r="AL77">
-        <v>0</v>
-      </c>
-      <c r="AM77">
-        <v>-1</v>
-      </c>
-      <c r="AN77">
-        <v>-1</v>
-      </c>
-      <c r="AO77">
-        <v>-1</v>
-      </c>
-      <c r="AP77">
-        <v>-1</v>
-      </c>
-      <c r="AQ77">
-        <v>0</v>
-      </c>
-      <c r="AR77">
-        <v>0</v>
-      </c>
-      <c r="AS77">
-        <v>0</v>
-      </c>
-      <c r="AT77">
-        <v>0</v>
-      </c>
-      <c r="AU77" t="inlineStr">
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <v>0</v>
+      </c>
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+      <c r="AA82">
+        <v>0</v>
+      </c>
+      <c r="AB82">
+        <v>0</v>
+      </c>
+      <c r="AC82">
+        <v>0</v>
+      </c>
+      <c r="AD82">
+        <v>0</v>
+      </c>
+      <c r="AE82">
+        <v>0</v>
+      </c>
+      <c r="AF82">
+        <v>0</v>
+      </c>
+      <c r="AG82">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
+        <v>0</v>
+      </c>
+      <c r="AK82">
+        <v>0</v>
+      </c>
+      <c r="AL82">
+        <v>0</v>
+      </c>
+      <c r="AM82">
+        <v>-1</v>
+      </c>
+      <c r="AN82">
+        <v>-1</v>
+      </c>
+      <c r="AO82">
+        <v>-1</v>
+      </c>
+      <c r="AP82">
+        <v>-1</v>
+      </c>
+      <c r="AQ82">
+        <v>0</v>
+      </c>
+      <c r="AR82">
+        <v>0</v>
+      </c>
+      <c r="AS82">
+        <v>0</v>
+      </c>
+      <c r="AT82">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
         <is>
           <t>2026-11-02 22:00:00</t>
         </is>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G27">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC81">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G7">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N21">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G59">
@@ -12543,55 +12543,55 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R75">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="S75">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T75">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="U75">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V75">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="W75">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y75">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z75">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AA75">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC75">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD75">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE75">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF75">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG75">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK75">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G29">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G59">

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU82"/>
+  <dimension ref="A1:AU84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="G8">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-11-02 10:00:00</t>
+          <t>2026-11-02 09:00:00</t>
         </is>
       </c>
     </row>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G9">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Safa</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00:00</t>
+          <t>2026-11-02 10:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-11-02 12:00:00</t>
+          <t>2026-11-02 10:00:00</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Safa</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>5.02</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2386,22 +2386,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>5.02</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.76</v>
+        <v>1.99</v>
       </c>
       <c r="O15">
-        <v>3.86</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>4.64</v>
+        <v>3.64</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-11-02 12:15:00</t>
+          <t>2026-11-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-11-02 12:30:00</t>
+          <t>2026-11-02 12:00:00</t>
         </is>
       </c>
     </row>
@@ -3033,27 +3033,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="O17">
-        <v>2.75</v>
+        <v>3.86</v>
       </c>
       <c r="P17">
-        <v>3.4</v>
+        <v>4.64</v>
       </c>
       <c r="Q17">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>2.78</v>
+        <v>1.91</v>
       </c>
       <c r="AB17">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="AC17">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-11-02 13:00:00</t>
+          <t>2026-11-02 12:15:00</t>
         </is>
       </c>
     </row>
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-11-02 13:00:00</t>
+          <t>2026-11-02 12:30:00</t>
         </is>
       </c>
     </row>
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atromitos</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="O19">
+        <v>2.75</v>
+      </c>
+      <c r="P19">
         <v>3.4</v>
       </c>
-      <c r="P19">
-        <v>3.7</v>
-      </c>
       <c r="Q19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA19">
-        <v>2.03</v>
+        <v>2.78</v>
       </c>
       <c r="AB19">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G20">
@@ -3685,12 +3685,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Temouchent</t>
+          <t>Atromitos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>US Biskra</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3771,10 +3771,10 @@
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC21">
         <v>0</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2026-11-02 13:45:00</t>
+          <t>2026-11-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -3848,12 +3848,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3934,10 +3934,10 @@
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AB22">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC22">
         <v>0</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2026-11-02 14:00:00</t>
+          <t>2026-11-02 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Temouchent</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>US Biskra</t>
         </is>
       </c>
       <c r="G23">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2026-11-02 14:00:00</t>
+          <t>2026-11-02 13:45:00</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G27">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G28">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,22 +5157,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G30">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5483,22 +5483,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5646,22 +5646,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5972,22 +5972,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Muğlaspor</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G35">
@@ -6130,27 +6130,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Muğlaspor</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.04</v>
+        <v>2.47</v>
       </c>
       <c r="O39">
-        <v>3.73</v>
+        <v>3.24</v>
       </c>
       <c r="P39">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P40">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="O41">
-        <v>3.1</v>
+        <v>3.73</v>
       </c>
       <c r="P41">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7113,22 +7113,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.7</v>
+        <v>1.93</v>
       </c>
       <c r="O42">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="P42">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -7194,10 +7194,10 @@
         <v>0</v>
       </c>
       <c r="AA42">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC42">
         <v>0</v>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.19</v>
+        <v>3.2</v>
       </c>
       <c r="O43">
-        <v>3.56</v>
+        <v>3.1</v>
       </c>
       <c r="P43">
-        <v>2.92</v>
+        <v>2.15</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7357,10 +7357,10 @@
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC43">
         <v>0</v>
@@ -7439,7 +7439,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="O44">
-        <v>3.4</v>
+        <v>2.99</v>
       </c>
       <c r="P44">
-        <v>2.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>1.81</v>
+        <v>2.19</v>
       </c>
       <c r="O45">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="P45">
-        <v>3.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>7.65</v>
+        <v>2.26</v>
       </c>
       <c r="O46">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>1.29</v>
+        <v>2.97</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>6.65</v>
+        <v>1.81</v>
       </c>
       <c r="O47">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="P47">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.1</v>
+        <v>7.65</v>
       </c>
       <c r="O48">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="P48">
-        <v>2.71</v>
+        <v>1.29</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8249,27 +8249,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.96</v>
+        <v>6.65</v>
       </c>
       <c r="O49">
-        <v>3.68</v>
+        <v>4.7</v>
       </c>
       <c r="P49">
-        <v>3.37</v>
+        <v>1.4</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>2026-11-02 15:05:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8412,27 +8412,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="O50">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="P50">
-        <v>3.22</v>
+        <v>2.71</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8563,7 +8563,7 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8575,27 +8575,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="O51">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="P51">
-        <v>2.7</v>
+        <v>3.37</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:05:00</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.51</v>
+        <v>2.09</v>
       </c>
       <c r="O52">
         <v>3.5</v>
       </c>
       <c r="P52">
-        <v>2.28</v>
+        <v>3.22</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8901,12 +8901,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9052,7 +9052,7 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -9064,27 +9064,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q54">
         <v>0</v>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G56">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G59">
@@ -10047,22 +10047,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,13 +10252,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P61">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10368,27 +10368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,13 +10415,13 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="O62">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P62">
-        <v>2.43</v>
+        <v>4.07</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -10454,10 +10454,10 @@
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P63">
-        <v>2.87</v>
+        <v>2.44</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="O64">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="P64">
-        <v>2.96</v>
+        <v>2.43</v>
       </c>
       <c r="Q64">
         <v>0</v>
@@ -10780,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC64">
         <v>0</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="O65">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>3.43</v>
+        <v>2.87</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="P66">
-        <v>3.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AB66">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.93</v>
+        <v>1.98</v>
       </c>
       <c r="O67">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
-        <v>2.52</v>
+        <v>3.43</v>
       </c>
       <c r="Q67">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T67">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U67">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W67">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y67">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z67">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AA67">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC67">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE67">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF67">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG67">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK67">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-11-02 16:45:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="O68">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P68">
-        <v>3</v>
+        <v>3.92</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="AB68">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-11-02 16:45:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.43</v>
+        <v>2.93</v>
       </c>
       <c r="O69">
-        <v>5</v>
+        <v>3.62</v>
       </c>
       <c r="P69">
-        <v>8.550000000000001</v>
+        <v>2.52</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="O70">
-        <v>3.78</v>
+        <v>3.1</v>
       </c>
       <c r="P70">
-        <v>3.23</v>
+        <v>3</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>1.66</v>
+        <v>2.03</v>
       </c>
       <c r="AB70">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O71">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P71">
-        <v>8.199999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.93</v>
+        <v>1.4</v>
       </c>
       <c r="O73">
-        <v>3.36</v>
+        <v>4.9</v>
       </c>
       <c r="P73">
-        <v>2.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AB73">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -12324,12 +12324,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="O74">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="P74">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12416,10 +12416,10 @@
         <v>0</v>
       </c>
       <c r="AC74">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD74">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE74">
         <v>0</v>
@@ -12475,7 +12475,7 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -12487,27 +12487,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-11-02 17:30:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -12650,27 +12650,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>9.85</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12742,10 +12742,10 @@
         <v>0</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE76">
         <v>0</v>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -12976,27 +12976,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G78">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-11-02 19:05:00</t>
+          <t>2026-11-02 18:00:00</t>
         </is>
       </c>
     </row>
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O79">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="P79">
-        <v>3.59</v>
+        <v>3.21</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-11-02 20:00:00</t>
+          <t>2026-11-02 18:00:00</t>
         </is>
       </c>
     </row>
@@ -13302,27 +13302,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G80">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-11-02 20:30:00</t>
+          <t>2026-11-02 19:05:00</t>
         </is>
       </c>
     </row>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.44</v>
+        <v>2</v>
       </c>
       <c r="O81">
-        <v>3.36</v>
+        <v>3.8</v>
       </c>
       <c r="P81">
-        <v>2.64</v>
+        <v>3.59</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AB81">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-11-02 20:30:00</t>
+          <t>2026-11-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -13628,156 +13628,482 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Palestino</t>
+        </is>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <v>0</v>
+      </c>
+      <c r="U82">
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0</v>
+      </c>
+      <c r="X82">
+        <v>0</v>
+      </c>
+      <c r="Y82">
+        <v>0</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+      <c r="AA82">
+        <v>0</v>
+      </c>
+      <c r="AB82">
+        <v>0</v>
+      </c>
+      <c r="AC82">
+        <v>0</v>
+      </c>
+      <c r="AD82">
+        <v>0</v>
+      </c>
+      <c r="AE82">
+        <v>0</v>
+      </c>
+      <c r="AF82">
+        <v>0</v>
+      </c>
+      <c r="AG82">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ82">
+        <v>0</v>
+      </c>
+      <c r="AK82">
+        <v>0</v>
+      </c>
+      <c r="AL82">
+        <v>0</v>
+      </c>
+      <c r="AM82">
+        <v>-1</v>
+      </c>
+      <c r="AN82">
+        <v>-1</v>
+      </c>
+      <c r="AO82">
+        <v>-1</v>
+      </c>
+      <c r="AP82">
+        <v>-1</v>
+      </c>
+      <c r="AQ82">
+        <v>0</v>
+      </c>
+      <c r="AR82">
+        <v>0</v>
+      </c>
+      <c r="AS82">
+        <v>0</v>
+      </c>
+      <c r="AT82">
+        <v>0</v>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N83">
+        <v>2.44</v>
+      </c>
+      <c r="O83">
+        <v>3.36</v>
+      </c>
+      <c r="P83">
+        <v>2.64</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>0</v>
+      </c>
+      <c r="U83">
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0</v>
+      </c>
+      <c r="X83">
+        <v>0</v>
+      </c>
+      <c r="Y83">
+        <v>0</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+      <c r="AA83">
+        <v>1.73</v>
+      </c>
+      <c r="AB83">
+        <v>1.98</v>
+      </c>
+      <c r="AC83">
+        <v>0</v>
+      </c>
+      <c r="AD83">
+        <v>0</v>
+      </c>
+      <c r="AE83">
+        <v>0</v>
+      </c>
+      <c r="AF83">
+        <v>0</v>
+      </c>
+      <c r="AG83">
+        <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
+        <v>0</v>
+      </c>
+      <c r="AK83">
+        <v>0</v>
+      </c>
+      <c r="AL83">
+        <v>0</v>
+      </c>
+      <c r="AM83">
+        <v>-1</v>
+      </c>
+      <c r="AN83">
+        <v>-1</v>
+      </c>
+      <c r="AO83">
+        <v>-1</v>
+      </c>
+      <c r="AP83">
+        <v>-1</v>
+      </c>
+      <c r="AQ83">
+        <v>0</v>
+      </c>
+      <c r="AR83">
+        <v>0</v>
+      </c>
+      <c r="AS83">
+        <v>0</v>
+      </c>
+      <c r="AT83">
+        <v>0</v>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Waterhouse</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Cavalier</t>
         </is>
       </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-      <c r="H82">
-        <v>0</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82">
-        <v>0</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82" t="inlineStr">
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>0</v>
-      </c>
-      <c r="Q82">
-        <v>0</v>
-      </c>
-      <c r="R82">
-        <v>0</v>
-      </c>
-      <c r="S82">
-        <v>0</v>
-      </c>
-      <c r="T82">
-        <v>0</v>
-      </c>
-      <c r="U82">
-        <v>0</v>
-      </c>
-      <c r="V82">
-        <v>0</v>
-      </c>
-      <c r="W82">
-        <v>0</v>
-      </c>
-      <c r="X82">
-        <v>0</v>
-      </c>
-      <c r="Y82">
-        <v>0</v>
-      </c>
-      <c r="Z82">
-        <v>0</v>
-      </c>
-      <c r="AA82">
-        <v>0</v>
-      </c>
-      <c r="AB82">
-        <v>0</v>
-      </c>
-      <c r="AC82">
-        <v>0</v>
-      </c>
-      <c r="AD82">
-        <v>0</v>
-      </c>
-      <c r="AE82">
-        <v>0</v>
-      </c>
-      <c r="AF82">
-        <v>0</v>
-      </c>
-      <c r="AG82">
-        <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ82">
-        <v>0</v>
-      </c>
-      <c r="AK82">
-        <v>0</v>
-      </c>
-      <c r="AL82">
-        <v>0</v>
-      </c>
-      <c r="AM82">
-        <v>-1</v>
-      </c>
-      <c r="AN82">
-        <v>-1</v>
-      </c>
-      <c r="AO82">
-        <v>-1</v>
-      </c>
-      <c r="AP82">
-        <v>-1</v>
-      </c>
-      <c r="AQ82">
-        <v>0</v>
-      </c>
-      <c r="AR82">
-        <v>0</v>
-      </c>
-      <c r="AS82">
-        <v>0</v>
-      </c>
-      <c r="AT82">
-        <v>0</v>
-      </c>
-      <c r="AU82" t="inlineStr">
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+      <c r="AA84">
+        <v>0</v>
+      </c>
+      <c r="AB84">
+        <v>0</v>
+      </c>
+      <c r="AC84">
+        <v>0</v>
+      </c>
+      <c r="AD84">
+        <v>0</v>
+      </c>
+      <c r="AE84">
+        <v>0</v>
+      </c>
+      <c r="AF84">
+        <v>0</v>
+      </c>
+      <c r="AG84">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
+        <v>0</v>
+      </c>
+      <c r="AK84">
+        <v>0</v>
+      </c>
+      <c r="AL84">
+        <v>0</v>
+      </c>
+      <c r="AM84">
+        <v>-1</v>
+      </c>
+      <c r="AN84">
+        <v>-1</v>
+      </c>
+      <c r="AO84">
+        <v>-1</v>
+      </c>
+      <c r="AP84">
+        <v>-1</v>
+      </c>
+      <c r="AQ84">
+        <v>0</v>
+      </c>
+      <c r="AR84">
+        <v>0</v>
+      </c>
+      <c r="AS84">
+        <v>0</v>
+      </c>
+      <c r="AT84">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
         <is>
           <t>2026-11-02 22:00:00</t>
         </is>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G60">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G61">

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2763,55 +2763,55 @@
         <v>3.64</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC40">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2600,55 +2600,55 @@
         <v>1.45</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q77">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU84"/>
+  <dimension ref="A1:AU85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G7">
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="O70">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P70">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA70">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AB70">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="O71">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="P71">
-        <v>8.550000000000001</v>
+        <v>3</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.27</v>
+        <v>1.43</v>
       </c>
       <c r="O72">
-        <v>3.78</v>
+        <v>5</v>
       </c>
       <c r="P72">
-        <v>3.23</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12084,10 +12084,10 @@
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AB72">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC72">
         <v>0</v>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.4</v>
+        <v>2.27</v>
       </c>
       <c r="O73">
-        <v>4.9</v>
+        <v>3.78</v>
       </c>
       <c r="P73">
-        <v>8.199999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AB73">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12487,12 +12487,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.13</v>
+        <v>2.93</v>
       </c>
       <c r="O76">
-        <v>9.85</v>
+        <v>3.36</v>
       </c>
       <c r="P76">
-        <v>21</v>
+        <v>2.55</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,16 +12736,16 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC76">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AD76">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE76">
         <v>0</v>
@@ -12813,27 +12813,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.83</v>
+        <v>1.13</v>
       </c>
       <c r="O77">
-        <v>3.34</v>
+        <v>9.85</v>
       </c>
       <c r="P77">
-        <v>4.49</v>
+        <v>21</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12905,10 +12905,10 @@
         <v>0</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-11-02 17:30:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -12976,12 +12976,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13302,27 +13302,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-11-02 19:05:00</t>
+          <t>2026-11-02 18:00:00</t>
         </is>
       </c>
     </row>
@@ -13465,27 +13465,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB81">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-11-02 20:00:00</t>
+          <t>2026-11-02 19:05:00</t>
         </is>
       </c>
     </row>
@@ -13628,12 +13628,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-11-02 20:30:00</t>
+          <t>2026-11-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB83">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -13954,156 +13954,319 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N84">
+        <v>2.44</v>
+      </c>
+      <c r="O84">
+        <v>3.36</v>
+      </c>
+      <c r="P84">
+        <v>2.64</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+      <c r="AA84">
+        <v>1.73</v>
+      </c>
+      <c r="AB84">
+        <v>1.98</v>
+      </c>
+      <c r="AC84">
+        <v>0</v>
+      </c>
+      <c r="AD84">
+        <v>0</v>
+      </c>
+      <c r="AE84">
+        <v>0</v>
+      </c>
+      <c r="AF84">
+        <v>0</v>
+      </c>
+      <c r="AG84">
+        <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ84">
+        <v>0</v>
+      </c>
+      <c r="AK84">
+        <v>0</v>
+      </c>
+      <c r="AL84">
+        <v>0</v>
+      </c>
+      <c r="AM84">
+        <v>-1</v>
+      </c>
+      <c r="AN84">
+        <v>-1</v>
+      </c>
+      <c r="AO84">
+        <v>-1</v>
+      </c>
+      <c r="AP84">
+        <v>-1</v>
+      </c>
+      <c r="AQ84">
+        <v>0</v>
+      </c>
+      <c r="AR84">
+        <v>0</v>
+      </c>
+      <c r="AS84">
+        <v>0</v>
+      </c>
+      <c r="AT84">
+        <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Waterhouse</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Cavalier</t>
         </is>
       </c>
-      <c r="G84">
-        <v>0</v>
-      </c>
-      <c r="H84">
-        <v>0</v>
-      </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
-      <c r="J84">
-        <v>0</v>
-      </c>
-      <c r="K84">
-        <v>0</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84" t="inlineStr">
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84">
-        <v>0</v>
-      </c>
-      <c r="R84">
-        <v>0</v>
-      </c>
-      <c r="S84">
-        <v>0</v>
-      </c>
-      <c r="T84">
-        <v>0</v>
-      </c>
-      <c r="U84">
-        <v>0</v>
-      </c>
-      <c r="V84">
-        <v>0</v>
-      </c>
-      <c r="W84">
-        <v>0</v>
-      </c>
-      <c r="X84">
-        <v>0</v>
-      </c>
-      <c r="Y84">
-        <v>0</v>
-      </c>
-      <c r="Z84">
-        <v>0</v>
-      </c>
-      <c r="AA84">
-        <v>0</v>
-      </c>
-      <c r="AB84">
-        <v>0</v>
-      </c>
-      <c r="AC84">
-        <v>0</v>
-      </c>
-      <c r="AD84">
-        <v>0</v>
-      </c>
-      <c r="AE84">
-        <v>0</v>
-      </c>
-      <c r="AF84">
-        <v>0</v>
-      </c>
-      <c r="AG84">
-        <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ84">
-        <v>0</v>
-      </c>
-      <c r="AK84">
-        <v>0</v>
-      </c>
-      <c r="AL84">
-        <v>0</v>
-      </c>
-      <c r="AM84">
-        <v>-1</v>
-      </c>
-      <c r="AN84">
-        <v>-1</v>
-      </c>
-      <c r="AO84">
-        <v>-1</v>
-      </c>
-      <c r="AP84">
-        <v>-1</v>
-      </c>
-      <c r="AQ84">
-        <v>0</v>
-      </c>
-      <c r="AR84">
-        <v>0</v>
-      </c>
-      <c r="AS84">
-        <v>0</v>
-      </c>
-      <c r="AT84">
-        <v>0</v>
-      </c>
-      <c r="AU84" t="inlineStr">
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>0</v>
+      </c>
+      <c r="U85">
+        <v>0</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
+      </c>
+      <c r="X85">
+        <v>0</v>
+      </c>
+      <c r="Y85">
+        <v>0</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+      <c r="AA85">
+        <v>0</v>
+      </c>
+      <c r="AB85">
+        <v>0</v>
+      </c>
+      <c r="AC85">
+        <v>0</v>
+      </c>
+      <c r="AD85">
+        <v>0</v>
+      </c>
+      <c r="AE85">
+        <v>0</v>
+      </c>
+      <c r="AF85">
+        <v>0</v>
+      </c>
+      <c r="AG85">
+        <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
+        <v>0</v>
+      </c>
+      <c r="AK85">
+        <v>0</v>
+      </c>
+      <c r="AL85">
+        <v>0</v>
+      </c>
+      <c r="AM85">
+        <v>-1</v>
+      </c>
+      <c r="AN85">
+        <v>-1</v>
+      </c>
+      <c r="AO85">
+        <v>-1</v>
+      </c>
+      <c r="AP85">
+        <v>-1</v>
+      </c>
+      <c r="AQ85">
+        <v>0</v>
+      </c>
+      <c r="AR85">
+        <v>0</v>
+      </c>
+      <c r="AS85">
+        <v>0</v>
+      </c>
+      <c r="AT85">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
         <is>
           <t>2026-11-02 22:00:00</t>
         </is>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q56">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G6">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -3089,34 +3089,34 @@
         <v>4.64</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
         <v>1.91</v>
@@ -3125,19 +3125,19 @@
         <v>1.89</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>2.29</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3741,34 +3741,34 @@
         <v>3.7</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA21">
         <v>2.03</v>
@@ -3777,19 +3777,19 @@
         <v>1.78</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>3.23</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA24">
         <v>1.97</v>
@@ -4266,19 +4266,19 @@
         <v>1.79</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G29">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5697,55 +5697,55 @@
         <v>2.82</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,55 +5860,55 @@
         <v>2.65</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6512,55 +6512,55 @@
         <v>3.8</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6838,34 +6838,34 @@
         <v>4.98</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA40">
         <v>1.93</v>
@@ -6874,19 +6874,19 @@
         <v>1.83</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>2.39</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>3.8</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>1.29</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>7.03</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>1.4</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>4.73</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8468,55 +8468,55 @@
         <v>2.71</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8794,55 +8794,55 @@
         <v>3.22</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8957,55 +8957,55 @@
         <v>2.7</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9120,55 +9120,55 @@
         <v>2.28</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X54">
         <v>0</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9446,55 +9446,55 @@
         <v>3</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10424,34 +10424,34 @@
         <v>4.07</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA62">
         <v>2</v>
@@ -10460,19 +10460,19 @@
         <v>1.71</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O63">
         <v>3.34</v>
       </c>
       <c r="P63">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O64">
         <v>3.34</v>
       </c>
       <c r="P64">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,55 +10913,55 @@
         <v>2.87</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11076,34 +11076,34 @@
         <v>2.96</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA66">
         <v>1.88</v>
@@ -11112,19 +11112,19 @@
         <v>1.93</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11239,55 +11239,55 @@
         <v>3.43</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11402,34 +11402,34 @@
         <v>3.92</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA68">
         <v>1.83</v>
@@ -11438,19 +11438,19 @@
         <v>1.98</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11891,34 +11891,34 @@
         <v>3</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="AA71">
         <v>2.03</v>
@@ -11927,19 +11927,19 @@
         <v>1.78</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12054,55 +12054,55 @@
         <v>8.550000000000001</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12380,34 +12380,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA74">
         <v>1.84</v>
@@ -12416,19 +12416,19 @@
         <v>1.96</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12543,55 +12543,55 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12706,34 +12706,34 @@
         <v>2.55</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA76">
         <v>2.15</v>
@@ -12742,19 +12742,19 @@
         <v>1.6</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12869,40 +12869,40 @@
         <v>21</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC77">
         <v>1.93</v>
@@ -12911,13 +12911,13 @@
         <v>1.75</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13358,55 +13358,55 @@
         <v>3.21</v>
       </c>
       <c r="Q80">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T80">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U80">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V80">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W80">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X80">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y80">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z80">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE80">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF80">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG80">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK80">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14010,34 +14010,34 @@
         <v>2.64</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AA84">
         <v>1.73</v>
@@ -14046,19 +14046,19 @@
         <v>1.98</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL84">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G5">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G7">
@@ -7653,55 +7653,55 @@
         <v>2.92</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -8631,55 +8631,55 @@
         <v>3.37</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O63">
         <v>3.34</v>
       </c>
       <c r="P63">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="Q63">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R63">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S63">
         <v>1.3</v>
       </c>
       <c r="T63">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U63">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V63">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W63">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X63">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z63">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA63">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB63">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC63">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD63">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE63">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG63">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O64">
         <v>3.34</v>
       </c>
       <c r="P64">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="Q64">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="R64">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S64">
         <v>1.3</v>
       </c>
       <c r="T64">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U64">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="V64">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W64">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X64">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y64">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z64">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA64">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AB64">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="AC64">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD64">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE64">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF64">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AG64">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -12217,34 +12217,34 @@
         <v>3.23</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA73">
         <v>1.66</v>
@@ -12253,19 +12253,19 @@
         <v>2.1</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.93</v>
+        <v>1.13</v>
       </c>
       <c r="O76">
-        <v>3.36</v>
+        <v>9.85</v>
       </c>
       <c r="P76">
-        <v>2.55</v>
+        <v>21</v>
       </c>
       <c r="Q76">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="R76">
-        <v>2.05</v>
+        <v>3.06</v>
       </c>
       <c r="S76">
+        <v>1.22</v>
+      </c>
+      <c r="T76">
+        <v>4</v>
+      </c>
+      <c r="U76">
+        <v>1.97</v>
+      </c>
+      <c r="V76">
+        <v>1.72</v>
+      </c>
+      <c r="W76">
+        <v>1.2</v>
+      </c>
+      <c r="X76">
+        <v>1</v>
+      </c>
+      <c r="Y76">
+        <v>1.11</v>
+      </c>
+      <c r="Z76">
+        <v>4.84</v>
+      </c>
+      <c r="AA76">
         <v>1.4</v>
       </c>
-      <c r="T76">
-        <v>2.7</v>
-      </c>
-      <c r="U76">
-        <v>3.1</v>
-      </c>
-      <c r="V76">
-        <v>1.33</v>
-      </c>
-      <c r="W76">
-        <v>1.06</v>
-      </c>
-      <c r="X76">
-        <v>1.05</v>
-      </c>
-      <c r="Y76">
-        <v>1.4</v>
-      </c>
-      <c r="Z76">
-        <v>2.66</v>
-      </c>
-      <c r="AA76">
-        <v>2.15</v>
-      </c>
       <c r="AB76">
-        <v>1.6</v>
+        <v>2.87</v>
       </c>
       <c r="AC76">
-        <v>4.2</v>
+        <v>1.93</v>
       </c>
       <c r="AD76">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AE76">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="AF76">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG76">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK76">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,80 +12860,80 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.13</v>
+        <v>2.93</v>
       </c>
       <c r="O77">
-        <v>9.85</v>
+        <v>3.36</v>
       </c>
       <c r="P77">
-        <v>21</v>
+        <v>2.55</v>
       </c>
       <c r="Q77">
-        <v>1.47</v>
+        <v>3.5</v>
       </c>
       <c r="R77">
-        <v>3.06</v>
+        <v>2.05</v>
       </c>
       <c r="S77">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T77">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="U77">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="V77">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y77">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="Z77">
-        <v>4.84</v>
+        <v>2.66</v>
       </c>
       <c r="AA77">
+        <v>2.15</v>
+      </c>
+      <c r="AB77">
+        <v>1.6</v>
+      </c>
+      <c r="AC77">
+        <v>4.2</v>
+      </c>
+      <c r="AD77">
+        <v>1.18</v>
+      </c>
+      <c r="AE77">
+        <v>1.04</v>
+      </c>
+      <c r="AF77">
+        <v>1.87</v>
+      </c>
+      <c r="AG77">
+        <v>1.83</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
+        <v>1.33</v>
+      </c>
+      <c r="AK77">
         <v>1.4</v>
-      </c>
-      <c r="AB77">
-        <v>2.87</v>
-      </c>
-      <c r="AC77">
-        <v>1.93</v>
-      </c>
-      <c r="AD77">
-        <v>1.75</v>
-      </c>
-      <c r="AE77">
-        <v>1.34</v>
-      </c>
-      <c r="AF77">
-        <v>2</v>
-      </c>
-      <c r="AG77">
-        <v>1.75</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.1</v>
-      </c>
-      <c r="AK77">
-        <v>4.8</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13032,55 +13032,55 @@
         <v>4.49</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13684,34 +13684,34 @@
         <v>3.59</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA82">
         <v>1.68</v>
@@ -13720,19 +13720,19 @@
         <v>2</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL83">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU85"/>
+  <dimension ref="A1:AU86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.68</v>
+        <v>4.06</v>
       </c>
       <c r="O30">
-        <v>3.27</v>
+        <v>3.72</v>
       </c>
       <c r="P30">
-        <v>2.68</v>
+        <v>1.86</v>
       </c>
       <c r="Q30">
-        <v>3.3</v>
+        <v>4.45</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="S30">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="T30">
-        <v>2.61</v>
+        <v>2.95</v>
       </c>
       <c r="U30">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z30">
-        <v>2.83</v>
+        <v>3.52</v>
       </c>
       <c r="AA30">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB30">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC30">
-        <v>4.28</v>
+        <v>3.04</v>
       </c>
       <c r="AD30">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE30">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AG30">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK30">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,65 +5362,65 @@
         </is>
       </c>
       <c r="N31">
-        <v>4.06</v>
+        <v>2.68</v>
       </c>
       <c r="O31">
-        <v>3.72</v>
+        <v>3.27</v>
       </c>
       <c r="P31">
+        <v>2.68</v>
+      </c>
+      <c r="Q31">
+        <v>3.3</v>
+      </c>
+      <c r="R31">
+        <v>2</v>
+      </c>
+      <c r="S31">
+        <v>1.39</v>
+      </c>
+      <c r="T31">
+        <v>2.61</v>
+      </c>
+      <c r="U31">
+        <v>3.2</v>
+      </c>
+      <c r="V31">
+        <v>1.3</v>
+      </c>
+      <c r="W31">
+        <v>1.05</v>
+      </c>
+      <c r="X31">
+        <v>1.03</v>
+      </c>
+      <c r="Y31">
+        <v>1.33</v>
+      </c>
+      <c r="Z31">
+        <v>2.83</v>
+      </c>
+      <c r="AA31">
+        <v>2.2</v>
+      </c>
+      <c r="AB31">
+        <v>1.65</v>
+      </c>
+      <c r="AC31">
+        <v>4.28</v>
+      </c>
+      <c r="AD31">
+        <v>1.2</v>
+      </c>
+      <c r="AE31">
+        <v>1.04</v>
+      </c>
+      <c r="AF31">
+        <v>1.83</v>
+      </c>
+      <c r="AG31">
         <v>1.86</v>
       </c>
-      <c r="Q31">
-        <v>4.45</v>
-      </c>
-      <c r="R31">
-        <v>2.15</v>
-      </c>
-      <c r="S31">
-        <v>1.31</v>
-      </c>
-      <c r="T31">
-        <v>2.95</v>
-      </c>
-      <c r="U31">
-        <v>2.55</v>
-      </c>
-      <c r="V31">
-        <v>1.41</v>
-      </c>
-      <c r="W31">
-        <v>1.07</v>
-      </c>
-      <c r="X31">
-        <v>1</v>
-      </c>
-      <c r="Y31">
-        <v>1.25</v>
-      </c>
-      <c r="Z31">
-        <v>3.52</v>
-      </c>
-      <c r="AA31">
-        <v>1.98</v>
-      </c>
-      <c r="AB31">
-        <v>1.83</v>
-      </c>
-      <c r="AC31">
-        <v>3.04</v>
-      </c>
-      <c r="AD31">
-        <v>1.29</v>
-      </c>
-      <c r="AE31">
-        <v>1.08</v>
-      </c>
-      <c r="AF31">
-        <v>1.73</v>
-      </c>
-      <c r="AG31">
-        <v>1.97</v>
-      </c>
       <c r="AH31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AK31">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-11-02 14:30:00</t>
+          <t>2026-11-02 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kalamata</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Iraklis Thessaloniki</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="O39">
-        <v>3.24</v>
+        <v>3.59</v>
       </c>
       <c r="P39">
-        <v>2.77</v>
+        <v>3.8</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA39">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB39">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Kalamata</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Iraklis Thessaloniki</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.64</v>
+        <v>2.47</v>
       </c>
       <c r="O40">
-        <v>3.75</v>
+        <v>3.24</v>
       </c>
       <c r="P40">
-        <v>4.98</v>
+        <v>2.77</v>
       </c>
       <c r="Q40">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R40">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S40">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T40">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W40">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X40">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z40">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AA40">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB40">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC40">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="AD40">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE40">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF40">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG40">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK40">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.04</v>
+        <v>1.64</v>
       </c>
       <c r="O41">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="P41">
-        <v>2.39</v>
+        <v>4.98</v>
       </c>
       <c r="Q41">
-        <v>3.06</v>
+        <v>2.18</v>
       </c>
       <c r="R41">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S41">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="T41">
-        <v>3.26</v>
+        <v>2.75</v>
       </c>
       <c r="U41">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z41">
-        <v>4.61</v>
+        <v>2.81</v>
       </c>
       <c r="AA41">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AB41">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="AC41">
-        <v>2.49</v>
+        <v>3.74</v>
       </c>
       <c r="AD41">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AE41">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AF41">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AG41">
-        <v>2.4</v>
+        <v>1.64</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>1.44</v>
+        <v>2.23</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CD Feirense</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,80 +7155,80 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.93</v>
+        <v>3.04</v>
       </c>
       <c r="O42">
-        <v>3.36</v>
+        <v>3.73</v>
       </c>
       <c r="P42">
-        <v>3.8</v>
+        <v>2.39</v>
       </c>
       <c r="Q42">
-        <v>2.56</v>
+        <v>3.06</v>
       </c>
       <c r="R42">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>2.71</v>
+        <v>3.26</v>
       </c>
       <c r="U42">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="W42">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>2.88</v>
+        <v>4.61</v>
       </c>
       <c r="AA42">
-        <v>2.08</v>
+        <v>1.6</v>
       </c>
       <c r="AB42">
-        <v>1.69</v>
+        <v>2.36</v>
       </c>
       <c r="AC42">
-        <v>3.58</v>
+        <v>2.49</v>
       </c>
       <c r="AD42">
+        <v>1.5</v>
+      </c>
+      <c r="AE42">
+        <v>1.2</v>
+      </c>
+      <c r="AF42">
+        <v>1.5</v>
+      </c>
+      <c r="AG42">
+        <v>2.4</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.25</v>
       </c>
-      <c r="AE42">
-        <v>1.05</v>
-      </c>
-      <c r="AF42">
-        <v>1.88</v>
-      </c>
-      <c r="AG42">
-        <v>1.8</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.33</v>
-      </c>
       <c r="AK42">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-11-02 15:00:00</t>
+          <t>2026-11-02 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7276,22 +7276,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>CD Feirense</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.2</v>
+        <v>1.93</v>
       </c>
       <c r="O43">
-        <v>3.1</v>
+        <v>3.36</v>
       </c>
       <c r="P43">
-        <v>2.15</v>
+        <v>3.8</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA43">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="AB43">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O44">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="P44">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -7520,10 +7520,10 @@
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB44">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC44">
         <v>0</v>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.19</v>
+        <v>3.7</v>
       </c>
       <c r="O45">
-        <v>3.56</v>
+        <v>2.99</v>
       </c>
       <c r="P45">
-        <v>2.92</v>
+        <v>2.1</v>
       </c>
       <c r="Q45">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S45">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T45">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U45">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V45">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W45">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z45">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.58</v>
+        <v>2.6</v>
       </c>
       <c r="AB45">
-        <v>2.29</v>
+        <v>1.47</v>
       </c>
       <c r="AC45">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AE45">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF45">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK45">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="O46">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="P46">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="O47">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
-        <v>3.9</v>
+        <v>2.97</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8091,22 +8091,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>7.65</v>
+        <v>1.81</v>
       </c>
       <c r="O48">
-        <v>5.9</v>
+        <v>3.75</v>
       </c>
       <c r="P48">
-        <v>1.29</v>
+        <v>3.9</v>
       </c>
       <c r="Q48">
-        <v>7.03</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W48">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y48">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Z48">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AC48">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE48">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF48">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG48">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>SønderjyskE</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>6.65</v>
+        <v>7.65</v>
       </c>
       <c r="O49">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="P49">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Q49">
-        <v>4.73</v>
+        <v>7.03</v>
       </c>
       <c r="R49">
-        <v>2.45</v>
+        <v>2.84</v>
       </c>
       <c r="S49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T49">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U49">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="V49">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Z49">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AA49">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="AB49">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="AC49">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="AD49">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="AE49">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF49">
         <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK49">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>SønderjyskE</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>København</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.1</v>
+        <v>6.65</v>
       </c>
       <c r="O50">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="P50">
-        <v>2.71</v>
+        <v>1.4</v>
       </c>
       <c r="Q50">
-        <v>2.31</v>
+        <v>4.73</v>
       </c>
       <c r="R50">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="S50">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="U50">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="V50">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="W50">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>9.699999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="AA50">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="AB50">
-        <v>4.03</v>
+        <v>2.6</v>
       </c>
       <c r="AC50">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="AD50">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="AE50">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AF50">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>3.9</v>
+        <v>2.25</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK50">
-        <v>1.69</v>
+        <v>1.07</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="O51">
-        <v>3.68</v>
+        <v>4.3</v>
       </c>
       <c r="P51">
-        <v>3.37</v>
+        <v>2.71</v>
       </c>
       <c r="Q51">
         <v>2.31</v>
       </c>
       <c r="R51">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.06</v>
       </c>
       <c r="T51">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="U51">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="V51">
-        <v>1.56</v>
+        <v>2.2</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.34</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="Z51">
-        <v>4.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA51">
-        <v>1.59</v>
+        <v>1.15</v>
       </c>
       <c r="AB51">
-        <v>2.32</v>
+        <v>4.03</v>
       </c>
       <c r="AC51">
-        <v>2.38</v>
+        <v>1.58</v>
       </c>
       <c r="AD51">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="AE51">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="AF51">
-        <v>1.55</v>
+        <v>1.19</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK51">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>2026-11-02 15:05:00</t>
+          <t>2026-11-02 15:00:00</t>
         </is>
       </c>
     </row>
@@ -8738,27 +8738,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,80 +8785,80 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="P52">
-        <v>3.22</v>
+        <v>3.37</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="R52">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="S52">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T52">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="U52">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="V52">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W52">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z52">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA52">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AB52">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="AC52">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AD52">
+        <v>1.53</v>
+      </c>
+      <c r="AE52">
+        <v>1.21</v>
+      </c>
+      <c r="AF52">
         <v>1.55</v>
       </c>
-      <c r="AE52">
+      <c r="AG52">
+        <v>2.3</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ52">
         <v>1.18</v>
       </c>
-      <c r="AF52">
-        <v>1.48</v>
-      </c>
-      <c r="AG52">
-        <v>2.5</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ52">
-        <v>1.23</v>
-      </c>
       <c r="AK52">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>2026-11-02 15:30:00</t>
+          <t>2026-11-02 15:05:00</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.6</v>
+        <v>2.09</v>
       </c>
       <c r="O53">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="Q53">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="R53">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="S53">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T53">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="U53">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="V53">
+        <v>1.6</v>
+      </c>
+      <c r="W53">
+        <v>1.15</v>
+      </c>
+      <c r="X53">
+        <v>1.02</v>
+      </c>
+      <c r="Y53">
+        <v>1.13</v>
+      </c>
+      <c r="Z53">
+        <v>4.5</v>
+      </c>
+      <c r="AA53">
+        <v>1.56</v>
+      </c>
+      <c r="AB53">
+        <v>2.35</v>
+      </c>
+      <c r="AC53">
+        <v>2.28</v>
+      </c>
+      <c r="AD53">
         <v>1.55</v>
       </c>
-      <c r="W53">
-        <v>1.12</v>
-      </c>
-      <c r="X53">
-        <v>1.01</v>
-      </c>
-      <c r="Y53">
-        <v>1.14</v>
-      </c>
-      <c r="Z53">
-        <v>4.4</v>
-      </c>
-      <c r="AA53">
-        <v>1.61</v>
-      </c>
-      <c r="AB53">
-        <v>2.25</v>
-      </c>
-      <c r="AC53">
-        <v>2.39</v>
-      </c>
-      <c r="AD53">
-        <v>1.43</v>
-      </c>
       <c r="AE53">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AG53">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK53">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,43 +9111,43 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="P54">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="Q54">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="R54">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="S54">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="T54">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="U54">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V54">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W54">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y54">
         <v>1.14</v>
       </c>
       <c r="Z54">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA54">
         <v>1.61</v>
@@ -9156,35 +9156,35 @@
         <v>2.25</v>
       </c>
       <c r="AC54">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AD54">
+        <v>1.43</v>
+      </c>
+      <c r="AE54">
+        <v>1.13</v>
+      </c>
+      <c r="AF54">
+        <v>1.5</v>
+      </c>
+      <c r="AG54">
+        <v>2.42</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ54">
+        <v>1.3</v>
+      </c>
+      <c r="AK54">
         <v>1.44</v>
-      </c>
-      <c r="AE54">
-        <v>1.14</v>
-      </c>
-      <c r="AF54">
-        <v>1.49</v>
-      </c>
-      <c r="AG54">
-        <v>2.39</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ54">
-        <v>1.47</v>
-      </c>
-      <c r="AK54">
-        <v>1.39</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X55">
         <v>0</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 15:30:00</t>
         </is>
       </c>
     </row>
@@ -9395,22 +9395,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q56">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="R56">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S56">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T56">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U56">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V56">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W56">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X56">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y56">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z56">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA56">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB56">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC56">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD56">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE56">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF56">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG56">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AK56">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="S58">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="T58">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="U58">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V58">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z58">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA58">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB58">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AC58">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AD58">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE58">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK58">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.15</v>
+        <v>1.1</v>
       </c>
       <c r="O59">
-        <v>3.88</v>
+        <v>7.2</v>
       </c>
       <c r="P59">
-        <v>2.48</v>
+        <v>9.6</v>
       </c>
       <c r="Q59">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="R59">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
       <c r="S59">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T59">
-        <v>3.65</v>
+        <v>4.45</v>
       </c>
       <c r="U59">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="V59">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="W59">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="X59">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z59">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="AA59">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="AB59">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AC59">
-        <v>2.16</v>
+        <v>1.71</v>
       </c>
       <c r="AD59">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="AE59">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="AF59">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="AK59">
-        <v>1.57</v>
+        <v>4.55</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>4.66</v>
+        <v>2.15</v>
       </c>
       <c r="O60">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="P60">
-        <v>1.47</v>
+        <v>2.48</v>
       </c>
       <c r="Q60">
-        <v>4.79</v>
+        <v>2.8</v>
       </c>
       <c r="R60">
-        <v>2.82</v>
+        <v>2.45</v>
       </c>
       <c r="S60">
+        <v>1.22</v>
+      </c>
+      <c r="T60">
+        <v>3.65</v>
+      </c>
+      <c r="U60">
+        <v>2.1</v>
+      </c>
+      <c r="V60">
+        <v>1.67</v>
+      </c>
+      <c r="W60">
         <v>1.18</v>
       </c>
-      <c r="T60">
-        <v>4.7</v>
-      </c>
-      <c r="U60">
-        <v>1.91</v>
-      </c>
-      <c r="V60">
-        <v>1.84</v>
-      </c>
-      <c r="W60">
-        <v>1.22</v>
-      </c>
       <c r="X60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z60">
-        <v>5.63</v>
+        <v>5.75</v>
       </c>
       <c r="AA60">
-        <v>1.28</v>
+        <v>1.53</v>
       </c>
       <c r="AB60">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AC60">
-        <v>1.84</v>
+        <v>2.16</v>
       </c>
       <c r="AD60">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AE60">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AF60">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG60">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK60">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>3.01</v>
+        <v>4.66</v>
       </c>
       <c r="O61">
         <v>4.05</v>
       </c>
       <c r="P61">
-        <v>1.99</v>
+        <v>1.47</v>
       </c>
       <c r="Q61">
-        <v>3.4</v>
+        <v>4.79</v>
       </c>
       <c r="R61">
-        <v>2.57</v>
+        <v>2.82</v>
       </c>
       <c r="S61">
         <v>1.18</v>
       </c>
       <c r="T61">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="U61">
         <v>1.91</v>
       </c>
       <c r="V61">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W61">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z61">
-        <v>7.5</v>
+        <v>5.63</v>
       </c>
       <c r="AA61">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AB61">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AC61">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AD61">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AE61">
+        <v>1.33</v>
+      </c>
+      <c r="AF61">
         <v>1.4</v>
       </c>
-      <c r="AF61">
-        <v>1.29</v>
-      </c>
       <c r="AG61">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK61">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.86</v>
+        <v>3.01</v>
       </c>
       <c r="O62">
-        <v>3.38</v>
+        <v>4.05</v>
       </c>
       <c r="P62">
-        <v>4.07</v>
+        <v>1.99</v>
       </c>
       <c r="Q62">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="R62">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="S62">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="T62">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="U62">
-        <v>2.79</v>
+        <v>1.91</v>
       </c>
       <c r="V62">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="W62">
+        <v>1.25</v>
+      </c>
+      <c r="X62">
+        <v>1.01</v>
+      </c>
+      <c r="Y62">
         <v>1.06</v>
       </c>
-      <c r="X62">
-        <v>1.02</v>
-      </c>
-      <c r="Y62">
+      <c r="Z62">
+        <v>7.5</v>
+      </c>
+      <c r="AA62">
         <v>1.3</v>
       </c>
-      <c r="Z62">
-        <v>2.97</v>
-      </c>
-      <c r="AA62">
-        <v>2</v>
-      </c>
       <c r="AB62">
-        <v>1.71</v>
+        <v>3.3</v>
       </c>
       <c r="AC62">
-        <v>3.5</v>
+        <v>1.81</v>
       </c>
       <c r="AD62">
-        <v>1.22</v>
+        <v>1.9</v>
       </c>
       <c r="AE62">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="AF62">
-        <v>1.83</v>
+        <v>1.29</v>
       </c>
       <c r="AG62">
-        <v>1.85</v>
+        <v>3.25</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK62">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.44</v>
+        <v>1.86</v>
       </c>
       <c r="O63">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="P63">
-        <v>2.44</v>
+        <v>4.07</v>
       </c>
       <c r="Q63">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="R63">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S63">
+        <v>1.38</v>
+      </c>
+      <c r="T63">
+        <v>2.75</v>
+      </c>
+      <c r="U63">
+        <v>2.79</v>
+      </c>
+      <c r="V63">
+        <v>1.37</v>
+      </c>
+      <c r="W63">
+        <v>1.06</v>
+      </c>
+      <c r="X63">
+        <v>1.02</v>
+      </c>
+      <c r="Y63">
         <v>1.3</v>
       </c>
-      <c r="T63">
-        <v>3.3</v>
-      </c>
-      <c r="U63">
-        <v>2.34</v>
-      </c>
-      <c r="V63">
-        <v>1.51</v>
-      </c>
-      <c r="W63">
-        <v>1.12</v>
-      </c>
-      <c r="X63">
-        <v>1.03</v>
-      </c>
-      <c r="Y63">
-        <v>1.2</v>
-      </c>
       <c r="Z63">
-        <v>4.1</v>
+        <v>2.97</v>
       </c>
       <c r="AA63">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AB63">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="AC63">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="AD63">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AE63">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AF63">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AG63">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK63">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:00:00</t>
         </is>
       </c>
     </row>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O64">
         <v>3.34</v>
       </c>
       <c r="P64">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="Q64">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="R64">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S64">
         <v>1.3</v>
       </c>
       <c r="T64">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U64">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="V64">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W64">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z64">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB64">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="AC64">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD64">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE64">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF64">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AG64">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="O65">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="P65">
+        <v>2.43</v>
+      </c>
+      <c r="Q65">
         <v>2.87</v>
       </c>
-      <c r="Q65">
-        <v>2.62</v>
-      </c>
       <c r="R65">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S65">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.78</v>
+        <v>3.18</v>
       </c>
       <c r="U65">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="V65">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W65">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>5.03</v>
+        <v>3.74</v>
       </c>
       <c r="AA65">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AB65">
-        <v>2.44</v>
+        <v>1.96</v>
       </c>
       <c r="AC65">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AD65">
-        <v>1.57</v>
+        <v>1.35</v>
       </c>
       <c r="AE65">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AF65">
+        <v>1.59</v>
+      </c>
+      <c r="AG65">
+        <v>2.19</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
+        <v>1.3</v>
+      </c>
+      <c r="AK65">
         <v>1.44</v>
-      </c>
-      <c r="AG65">
-        <v>2.58</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.23</v>
-      </c>
-      <c r="AK65">
-        <v>1.55</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="O66">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="P66">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="Q66">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R66">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="S66">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T66">
-        <v>2.95</v>
+        <v>3.78</v>
       </c>
       <c r="U66">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="V66">
+        <v>1.62</v>
+      </c>
+      <c r="W66">
+        <v>1.17</v>
+      </c>
+      <c r="X66">
+        <v>1.03</v>
+      </c>
+      <c r="Y66">
+        <v>1.11</v>
+      </c>
+      <c r="Z66">
+        <v>5.03</v>
+      </c>
+      <c r="AA66">
+        <v>1.48</v>
+      </c>
+      <c r="AB66">
+        <v>2.44</v>
+      </c>
+      <c r="AC66">
+        <v>2.4</v>
+      </c>
+      <c r="AD66">
+        <v>1.57</v>
+      </c>
+      <c r="AE66">
+        <v>1.22</v>
+      </c>
+      <c r="AF66">
         <v>1.44</v>
       </c>
-      <c r="W66">
-        <v>1.08</v>
-      </c>
-      <c r="X66">
-        <v>1</v>
-      </c>
-      <c r="Y66">
+      <c r="AG66">
+        <v>2.58</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.23</v>
       </c>
-      <c r="Z66">
-        <v>3.42</v>
-      </c>
-      <c r="AA66">
-        <v>1.88</v>
-      </c>
-      <c r="AB66">
-        <v>1.93</v>
-      </c>
-      <c r="AC66">
-        <v>2.92</v>
-      </c>
-      <c r="AD66">
-        <v>1.31</v>
-      </c>
-      <c r="AE66">
-        <v>1.09</v>
-      </c>
-      <c r="AF66">
-        <v>1.64</v>
-      </c>
-      <c r="AG66">
-        <v>2.08</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.25</v>
-      </c>
       <c r="AK66">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="P67">
-        <v>3.43</v>
+        <v>2.96</v>
       </c>
       <c r="Q67">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="R67">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="T67">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U67">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="V67">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X67">
         <v>1</v>
       </c>
       <c r="Y67">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z67">
-        <v>3.05</v>
+        <v>3.42</v>
       </c>
       <c r="AA67">
-        <v>2.05</v>
+        <v>1.88</v>
       </c>
       <c r="AB67">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="AC67">
-        <v>3.5</v>
+        <v>2.92</v>
       </c>
       <c r="AD67">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AE67">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AF67">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AG67">
-        <v>1.84</v>
+        <v>2.08</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK67">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="O68">
+        <v>3.2</v>
+      </c>
+      <c r="P68">
+        <v>3.43</v>
+      </c>
+      <c r="Q68">
+        <v>2.64</v>
+      </c>
+      <c r="R68">
+        <v>2.01</v>
+      </c>
+      <c r="S68">
+        <v>1.4</v>
+      </c>
+      <c r="T68">
+        <v>2.75</v>
+      </c>
+      <c r="U68">
+        <v>3</v>
+      </c>
+      <c r="V68">
+        <v>1.33</v>
+      </c>
+      <c r="W68">
+        <v>1.06</v>
+      </c>
+      <c r="X68">
+        <v>1</v>
+      </c>
+      <c r="Y68">
+        <v>1.28</v>
+      </c>
+      <c r="Z68">
+        <v>3.05</v>
+      </c>
+      <c r="AA68">
+        <v>2.05</v>
+      </c>
+      <c r="AB68">
+        <v>1.75</v>
+      </c>
+      <c r="AC68">
         <v>3.5</v>
       </c>
-      <c r="P68">
-        <v>3.92</v>
-      </c>
-      <c r="Q68">
-        <v>2.29</v>
-      </c>
-      <c r="R68">
-        <v>2.13</v>
-      </c>
-      <c r="S68">
-        <v>1.32</v>
-      </c>
-      <c r="T68">
-        <v>2.9</v>
-      </c>
-      <c r="U68">
-        <v>2.45</v>
-      </c>
-      <c r="V68">
-        <v>1.44</v>
-      </c>
-      <c r="W68">
-        <v>1.08</v>
-      </c>
-      <c r="X68">
-        <v>1.01</v>
-      </c>
-      <c r="Y68">
-        <v>1.23</v>
-      </c>
-      <c r="Z68">
-        <v>3.42</v>
-      </c>
-      <c r="AA68">
-        <v>1.83</v>
-      </c>
-      <c r="AB68">
-        <v>1.98</v>
-      </c>
-      <c r="AC68">
-        <v>2.88</v>
-      </c>
       <c r="AD68">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AE68">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF68">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AG68">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK68">
-        <v>1.88</v>
+        <v>1.64</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.93</v>
+        <v>1.76</v>
       </c>
       <c r="O69">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="P69">
-        <v>2.52</v>
+        <v>3.92</v>
       </c>
       <c r="Q69">
-        <v>3.1</v>
+        <v>2.29</v>
       </c>
       <c r="R69">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S69">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="T69">
         <v>2.9</v>
       </c>
       <c r="U69">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="V69">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X69">
         <v>1.01</v>
       </c>
       <c r="Y69">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z69">
-        <v>2.95</v>
+        <v>3.42</v>
       </c>
       <c r="AA69">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AB69">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AC69">
-        <v>3.55</v>
+        <v>2.88</v>
       </c>
       <c r="AD69">
         <v>1.32</v>
       </c>
       <c r="AE69">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF69">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AG69">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AK69">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-11-02 16:45:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.47</v>
+        <v>2.93</v>
       </c>
       <c r="O70">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="P70">
-        <v>4.35</v>
+        <v>2.52</v>
       </c>
       <c r="Q70">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="R70">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S70">
+        <v>1.4</v>
+      </c>
+      <c r="T70">
+        <v>2.9</v>
+      </c>
+      <c r="U70">
+        <v>2.88</v>
+      </c>
+      <c r="V70">
+        <v>1.4</v>
+      </c>
+      <c r="W70">
+        <v>1.05</v>
+      </c>
+      <c r="X70">
+        <v>1.01</v>
+      </c>
+      <c r="Y70">
         <v>1.33</v>
       </c>
-      <c r="T70">
-        <v>3.17</v>
-      </c>
-      <c r="U70">
-        <v>2.68</v>
-      </c>
-      <c r="V70">
-        <v>1.44</v>
-      </c>
-      <c r="W70">
+      <c r="Z70">
+        <v>2.95</v>
+      </c>
+      <c r="AA70">
+        <v>1.9</v>
+      </c>
+      <c r="AB70">
+        <v>1.9</v>
+      </c>
+      <c r="AC70">
+        <v>3.55</v>
+      </c>
+      <c r="AD70">
+        <v>1.32</v>
+      </c>
+      <c r="AE70">
         <v>1.11</v>
-      </c>
-      <c r="X70">
-        <v>1.02</v>
-      </c>
-      <c r="Y70">
-        <v>1.25</v>
-      </c>
-      <c r="Z70">
-        <v>3.9</v>
-      </c>
-      <c r="AA70">
-        <v>1.8</v>
-      </c>
-      <c r="AB70">
-        <v>2.01</v>
-      </c>
-      <c r="AC70">
-        <v>2.98</v>
-      </c>
-      <c r="AD70">
-        <v>1.38</v>
-      </c>
-      <c r="AE70">
-        <v>1.14</v>
       </c>
       <c r="AF70">
         <v>1.75</v>
       </c>
       <c r="AG70">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AK70">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.15</v>
+        <v>1.47</v>
       </c>
       <c r="O71">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="P71">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="Q71">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="R71">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="S71">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T71">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="U71">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="V71">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>3.37</v>
+        <v>3.9</v>
       </c>
       <c r="AA71">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AB71">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AC71">
-        <v>3.47</v>
+        <v>2.98</v>
       </c>
       <c r="AD71">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AE71">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AF71">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AG71">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AK71">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.43</v>
+        <v>2.15</v>
       </c>
       <c r="O72">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="P72">
-        <v>8.550000000000001</v>
+        <v>3</v>
       </c>
       <c r="Q72">
-        <v>1.96</v>
+        <v>2.9</v>
       </c>
       <c r="R72">
-        <v>2.27</v>
+        <v>2.1</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T72">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="U72">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="V72">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W72">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
         <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z72">
-        <v>4.33</v>
+        <v>3.37</v>
       </c>
       <c r="AA72">
-        <v>1.67</v>
+        <v>2.03</v>
       </c>
       <c r="AB72">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AC72">
-        <v>2.59</v>
+        <v>3.47</v>
       </c>
       <c r="AD72">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="AE72">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AF72">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AG72">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.17</v>
+        <v>1.28</v>
       </c>
       <c r="AK72">
-        <v>2.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
+        <v>1.43</v>
+      </c>
+      <c r="O73">
+        <v>5</v>
+      </c>
+      <c r="P73">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="Q73">
+        <v>1.96</v>
+      </c>
+      <c r="R73">
         <v>2.27</v>
       </c>
-      <c r="O73">
-        <v>3.78</v>
-      </c>
-      <c r="P73">
-        <v>3.23</v>
-      </c>
-      <c r="Q73">
-        <v>2.56</v>
-      </c>
-      <c r="R73">
-        <v>2.2</v>
-      </c>
       <c r="S73">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T73">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U73">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="V73">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W73">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X73">
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z73">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA73">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB73">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AC73">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD73">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE73">
         <v>1.13</v>
       </c>
       <c r="AF73">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG73">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AK73">
-        <v>1.66</v>
+        <v>2.62</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.4</v>
+        <v>2.27</v>
       </c>
       <c r="O74">
-        <v>4.9</v>
+        <v>3.78</v>
       </c>
       <c r="P74">
-        <v>8.199999999999999</v>
+        <v>3.23</v>
       </c>
       <c r="Q74">
-        <v>1.95</v>
+        <v>2.56</v>
       </c>
       <c r="R74">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S74">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T74">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="U74">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="V74">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y74">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z74">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA74">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AB74">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AC74">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="AD74">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE74">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="AF74">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AG74">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK74">
-        <v>2.61</v>
+        <v>1.66</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q75">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="R75">
-        <v>1.98</v>
+        <v>2.25</v>
       </c>
       <c r="S75">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T75">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="U75">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="V75">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
         <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA75">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="AB75">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AC75">
-        <v>4.08</v>
+        <v>3.3</v>
       </c>
       <c r="AD75">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE75">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="AG75">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AK75">
-        <v>1.67</v>
+        <v>2.61</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="O76">
-        <v>9.85</v>
+        <v>0</v>
       </c>
       <c r="P76">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q76">
-        <v>1.47</v>
+        <v>2.7</v>
       </c>
       <c r="R76">
-        <v>3.06</v>
+        <v>1.98</v>
       </c>
       <c r="S76">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="T76">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="U76">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="V76">
-        <v>1.72</v>
+        <v>1.35</v>
       </c>
       <c r="W76">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="X76">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="Z76">
-        <v>4.84</v>
+        <v>2.7</v>
       </c>
       <c r="AA76">
-        <v>1.4</v>
+        <v>2.28</v>
       </c>
       <c r="AB76">
-        <v>2.87</v>
+        <v>1.62</v>
       </c>
       <c r="AC76">
-        <v>1.93</v>
+        <v>4.08</v>
       </c>
       <c r="AD76">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AE76">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="AF76">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG76">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.1</v>
+        <v>1.35</v>
       </c>
       <c r="AK76">
-        <v>4.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.93</v>
+        <v>1.13</v>
       </c>
       <c r="O77">
-        <v>3.36</v>
+        <v>9.85</v>
       </c>
       <c r="P77">
-        <v>2.55</v>
+        <v>21</v>
       </c>
       <c r="Q77">
-        <v>3.5</v>
+        <v>1.47</v>
       </c>
       <c r="R77">
-        <v>2.05</v>
+        <v>3.06</v>
       </c>
       <c r="S77">
+        <v>1.22</v>
+      </c>
+      <c r="T77">
+        <v>4</v>
+      </c>
+      <c r="U77">
+        <v>1.97</v>
+      </c>
+      <c r="V77">
+        <v>1.72</v>
+      </c>
+      <c r="W77">
+        <v>1.2</v>
+      </c>
+      <c r="X77">
+        <v>1</v>
+      </c>
+      <c r="Y77">
+        <v>1.11</v>
+      </c>
+      <c r="Z77">
+        <v>4.84</v>
+      </c>
+      <c r="AA77">
         <v>1.4</v>
       </c>
-      <c r="T77">
-        <v>2.7</v>
-      </c>
-      <c r="U77">
-        <v>3.1</v>
-      </c>
-      <c r="V77">
-        <v>1.33</v>
-      </c>
-      <c r="W77">
-        <v>1.06</v>
-      </c>
-      <c r="X77">
-        <v>1.05</v>
-      </c>
-      <c r="Y77">
-        <v>1.4</v>
-      </c>
-      <c r="Z77">
-        <v>2.66</v>
-      </c>
-      <c r="AA77">
-        <v>2.15</v>
-      </c>
       <c r="AB77">
-        <v>1.6</v>
+        <v>2.87</v>
       </c>
       <c r="AC77">
-        <v>4.2</v>
+        <v>1.93</v>
       </c>
       <c r="AD77">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="AE77">
-        <v>1.04</v>
+        <v>1.34</v>
       </c>
       <c r="AF77">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AG77">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK77">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12976,27 +12976,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.83</v>
+        <v>2.93</v>
       </c>
       <c r="O78">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="P78">
-        <v>4.49</v>
+        <v>2.55</v>
       </c>
       <c r="Q78">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="R78">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="S78">
         <v>1.4</v>
       </c>
       <c r="T78">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U78">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W78">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y78">
+        <v>1.4</v>
+      </c>
+      <c r="Z78">
+        <v>2.66</v>
+      </c>
+      <c r="AA78">
+        <v>2.15</v>
+      </c>
+      <c r="AB78">
+        <v>1.6</v>
+      </c>
+      <c r="AC78">
+        <v>4.2</v>
+      </c>
+      <c r="AD78">
+        <v>1.18</v>
+      </c>
+      <c r="AE78">
+        <v>1.04</v>
+      </c>
+      <c r="AF78">
+        <v>1.87</v>
+      </c>
+      <c r="AG78">
+        <v>1.83</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
         <v>1.33</v>
       </c>
-      <c r="Z78">
-        <v>2.91</v>
-      </c>
-      <c r="AA78">
-        <v>2.1</v>
-      </c>
-      <c r="AB78">
-        <v>1.7</v>
-      </c>
-      <c r="AC78">
-        <v>3.72</v>
-      </c>
-      <c r="AD78">
-        <v>1.24</v>
-      </c>
-      <c r="AE78">
-        <v>1.05</v>
-      </c>
-      <c r="AF78">
-        <v>1.85</v>
-      </c>
-      <c r="AG78">
-        <v>1.78</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.2</v>
-      </c>
       <c r="AK78">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-11-02 17:30:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="O79">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="P79">
-        <v>2.95</v>
+        <v>4.49</v>
       </c>
       <c r="Q79">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="R79">
-        <v>2.35</v>
+        <v>1.99</v>
       </c>
       <c r="S79">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="T79">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U79">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="V79">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="W79">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X79">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y79">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="Z79">
-        <v>4.15</v>
+        <v>2.91</v>
       </c>
       <c r="AA79">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AC79">
-        <v>2.47</v>
+        <v>3.72</v>
       </c>
       <c r="AD79">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="AE79">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="AF79">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG79">
-        <v>2.31</v>
+        <v>1.78</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK79">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
+        <v>2.15</v>
+      </c>
+      <c r="O80">
+        <v>3.7</v>
+      </c>
+      <c r="P80">
+        <v>2.95</v>
+      </c>
+      <c r="Q80">
+        <v>2.52</v>
+      </c>
+      <c r="R80">
+        <v>2.35</v>
+      </c>
+      <c r="S80">
+        <v>1.29</v>
+      </c>
+      <c r="T80">
+        <v>3.25</v>
+      </c>
+      <c r="U80">
+        <v>2.5</v>
+      </c>
+      <c r="V80">
+        <v>1.53</v>
+      </c>
+      <c r="W80">
+        <v>1.13</v>
+      </c>
+      <c r="X80">
+        <v>1.01</v>
+      </c>
+      <c r="Y80">
+        <v>1.16</v>
+      </c>
+      <c r="Z80">
+        <v>4.15</v>
+      </c>
+      <c r="AA80">
+        <v>1.6</v>
+      </c>
+      <c r="AB80">
         <v>2.2</v>
       </c>
-      <c r="O80">
-        <v>3.2</v>
-      </c>
-      <c r="P80">
-        <v>3.21</v>
-      </c>
-      <c r="Q80">
-        <v>3.13</v>
-      </c>
-      <c r="R80">
-        <v>2.07</v>
-      </c>
-      <c r="S80">
-        <v>1.46</v>
-      </c>
-      <c r="T80">
-        <v>2.62</v>
-      </c>
-      <c r="U80">
-        <v>3.02</v>
-      </c>
-      <c r="V80">
-        <v>1.32</v>
-      </c>
-      <c r="W80">
-        <v>1.03</v>
-      </c>
-      <c r="X80">
-        <v>1.02</v>
-      </c>
-      <c r="Y80">
-        <v>1.4</v>
-      </c>
-      <c r="Z80">
-        <v>2.88</v>
-      </c>
-      <c r="AA80">
-        <v>2.23</v>
-      </c>
-      <c r="AB80">
-        <v>1.6</v>
-      </c>
       <c r="AC80">
-        <v>4.15</v>
+        <v>2.47</v>
       </c>
       <c r="AD80">
+        <v>1.48</v>
+      </c>
+      <c r="AE80">
         <v>1.16</v>
       </c>
-      <c r="AE80">
-        <v>1.01</v>
-      </c>
       <c r="AF80">
-        <v>1.9</v>
+        <v>1.53</v>
       </c>
       <c r="AG80">
-        <v>1.78</v>
+        <v>2.31</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK80">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13465,27 +13465,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-11-02 19:05:00</t>
+          <t>2026-11-02 18:00:00</t>
         </is>
       </c>
     </row>
@@ -13628,27 +13628,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="Q82">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R82">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S82">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T82">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U82">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V82">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W82">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y82">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z82">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA82">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB82">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC82">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD82">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE82">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF82">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG82">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK82">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-11-02 20:00:00</t>
+          <t>2026-11-02 19:05:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Palestino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O83">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P83">
-        <v>2.6</v>
+        <v>3.59</v>
       </c>
       <c r="Q83">
-        <v>3.1</v>
+        <v>2.57</v>
       </c>
       <c r="R83">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="S83">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="T83">
-        <v>3.07</v>
+        <v>3.4</v>
       </c>
       <c r="U83">
-        <v>2.77</v>
+        <v>2.3</v>
       </c>
       <c r="V83">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="W83">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X83">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="Z83">
-        <v>3.67</v>
+        <v>4.2</v>
       </c>
       <c r="AA83">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AB83">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC83">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AD83">
+        <v>1.53</v>
+      </c>
+      <c r="AE83">
+        <v>1.14</v>
+      </c>
+      <c r="AF83">
+        <v>1.53</v>
+      </c>
+      <c r="AG83">
+        <v>2.3</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.3</v>
       </c>
-      <c r="AE83">
-        <v>1.09</v>
-      </c>
-      <c r="AF83">
-        <v>1.7</v>
-      </c>
-      <c r="AG83">
-        <v>2</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.25</v>
-      </c>
       <c r="AK83">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-11-02 20:30:00</t>
+          <t>2026-11-02 20:00:00</t>
         </is>
       </c>
     </row>
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Palestino</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.44</v>
+        <v>2.55</v>
       </c>
       <c r="O84">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P84">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q84">
+        <v>3.1</v>
+      </c>
+      <c r="R84">
+        <v>2.2</v>
+      </c>
+      <c r="S84">
+        <v>1.35</v>
+      </c>
+      <c r="T84">
+        <v>3.07</v>
+      </c>
+      <c r="U84">
+        <v>2.77</v>
+      </c>
+      <c r="V84">
+        <v>1.41</v>
+      </c>
+      <c r="W84">
+        <v>1.1</v>
+      </c>
+      <c r="X84">
+        <v>1.01</v>
+      </c>
+      <c r="Y84">
+        <v>1.27</v>
+      </c>
+      <c r="Z84">
+        <v>3.67</v>
+      </c>
+      <c r="AA84">
+        <v>1.92</v>
+      </c>
+      <c r="AB84">
+        <v>1.9</v>
+      </c>
+      <c r="AC84">
         <v>3</v>
       </c>
-      <c r="R84">
-        <v>2.32</v>
-      </c>
-      <c r="S84">
-        <v>1.29</v>
-      </c>
-      <c r="T84">
-        <v>3.3</v>
-      </c>
-      <c r="U84">
-        <v>2.6</v>
-      </c>
-      <c r="V84">
-        <v>1.44</v>
-      </c>
-      <c r="W84">
-        <v>1.08</v>
-      </c>
-      <c r="X84">
-        <v>1.02</v>
-      </c>
-      <c r="Y84">
-        <v>1.23</v>
-      </c>
-      <c r="Z84">
-        <v>4.11</v>
-      </c>
-      <c r="AA84">
-        <v>1.73</v>
-      </c>
-      <c r="AB84">
-        <v>1.98</v>
-      </c>
-      <c r="AC84">
-        <v>2.92</v>
-      </c>
       <c r="AD84">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE84">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF84">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AG84">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK84">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14117,156 +14117,319 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N85">
+        <v>2.44</v>
+      </c>
+      <c r="O85">
+        <v>3.36</v>
+      </c>
+      <c r="P85">
+        <v>2.64</v>
+      </c>
+      <c r="Q85">
+        <v>3</v>
+      </c>
+      <c r="R85">
+        <v>2.32</v>
+      </c>
+      <c r="S85">
+        <v>1.29</v>
+      </c>
+      <c r="T85">
+        <v>3.3</v>
+      </c>
+      <c r="U85">
+        <v>2.6</v>
+      </c>
+      <c r="V85">
+        <v>1.44</v>
+      </c>
+      <c r="W85">
+        <v>1.08</v>
+      </c>
+      <c r="X85">
+        <v>1.02</v>
+      </c>
+      <c r="Y85">
+        <v>1.23</v>
+      </c>
+      <c r="Z85">
+        <v>4.11</v>
+      </c>
+      <c r="AA85">
+        <v>1.73</v>
+      </c>
+      <c r="AB85">
+        <v>1.98</v>
+      </c>
+      <c r="AC85">
+        <v>2.92</v>
+      </c>
+      <c r="AD85">
+        <v>1.4</v>
+      </c>
+      <c r="AE85">
+        <v>1.15</v>
+      </c>
+      <c r="AF85">
+        <v>1.62</v>
+      </c>
+      <c r="AG85">
+        <v>2.15</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ85">
+        <v>1.3</v>
+      </c>
+      <c r="AK85">
+        <v>1.5</v>
+      </c>
+      <c r="AL85">
+        <v>0</v>
+      </c>
+      <c r="AM85">
+        <v>-1</v>
+      </c>
+      <c r="AN85">
+        <v>-1</v>
+      </c>
+      <c r="AO85">
+        <v>-1</v>
+      </c>
+      <c r="AP85">
+        <v>-1</v>
+      </c>
+      <c r="AQ85">
+        <v>0</v>
+      </c>
+      <c r="AR85">
+        <v>0</v>
+      </c>
+      <c r="AS85">
+        <v>0</v>
+      </c>
+      <c r="AT85">
+        <v>0</v>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
+          <t>2026-11-02 20:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>2026/2027</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Waterhouse</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Cavalier</t>
         </is>
       </c>
-      <c r="G85">
-        <v>0</v>
-      </c>
-      <c r="H85">
-        <v>0</v>
-      </c>
-      <c r="I85">
-        <v>0</v>
-      </c>
-      <c r="J85">
-        <v>0</v>
-      </c>
-      <c r="K85">
-        <v>0</v>
-      </c>
-      <c r="L85">
-        <v>0</v>
-      </c>
-      <c r="M85" t="inlineStr">
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>0</v>
-      </c>
-      <c r="P85">
-        <v>0</v>
-      </c>
-      <c r="Q85">
-        <v>0</v>
-      </c>
-      <c r="R85">
-        <v>0</v>
-      </c>
-      <c r="S85">
-        <v>0</v>
-      </c>
-      <c r="T85">
-        <v>0</v>
-      </c>
-      <c r="U85">
-        <v>0</v>
-      </c>
-      <c r="V85">
-        <v>0</v>
-      </c>
-      <c r="W85">
-        <v>0</v>
-      </c>
-      <c r="X85">
-        <v>0</v>
-      </c>
-      <c r="Y85">
-        <v>0</v>
-      </c>
-      <c r="Z85">
-        <v>0</v>
-      </c>
-      <c r="AA85">
-        <v>0</v>
-      </c>
-      <c r="AB85">
-        <v>0</v>
-      </c>
-      <c r="AC85">
-        <v>0</v>
-      </c>
-      <c r="AD85">
-        <v>0</v>
-      </c>
-      <c r="AE85">
-        <v>0</v>
-      </c>
-      <c r="AF85">
-        <v>0</v>
-      </c>
-      <c r="AG85">
-        <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ85">
-        <v>0</v>
-      </c>
-      <c r="AK85">
-        <v>0</v>
-      </c>
-      <c r="AL85">
-        <v>0</v>
-      </c>
-      <c r="AM85">
-        <v>-1</v>
-      </c>
-      <c r="AN85">
-        <v>-1</v>
-      </c>
-      <c r="AO85">
-        <v>-1</v>
-      </c>
-      <c r="AP85">
-        <v>-1</v>
-      </c>
-      <c r="AQ85">
-        <v>0</v>
-      </c>
-      <c r="AR85">
-        <v>0</v>
-      </c>
-      <c r="AS85">
-        <v>0</v>
-      </c>
-      <c r="AT85">
-        <v>0</v>
-      </c>
-      <c r="AU85" t="inlineStr">
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <v>0</v>
+      </c>
+      <c r="T86">
+        <v>0</v>
+      </c>
+      <c r="U86">
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
+      <c r="X86">
+        <v>0</v>
+      </c>
+      <c r="Y86">
+        <v>0</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+      <c r="AA86">
+        <v>0</v>
+      </c>
+      <c r="AB86">
+        <v>0</v>
+      </c>
+      <c r="AC86">
+        <v>0</v>
+      </c>
+      <c r="AD86">
+        <v>0</v>
+      </c>
+      <c r="AE86">
+        <v>0</v>
+      </c>
+      <c r="AF86">
+        <v>0</v>
+      </c>
+      <c r="AG86">
+        <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
+        <v>0</v>
+      </c>
+      <c r="AK86">
+        <v>0</v>
+      </c>
+      <c r="AL86">
+        <v>0</v>
+      </c>
+      <c r="AM86">
+        <v>-1</v>
+      </c>
+      <c r="AN86">
+        <v>-1</v>
+      </c>
+      <c r="AO86">
+        <v>-1</v>
+      </c>
+      <c r="AP86">
+        <v>-1</v>
+      </c>
+      <c r="AQ86">
+        <v>0</v>
+      </c>
+      <c r="AR86">
+        <v>0</v>
+      </c>
+      <c r="AS86">
+        <v>0</v>
+      </c>
+      <c r="AT86">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
         <is>
           <t>2026-11-02 22:00:00</t>
         </is>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3578,55 +3578,55 @@
         <v>2.17</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="Q33">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="R33">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S33">
+        <v>1.36</v>
+      </c>
+      <c r="T33">
+        <v>3</v>
+      </c>
+      <c r="U33">
+        <v>2.7</v>
+      </c>
+      <c r="V33">
+        <v>1.4</v>
+      </c>
+      <c r="W33">
+        <v>1.08</v>
+      </c>
+      <c r="X33">
+        <v>1</v>
+      </c>
+      <c r="Y33">
         <v>1.25</v>
       </c>
-      <c r="T33">
-        <v>3.5</v>
-      </c>
-      <c r="U33">
-        <v>2.3</v>
-      </c>
-      <c r="V33">
-        <v>1.57</v>
-      </c>
-      <c r="W33">
-        <v>1.11</v>
-      </c>
-      <c r="X33">
-        <v>1.03</v>
-      </c>
-      <c r="Y33">
+      <c r="Z33">
+        <v>3.28</v>
+      </c>
+      <c r="AA33">
+        <v>1.97</v>
+      </c>
+      <c r="AB33">
+        <v>1.85</v>
+      </c>
+      <c r="AC33">
+        <v>3.32</v>
+      </c>
+      <c r="AD33">
+        <v>1.27</v>
+      </c>
+      <c r="AE33">
         <v>1.12</v>
       </c>
-      <c r="Z33">
-        <v>4.7</v>
-      </c>
-      <c r="AA33">
-        <v>1.54</v>
-      </c>
-      <c r="AB33">
-        <v>2.27</v>
-      </c>
-      <c r="AC33">
-        <v>2.29</v>
-      </c>
-      <c r="AD33">
-        <v>1.53</v>
-      </c>
-      <c r="AE33">
-        <v>1.18</v>
-      </c>
       <c r="AF33">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.53</v>
+        <v>2.04</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.55</v>
+        <v>2.31</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="Q34">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="R34">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U34">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="Z34">
-        <v>3.28</v>
+        <v>4.7</v>
       </c>
       <c r="AA34">
-        <v>1.97</v>
+        <v>1.54</v>
       </c>
       <c r="AB34">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="AC34">
-        <v>3.32</v>
+        <v>2.29</v>
       </c>
       <c r="AD34">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AE34">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF34">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AG34">
-        <v>2.04</v>
+        <v>2.53</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK34">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="AL34">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2274,22 +2274,22 @@
         <v>4.52</v>
       </c>
       <c r="Q12">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R12">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T12">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="U12">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
         <v>1.08</v>
@@ -2304,10 +2304,10 @@
         <v>3.28</v>
       </c>
       <c r="AA12">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
         <v>2.97</v>
@@ -2319,7 +2319,7 @@
         <v>1.08</v>
       </c>
       <c r="AF12">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG12">
         <v>1.89</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O14">
-        <v>5.02</v>
+        <v>4.25</v>
       </c>
       <c r="P14">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="Q14">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="R14">
         <v>2.41</v>
@@ -2612,7 +2612,7 @@
         <v>3.38</v>
       </c>
       <c r="U14">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="V14">
         <v>1.53</v>
@@ -2639,10 +2639,10 @@
         <v>2.52</v>
       </c>
       <c r="AD14">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AF14">
         <v>1.7</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
         <v>2.61</v>
@@ -2793,22 +2793,22 @@
         <v>2.7</v>
       </c>
       <c r="AA15">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AB15">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC15">
         <v>4.14</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE15">
         <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG15">
         <v>1.8</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK15">
         <v>1.73</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="O17">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>4.64</v>
+        <v>4.05</v>
       </c>
       <c r="Q17">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="R17">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
         <v>1.36</v>
@@ -3119,10 +3119,10 @@
         <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AB17">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
         <v>3.4</v>
@@ -3153,7 +3153,7 @@
         <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,22 +3243,22 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.22</v>
+        <v>2.83</v>
       </c>
       <c r="O18">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.29</v>
+        <v>2.19</v>
       </c>
       <c r="Q18">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S18">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
         <v>3.27</v>
@@ -3282,10 +3282,10 @@
         <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AB18">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC18">
         <v>2.74</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
         <v>1.38</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O19">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="P19">
+        <v>3</v>
+      </c>
+      <c r="Q19">
         <v>3.4</v>
       </c>
-      <c r="Q19">
-        <v>3.1</v>
-      </c>
       <c r="R19">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S19">
         <v>1.6</v>
@@ -3427,43 +3427,43 @@
         <v>2.2</v>
       </c>
       <c r="U19">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="V19">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Y19">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="Z19">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA19">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="AB19">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AC19">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AD19">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE19">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF19">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AG19">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AK19">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>2.99</v>
+        <v>3.7</v>
       </c>
       <c r="O20">
         <v>3.4</v>
       </c>
       <c r="P20">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="Q20">
-        <v>3.72</v>
+        <v>4.3</v>
       </c>
       <c r="R20">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="S20">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T20">
-        <v>3.38</v>
+        <v>3.24</v>
       </c>
       <c r="U20">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="V20">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W20">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AA20">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB20">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AC20">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AD20">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE20">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AF20">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="AG20">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="O21">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
         <v>3.7</v>
@@ -3759,7 +3759,7 @@
         <v>1.37</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -3771,10 +3771,10 @@
         <v>3.14</v>
       </c>
       <c r="AA21">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AB21">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC21">
         <v>3.47</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
         <v>1.91</v>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="O22">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P22">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T22">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U22">
         <v>2.25</v>
@@ -3922,34 +3922,34 @@
         <v>1.57</v>
       </c>
       <c r="W22">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA22">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AB22">
         <v>2.4</v>
       </c>
       <c r="AC22">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="AD22">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE22">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF22">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AG22">
         <v>2.75</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="G29">
@@ -7979,55 +7979,55 @@
         <v>2.97</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8142,55 +8142,55 @@
         <v>3.9</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q18">
         <v>3.3</v>
@@ -3928,28 +3928,28 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z22">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AA22">
         <v>1.68</v>
       </c>
       <c r="AB22">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AC22">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="AD22">
         <v>1.46</v>
       </c>
       <c r="AE22">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF22">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AG22">
         <v>2.75</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
         <v>1.46</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="O24">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P24">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="Q24">
         <v>2.55</v>
@@ -4251,19 +4251,19 @@
         <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA24">
-        <v>1.97</v>
+        <v>1.71</v>
       </c>
       <c r="AB24">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AC24">
         <v>2.88</v>
@@ -4272,7 +4272,7 @@
         <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF24">
         <v>1.62</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="O41">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>4.98</v>
+        <v>5</v>
       </c>
       <c r="Q41">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R41">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="S41">
         <v>1.4</v>
@@ -7013,31 +7013,31 @@
         <v>2.75</v>
       </c>
       <c r="U41">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W41">
         <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z41">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="AA41">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AB41">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC41">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="AD41">
         <v>1.23</v>
@@ -7046,10 +7046,10 @@
         <v>1.03</v>
       </c>
       <c r="AF41">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AG41">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK41">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="O42">
-        <v>3.73</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Q42">
         <v>3.06</v>
@@ -7194,16 +7194,16 @@
         <v>4.61</v>
       </c>
       <c r="AA42">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="AC42">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="AD42">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE42">
         <v>1.2</v>
@@ -9111,19 +9111,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O54">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="P54">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="Q54">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="R54">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="S54">
         <v>1.25</v>
@@ -9153,7 +9153,7 @@
         <v>1.61</v>
       </c>
       <c r="AB54">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC54">
         <v>2.39</v>
@@ -9313,7 +9313,7 @@
         <v>4.33</v>
       </c>
       <c r="AA55">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB55">
         <v>2.25</v>
@@ -10741,16 +10741,16 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="O64">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P64">
-        <v>2.44</v>
+        <v>2.64</v>
       </c>
       <c r="Q64">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="R64">
         <v>2.25</v>
@@ -10762,10 +10762,10 @@
         <v>3.3</v>
       </c>
       <c r="U64">
-        <v>2.34</v>
+        <v>2.51</v>
       </c>
       <c r="V64">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
         <v>1.12</v>
@@ -10777,19 +10777,19 @@
         <v>1.2</v>
       </c>
       <c r="Z64">
-        <v>4.1</v>
+        <v>4.21</v>
       </c>
       <c r="AA64">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB64">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC64">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AD64">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE64">
         <v>1.13</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
         <v>1.5</v>
@@ -10904,25 +10904,25 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O65">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="Q65">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="R65">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S65">
         <v>1.3</v>
       </c>
       <c r="T65">
-        <v>3.18</v>
+        <v>2.89</v>
       </c>
       <c r="U65">
         <v>2.45</v>
@@ -10934,34 +10934,34 @@
         <v>1.09</v>
       </c>
       <c r="X65">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
         <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AA65">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB65">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC65">
-        <v>2.74</v>
+        <v>2.94</v>
       </c>
       <c r="AD65">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE65">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF65">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG65">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11402,10 +11402,10 @@
         <v>3.43</v>
       </c>
       <c r="Q68">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="R68">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="S68">
         <v>1.4</v>
@@ -11414,22 +11414,22 @@
         <v>2.75</v>
       </c>
       <c r="U68">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="V68">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W68">
         <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z68">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AA68">
         <v>2.05</v>
@@ -11438,19 +11438,19 @@
         <v>1.75</v>
       </c>
       <c r="AC68">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD68">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE68">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG68">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK68">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="O69">
         <v>3.5</v>
       </c>
       <c r="P69">
-        <v>3.92</v>
+        <v>4.2</v>
       </c>
       <c r="Q69">
-        <v>2.29</v>
+        <v>2.22</v>
       </c>
       <c r="R69">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="S69">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U69">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V69">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W69">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z69">
-        <v>3.42</v>
+        <v>3.85</v>
       </c>
       <c r="AA69">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB69">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC69">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AD69">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="AE69">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF69">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG69">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AK69">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -12208,19 +12208,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="O73">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P73">
-        <v>8.550000000000001</v>
+        <v>6.5</v>
       </c>
       <c r="Q73">
         <v>1.96</v>
       </c>
       <c r="R73">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S73">
         <v>1.3</v>
@@ -12241,31 +12241,31 @@
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z73">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AA73">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB73">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AC73">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="AD73">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AE73">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF73">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG73">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK73">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="AL73">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2307,7 +2307,7 @@
         <v>1.8</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC12">
         <v>2.97</v>
@@ -3083,7 +3083,7 @@
         <v>1.73</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="P17">
         <v>4.05</v>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK17">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3412,7 +3412,7 @@
         <v>2.62</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q19">
         <v>3.4</v>
@@ -3445,7 +3445,7 @@
         <v>2.02</v>
       </c>
       <c r="AA19">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AB19">
         <v>1.3</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q20">
-        <v>4.3</v>
+        <v>4.06</v>
       </c>
       <c r="R20">
+        <v>2.24</v>
+      </c>
+      <c r="S20">
+        <v>1.25</v>
+      </c>
+      <c r="T20">
+        <v>3.3</v>
+      </c>
+      <c r="U20">
         <v>2.22</v>
       </c>
-      <c r="S20">
-        <v>1.26</v>
-      </c>
-      <c r="T20">
-        <v>3.24</v>
-      </c>
-      <c r="U20">
-        <v>2.25</v>
-      </c>
       <c r="V20">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W20">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z20">
-        <v>4.4</v>
+        <v>4.62</v>
       </c>
       <c r="AA20">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AB20">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="AC20">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AD20">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE20">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AF20">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AG20">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.2</v>
       </c>
       <c r="AK20">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="O25">
         <v>3.25</v>
@@ -4396,7 +4396,7 @@
         <v>3.34</v>
       </c>
       <c r="R25">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
         <v>1.43</v>
@@ -4417,19 +4417,19 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z25">
-        <v>3.08</v>
+        <v>3.43</v>
       </c>
       <c r="AA25">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="AB25">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC25">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD25">
         <v>1.25</v>
@@ -4457,7 +4457,7 @@
         <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>4.06</v>
+        <v>4.45</v>
       </c>
       <c r="O30">
-        <v>3.72</v>
+        <v>3.86</v>
       </c>
       <c r="P30">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="Q30">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="R30">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S30">
+        <v>1.36</v>
+      </c>
+      <c r="T30">
+        <v>3</v>
+      </c>
+      <c r="U30">
+        <v>2.88</v>
+      </c>
+      <c r="V30">
+        <v>1.36</v>
+      </c>
+      <c r="W30">
+        <v>1.08</v>
+      </c>
+      <c r="X30">
+        <v>1.01</v>
+      </c>
+      <c r="Y30">
+        <v>1.22</v>
+      </c>
+      <c r="Z30">
+        <v>3.64</v>
+      </c>
+      <c r="AA30">
+        <v>1.85</v>
+      </c>
+      <c r="AB30">
+        <v>1.88</v>
+      </c>
+      <c r="AC30">
+        <v>2.92</v>
+      </c>
+      <c r="AD30">
         <v>1.31</v>
-      </c>
-      <c r="T30">
-        <v>2.95</v>
-      </c>
-      <c r="U30">
-        <v>2.55</v>
-      </c>
-      <c r="V30">
-        <v>1.41</v>
-      </c>
-      <c r="W30">
-        <v>1.07</v>
-      </c>
-      <c r="X30">
-        <v>1</v>
-      </c>
-      <c r="Y30">
-        <v>1.25</v>
-      </c>
-      <c r="Z30">
-        <v>3.52</v>
-      </c>
-      <c r="AA30">
-        <v>1.98</v>
-      </c>
-      <c r="AB30">
-        <v>1.83</v>
-      </c>
-      <c r="AC30">
-        <v>3.04</v>
-      </c>
-      <c r="AD30">
-        <v>1.29</v>
       </c>
       <c r="AE30">
         <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AG30">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AK30">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="O31">
         <v>3.27</v>
       </c>
       <c r="P31">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="Q31">
         <v>3.3</v>
@@ -5377,10 +5377,10 @@
         <v>2</v>
       </c>
       <c r="S31">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T31">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="U31">
         <v>3.2</v>
@@ -5407,7 +5407,7 @@
         <v>1.65</v>
       </c>
       <c r="AC31">
-        <v>4.28</v>
+        <v>3.68</v>
       </c>
       <c r="AD31">
         <v>1.2</v>
@@ -5419,7 +5419,7 @@
         <v>1.83</v>
       </c>
       <c r="AG31">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P33">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -5761,7 +5761,7 @@
         <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,19 +5851,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="O34">
         <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="Q34">
         <v>2.44</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="S34">
         <v>1.25</v>
@@ -5878,7 +5878,7 @@
         <v>1.57</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
         <v>1.03</v>
@@ -5887,19 +5887,19 @@
         <v>1.12</v>
       </c>
       <c r="Z34">
-        <v>4.7</v>
+        <v>5.11</v>
       </c>
       <c r="AA34">
         <v>1.54</v>
       </c>
       <c r="AB34">
+        <v>2.28</v>
+      </c>
+      <c r="AC34">
         <v>2.27</v>
       </c>
-      <c r="AC34">
-        <v>2.29</v>
-      </c>
       <c r="AD34">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE34">
         <v>1.18</v>
@@ -6340,43 +6340,43 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="O37">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="P37">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R37">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="U37">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="V37">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z37">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AA37">
         <v>1.66</v>
@@ -6385,7 +6385,7 @@
         <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD37">
         <v>1.4</v>
@@ -6666,19 +6666,19 @@
         </is>
       </c>
       <c r="N39">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="O39">
-        <v>3.59</v>
+        <v>3.4</v>
       </c>
       <c r="P39">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="Q39">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R39">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="S39">
         <v>1.36</v>
@@ -6711,10 +6711,10 @@
         <v>1.83</v>
       </c>
       <c r="AC39">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD39">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE39">
         <v>1.06</v>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="O40">
-        <v>3.24</v>
+        <v>3</v>
       </c>
       <c r="P40">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -7158,16 +7158,16 @@
         <v>2.8</v>
       </c>
       <c r="O42">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
         <v>2.3</v>
       </c>
       <c r="Q42">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S42">
         <v>1.31</v>
@@ -7176,10 +7176,10 @@
         <v>3.26</v>
       </c>
       <c r="U42">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V42">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W42">
         <v>1.15</v>
@@ -7194,25 +7194,25 @@
         <v>4.61</v>
       </c>
       <c r="AA42">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AB42">
-        <v>2.39</v>
+        <v>2.49</v>
       </c>
       <c r="AC42">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="AD42">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE42">
         <v>1.2</v>
       </c>
       <c r="AF42">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG42">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK42">
         <v>1.44</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="O43">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="P43">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q43">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="R43">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="S43">
         <v>1.39</v>
@@ -7339,13 +7339,13 @@
         <v>2.71</v>
       </c>
       <c r="U43">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="V43">
         <v>1.36</v>
       </c>
       <c r="W43">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X43">
         <v>1.02</v>
@@ -7481,43 +7481,43 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O44">
-        <v>3.1</v>
+        <v>2.87</v>
       </c>
       <c r="P44">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA44">
         <v>2.7</v>
@@ -7526,19 +7526,19 @@
         <v>1.44</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="O45">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="P45">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AA45">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AB45">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,22 +7807,22 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="O46">
-        <v>3.56</v>
+        <v>3.58</v>
       </c>
       <c r="P46">
-        <v>2.92</v>
+        <v>2.71</v>
       </c>
       <c r="Q46">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R46">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
         <v>3.5</v>
@@ -7837,7 +7837,7 @@
         <v>1.12</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
         <v>1.13</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P47">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="Q47">
         <v>2.9</v>
@@ -7985,16 +7985,16 @@
         <v>2.15</v>
       </c>
       <c r="S47">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T47">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="U47">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V47">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W47">
         <v>1.06</v>
@@ -8003,16 +8003,16 @@
         <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z47">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="AA47">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AB47">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC47">
         <v>3.3</v>
@@ -8024,10 +8024,10 @@
         <v>1.07</v>
       </c>
       <c r="AF47">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8136,10 +8136,10 @@
         <v>1.81</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P48">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q48">
         <v>2.3</v>
@@ -8175,7 +8175,7 @@
         <v>1.66</v>
       </c>
       <c r="AB48">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC48">
         <v>2.56</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>7.65</v>
+        <v>6.5</v>
       </c>
       <c r="O49">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="P49">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Q49">
         <v>7.03</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="O52">
-        <v>3.68</v>
+        <v>3.47</v>
       </c>
       <c r="P52">
-        <v>3.37</v>
+        <v>3.17</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -8812,10 +8812,10 @@
         <v>1.56</v>
       </c>
       <c r="W52">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X52">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
         <v>1.18</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="Q53">
         <v>2.5</v>
@@ -8969,10 +8969,10 @@
         <v>3.48</v>
       </c>
       <c r="U53">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="V53">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W53">
         <v>1.15</v>
@@ -8987,16 +8987,16 @@
         <v>4.5</v>
       </c>
       <c r="AA53">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB53">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AC53">
         <v>2.28</v>
       </c>
       <c r="AD53">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AE53">
         <v>1.18</v>
@@ -9021,7 +9021,7 @@
         <v>1.23</v>
       </c>
       <c r="AK53">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9609,16 +9609,16 @@
         <v>3</v>
       </c>
       <c r="Q57">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="R57">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
         <v>1.29</v>
       </c>
       <c r="T57">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U57">
         <v>2.4</v>
@@ -9642,7 +9642,7 @@
         <v>1.63</v>
       </c>
       <c r="AB57">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC57">
         <v>2.52</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -11067,16 +11067,16 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="O66">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="P66">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="Q66">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="R66">
         <v>2.32</v>
@@ -11088,13 +11088,13 @@
         <v>3.78</v>
       </c>
       <c r="U66">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V66">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W66">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X66">
         <v>1.03</v>
@@ -11103,19 +11103,19 @@
         <v>1.11</v>
       </c>
       <c r="Z66">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="AA66">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AB66">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AC66">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AD66">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE66">
         <v>1.22</v>
@@ -11140,7 +11140,7 @@
         <v>1.23</v>
       </c>
       <c r="AK66">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11719,28 +11719,28 @@
         </is>
       </c>
       <c r="N70">
+        <v>2.5</v>
+      </c>
+      <c r="O70">
+        <v>3.3</v>
+      </c>
+      <c r="P70">
         <v>2.93</v>
       </c>
-      <c r="O70">
-        <v>3.62</v>
-      </c>
-      <c r="P70">
-        <v>2.52</v>
-      </c>
       <c r="Q70">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="R70">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="S70">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T70">
+        <v>2.89</v>
+      </c>
+      <c r="U70">
         <v>2.9</v>
-      </c>
-      <c r="U70">
-        <v>2.88</v>
       </c>
       <c r="V70">
         <v>1.4</v>
@@ -11749,7 +11749,7 @@
         <v>1.05</v>
       </c>
       <c r="X70">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
         <v>1.33</v>
@@ -11758,25 +11758,25 @@
         <v>2.95</v>
       </c>
       <c r="AA70">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB70">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AC70">
-        <v>3.55</v>
+        <v>3.67</v>
       </c>
       <c r="AD70">
         <v>1.32</v>
       </c>
       <c r="AE70">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG70">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
         <v>1.5</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="O71">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="P71">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="Q71">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R71">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S71">
         <v>1.33</v>
       </c>
       <c r="T71">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="U71">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V71">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W71">
         <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z71">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA71">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB71">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC71">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="AD71">
         <v>1.38</v>
       </c>
       <c r="AE71">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
         <v>1.75</v>
       </c>
       <c r="AG71">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK71">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="O72">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P72">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="Q72">
         <v>2.9</v>
@@ -12084,10 +12084,10 @@
         <v>3.37</v>
       </c>
       <c r="AA72">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB72">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC72">
         <v>3.47</v>
@@ -12208,19 +12208,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O73">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P73">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q73">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R73">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="S73">
         <v>1.3</v>
@@ -12229,13 +12229,13 @@
         <v>3.25</v>
       </c>
       <c r="U73">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V73">
         <v>1.5</v>
       </c>
       <c r="W73">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X73">
         <v>1.01</v>
@@ -12247,16 +12247,16 @@
         <v>4.6</v>
       </c>
       <c r="AA73">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB73">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AC73">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="AD73">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE73">
         <v>1.15</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK73">
-        <v>2.61</v>
+        <v>2.48</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,19 +12371,19 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="O74">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>3.23</v>
+        <v>2.77</v>
       </c>
       <c r="Q74">
         <v>2.56</v>
       </c>
       <c r="R74">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S74">
         <v>1.29</v>
@@ -12410,13 +12410,13 @@
         <v>4.1</v>
       </c>
       <c r="AA74">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AB74">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC74">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AD74">
         <v>1.43</v>
@@ -12444,7 +12444,7 @@
         <v>1.23</v>
       </c>
       <c r="AK74">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,16 +12534,16 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="O75">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="P75">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="Q75">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="R75">
         <v>2.25</v>
@@ -12570,16 +12570,16 @@
         <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AA75">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AB75">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AC75">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD75">
         <v>1.3</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AK75">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="AL75">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2437,55 +2437,55 @@
         <v>2.55</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X13">
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2760,7 +2760,7 @@
         <v>3.2</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>3.23</v>
       </c>
       <c r="Q15">
         <v>2.61</v>
@@ -3246,7 +3246,7 @@
         <v>2.7</v>
       </c>
       <c r="O18">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
         <v>2.25</v>
@@ -3415,22 +3415,22 @@
         <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R19">
         <v>1.8</v>
       </c>
       <c r="S19">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="T19">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U19">
-        <v>3.88</v>
+        <v>3.95</v>
       </c>
       <c r="V19">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W19">
         <v>1.02</v>
@@ -3439,22 +3439,22 @@
         <v>1.15</v>
       </c>
       <c r="Y19">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="Z19">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AA19">
-        <v>3.2</v>
+        <v>3.31</v>
       </c>
       <c r="AB19">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC19">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AD19">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AE19">
         <v>1.02</v>
@@ -3479,7 +3479,7 @@
         <v>1.4</v>
       </c>
       <c r="AK19">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,7 +3572,7 @@
         <v>3.3</v>
       </c>
       <c r="O20">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P20">
         <v>1.9</v>
@@ -3599,7 +3599,7 @@
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.15</v>
@@ -3937,7 +3937,7 @@
         <v>1.68</v>
       </c>
       <c r="AB22">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="AC22">
         <v>2.46</v>
@@ -4260,10 +4260,10 @@
         <v>3.9</v>
       </c>
       <c r="AA24">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
         <v>2.88</v>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="N30">
-        <v>4.45</v>
+        <v>5.2</v>
       </c>
       <c r="O30">
-        <v>3.86</v>
+        <v>3.97</v>
       </c>
       <c r="P30">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="Q30">
         <v>5</v>
       </c>
       <c r="R30">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="S30">
         <v>1.36</v>
@@ -5232,25 +5232,25 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z30">
-        <v>3.64</v>
+        <v>3.76</v>
       </c>
       <c r="AA30">
         <v>1.85</v>
       </c>
       <c r="AB30">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AC30">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="AD30">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF30">
         <v>1.85</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK30">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="O31">
-        <v>3.27</v>
+        <v>3.15</v>
       </c>
       <c r="P31">
         <v>2.67</v>
@@ -5857,7 +5857,7 @@
         <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="Q34">
         <v>2.44</v>
@@ -6672,7 +6672,7 @@
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>4.05</v>
+        <v>3.9</v>
       </c>
       <c r="Q39">
         <v>2.44</v>
@@ -6835,7 +6835,7 @@
         <v>3</v>
       </c>
       <c r="P40">
-        <v>3.1</v>
+        <v>3.39</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="O44">
+        <v>2.97</v>
+      </c>
+      <c r="P44">
+        <v>2.45</v>
+      </c>
+      <c r="Q44">
+        <v>3.84</v>
+      </c>
+      <c r="R44">
+        <v>1.84</v>
+      </c>
+      <c r="S44">
+        <v>1.57</v>
+      </c>
+      <c r="T44">
+        <v>2.2</v>
+      </c>
+      <c r="U44">
+        <v>3.6</v>
+      </c>
+      <c r="V44">
+        <v>1.25</v>
+      </c>
+      <c r="W44">
+        <v>1.03</v>
+      </c>
+      <c r="X44">
+        <v>1.1</v>
+      </c>
+      <c r="Y44">
+        <v>1.54</v>
+      </c>
+      <c r="Z44">
+        <v>2.27</v>
+      </c>
+      <c r="AA44">
         <v>2.87</v>
       </c>
-      <c r="P44">
-        <v>2.6</v>
-      </c>
-      <c r="Q44">
-        <v>3</v>
-      </c>
-      <c r="R44">
-        <v>1.85</v>
-      </c>
-      <c r="S44">
-        <v>1.52</v>
-      </c>
-      <c r="T44">
-        <v>2.31</v>
-      </c>
-      <c r="U44">
-        <v>3.5</v>
-      </c>
-      <c r="V44">
-        <v>1.21</v>
-      </c>
-      <c r="W44">
-        <v>1.01</v>
-      </c>
-      <c r="X44">
-        <v>1.11</v>
-      </c>
-      <c r="Y44">
-        <v>1.55</v>
-      </c>
-      <c r="Z44">
-        <v>2.24</v>
-      </c>
-      <c r="AA44">
-        <v>2.7</v>
-      </c>
       <c r="AB44">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AC44">
-        <v>5.8</v>
+        <v>5.45</v>
       </c>
       <c r="AD44">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE44">
         <v>1.03</v>
       </c>
       <c r="AF44">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AG44">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK44">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,37 +7644,37 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="O45">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="P45">
-        <v>2.01</v>
+        <v>2.6</v>
       </c>
       <c r="Q45">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="R45">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S45">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="T45">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="U45">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="V45">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W45">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X45">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y45">
         <v>1.55</v>
@@ -7686,7 +7686,7 @@
         <v>2.7</v>
       </c>
       <c r="AB45">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AC45">
         <v>5.8</v>
@@ -7698,26 +7698,26 @@
         <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AG45">
+        <v>1.58</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
+        <v>1.3</v>
+      </c>
+      <c r="AK45">
         <v>1.53</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.33</v>
-      </c>
-      <c r="AK45">
-        <v>1.22</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7849,7 +7849,7 @@
         <v>1.58</v>
       </c>
       <c r="AB46">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC46">
         <v>2.33</v>
@@ -7861,7 +7861,7 @@
         <v>1.16</v>
       </c>
       <c r="AF46">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AG46">
         <v>2.5</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O48">
         <v>3.7</v>
@@ -8160,7 +8160,7 @@
         <v>1.53</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>1.02</v>
@@ -8190,7 +8190,7 @@
         <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8459,22 +8459,22 @@
         </is>
       </c>
       <c r="N50">
-        <v>6.65</v>
+        <v>6.51</v>
       </c>
       <c r="O50">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="P50">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q50">
         <v>4.73</v>
       </c>
       <c r="R50">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
         <v>3.75</v>
@@ -8501,7 +8501,7 @@
         <v>1.52</v>
       </c>
       <c r="AB50">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC50">
         <v>2.3</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="O51">
-        <v>4.3</v>
+        <v>3.97</v>
       </c>
       <c r="P51">
-        <v>2.71</v>
+        <v>2.41</v>
       </c>
       <c r="Q51">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="R51">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="S51">
         <v>1.06</v>
@@ -8658,7 +8658,7 @@
         <v>1.01</v>
       </c>
       <c r="Z51">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AA51">
         <v>1.15</v>
@@ -8695,7 +8695,7 @@
         <v>1.17</v>
       </c>
       <c r="AK51">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="O52">
         <v>3.47</v>
@@ -8858,7 +8858,7 @@
         <v>1.18</v>
       </c>
       <c r="AK52">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -9929,7 +9929,7 @@
         <v>1.1</v>
       </c>
       <c r="O59">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
       <c r="P59">
         <v>9.6</v>
@@ -9938,7 +9938,7 @@
         <v>1.5</v>
       </c>
       <c r="R59">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="S59">
         <v>1.14</v>
@@ -10092,7 +10092,7 @@
         <v>2.15</v>
       </c>
       <c r="O60">
-        <v>3.88</v>
+        <v>3.64</v>
       </c>
       <c r="P60">
         <v>2.48</v>
@@ -10101,7 +10101,7 @@
         <v>2.8</v>
       </c>
       <c r="R60">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="S60">
         <v>1.22</v>
@@ -10128,10 +10128,10 @@
         <v>5.75</v>
       </c>
       <c r="AA60">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB60">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC60">
         <v>2.16</v>
@@ -10146,7 +10146,7 @@
         <v>1.41</v>
       </c>
       <c r="AG60">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>1.28</v>
       </c>
       <c r="AB61">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AC61">
         <v>1.84</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.01</v>
+        <v>2.62</v>
       </c>
       <c r="O62">
-        <v>4.05</v>
+        <v>3.98</v>
       </c>
       <c r="P62">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
       </c>
       <c r="R62">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="S62">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="U62">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V62">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="W62">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X62">
         <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z62">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AA62">
+        <v>1.33</v>
+      </c>
+      <c r="AB62">
+        <v>3.1</v>
+      </c>
+      <c r="AC62">
+        <v>1.87</v>
+      </c>
+      <c r="AD62">
+        <v>1.83</v>
+      </c>
+      <c r="AE62">
+        <v>1.33</v>
+      </c>
+      <c r="AF62">
         <v>1.3</v>
       </c>
-      <c r="AB62">
-        <v>3.3</v>
-      </c>
-      <c r="AC62">
-        <v>1.81</v>
-      </c>
-      <c r="AD62">
-        <v>1.9</v>
-      </c>
-      <c r="AE62">
-        <v>1.4</v>
-      </c>
-      <c r="AF62">
-        <v>1.29</v>
-      </c>
       <c r="AG62">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="O63">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
-        <v>4.07</v>
+        <v>3.25</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -10611,16 +10611,16 @@
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z63">
         <v>2.97</v>
       </c>
       <c r="AA63">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB63">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AC63">
         <v>3.5</v>
@@ -10768,7 +10768,7 @@
         <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X64">
         <v>1.03</v>
@@ -11070,16 +11070,16 @@
         <v>2.27</v>
       </c>
       <c r="O66">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q66">
         <v>2.46</v>
       </c>
       <c r="R66">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="S66">
         <v>1.25</v>
@@ -11140,7 +11140,7 @@
         <v>1.23</v>
       </c>
       <c r="AK66">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11233,61 +11233,61 @@
         <v>2.15</v>
       </c>
       <c r="O67">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P67">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="Q67">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S67">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="U67">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V67">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W67">
         <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="AA67">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AB67">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AC67">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AD67">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AE67">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AG67">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK67">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11725,7 +11725,7 @@
         <v>3.3</v>
       </c>
       <c r="P70">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="Q70">
         <v>2.84</v>
@@ -11758,10 +11758,10 @@
         <v>2.95</v>
       </c>
       <c r="AA70">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB70">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC70">
         <v>3.67</v>
@@ -11792,7 +11792,7 @@
         <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11888,7 +11888,7 @@
         <v>3.84</v>
       </c>
       <c r="P71">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="Q71">
         <v>2.2</v>
@@ -11897,16 +11897,16 @@
         <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T71">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="U71">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="V71">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
         <v>1.11</v>
@@ -11927,7 +11927,7 @@
         <v>2</v>
       </c>
       <c r="AC71">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="AD71">
         <v>1.38</v>
@@ -12087,7 +12087,7 @@
         <v>2</v>
       </c>
       <c r="AB72">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AC72">
         <v>3.47</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>3.63</v>
       </c>
       <c r="P74">
-        <v>2.77</v>
+        <v>2.9</v>
       </c>
       <c r="Q74">
         <v>2.56</v>
@@ -12416,7 +12416,7 @@
         <v>2.2</v>
       </c>
       <c r="AC74">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AD74">
         <v>1.43</v>
@@ -12570,7 +12570,7 @@
         <v>1.25</v>
       </c>
       <c r="Z75">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA75">
         <v>1.87</v>
@@ -12579,7 +12579,7 @@
         <v>1.86</v>
       </c>
       <c r="AC75">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD75">
         <v>1.3</v>
@@ -12607,7 +12607,7 @@
         <v>1.07</v>
       </c>
       <c r="AK75">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="O77">
-        <v>9.85</v>
+        <v>7.6</v>
       </c>
       <c r="P77">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="Q77">
         <v>1.47</v>
@@ -12899,16 +12899,16 @@
         <v>4.84</v>
       </c>
       <c r="AA77">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AB77">
         <v>2.87</v>
       </c>
       <c r="AC77">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AD77">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE77">
         <v>1.34</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.93</v>
+        <v>2.79</v>
       </c>
       <c r="O78">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="P78">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q78">
         <v>3.5</v>
@@ -13062,10 +13062,10 @@
         <v>2.66</v>
       </c>
       <c r="AA78">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AB78">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC78">
         <v>4.2</v>
@@ -13186,16 +13186,16 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="O79">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="P79">
-        <v>4.49</v>
+        <v>3.7</v>
       </c>
       <c r="Q79">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R79">
         <v>1.99</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK79">
         <v>1.95</v>
@@ -13349,19 +13349,19 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="Q80">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R80">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S80">
         <v>1.29</v>
@@ -13370,7 +13370,7 @@
         <v>3.25</v>
       </c>
       <c r="U80">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V80">
         <v>1.53</v>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK80">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,25 +13512,25 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O81">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P81">
-        <v>3.21</v>
+        <v>2.87</v>
       </c>
       <c r="Q81">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="R81">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="S81">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="T81">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="U81">
         <v>3.02</v>
@@ -13545,10 +13545,10 @@
         <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z81">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AA81">
         <v>2.23</v>
@@ -13838,22 +13838,22 @@
         </is>
       </c>
       <c r="N83">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O83">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="P83">
-        <v>3.59</v>
+        <v>2.88</v>
       </c>
       <c r="Q83">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="R83">
         <v>2.46</v>
       </c>
       <c r="S83">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T83">
         <v>3.4</v>
@@ -13877,10 +13877,10 @@
         <v>4.2</v>
       </c>
       <c r="AA83">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AB83">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC83">
         <v>2.63</v>
@@ -13895,7 +13895,7 @@
         <v>1.53</v>
       </c>
       <c r="AG83">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14001,28 +14001,28 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O84">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P84">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q84">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="R84">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="S84">
         <v>1.35</v>
       </c>
       <c r="T84">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="U84">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="V84">
         <v>1.41</v>
@@ -14037,7 +14037,7 @@
         <v>1.27</v>
       </c>
       <c r="Z84">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="AA84">
         <v>1.92</v>
@@ -14052,7 +14052,7 @@
         <v>1.3</v>
       </c>
       <c r="AE84">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF84">
         <v>1.7</v>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AK84">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14164,19 +14164,19 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="O85">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="P85">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q85">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="R85">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="S85">
         <v>1.29</v>
@@ -14197,19 +14197,19 @@
         <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="AA85">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB85">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AC85">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AD85">
         <v>1.4</v>
@@ -14218,7 +14218,7 @@
         <v>1.15</v>
       </c>
       <c r="AF85">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG85">
         <v>2.15</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2757,10 +2757,10 @@
         <v>1.91</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="P15">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
         <v>2.61</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O17">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
         <v>4.05</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P18">
         <v>2.25</v>
@@ -3436,7 +3436,7 @@
         <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Y19">
         <v>1.71</v>
@@ -3445,7 +3445,7 @@
         <v>1.98</v>
       </c>
       <c r="AA19">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="AB19">
         <v>1.28</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O20">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P20">
         <v>1.9</v>
@@ -3759,7 +3759,7 @@
         <v>1.37</v>
       </c>
       <c r="W21">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X21">
         <v>1.01</v>
@@ -4263,7 +4263,7 @@
         <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC24">
         <v>2.88</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="O25">
         <v>3.25</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>5.2</v>
+        <v>5.63</v>
       </c>
       <c r="O30">
         <v>3.97</v>
       </c>
       <c r="P30">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="Q30">
         <v>5</v>
@@ -5217,7 +5217,7 @@
         <v>1.36</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U30">
         <v>2.88</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="O31">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="P31">
         <v>2.67</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="O33">
         <v>3.35</v>
       </c>
       <c r="P33">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -5854,7 +5854,7 @@
         <v>2.17</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
         <v>2.92</v>
@@ -6379,7 +6379,7 @@
         <v>3.98</v>
       </c>
       <c r="AA37">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB37">
         <v>2.15</v>
@@ -6672,7 +6672,7 @@
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="Q39">
         <v>2.44</v>
@@ -6705,10 +6705,10 @@
         <v>3.4</v>
       </c>
       <c r="AA39">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
@@ -6835,7 +6835,7 @@
         <v>3</v>
       </c>
       <c r="P40">
-        <v>3.39</v>
+        <v>3.2</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6995,7 +6995,7 @@
         <v>1.43</v>
       </c>
       <c r="O41">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P41">
         <v>5</v>
@@ -7167,13 +7167,13 @@
         <v>3.04</v>
       </c>
       <c r="R42">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>3.26</v>
+        <v>3.34</v>
       </c>
       <c r="U42">
         <v>2.25</v>
@@ -7188,10 +7188,10 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z42">
-        <v>4.61</v>
+        <v>4.82</v>
       </c>
       <c r="AA42">
         <v>1.58</v>
@@ -7203,10 +7203,10 @@
         <v>2.43</v>
       </c>
       <c r="AD42">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE42">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF42">
         <v>1.44</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK42">
         <v>1.44</v>
@@ -7499,7 +7499,7 @@
         <v>1.57</v>
       </c>
       <c r="T44">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U44">
         <v>3.6</v>
@@ -7686,7 +7686,7 @@
         <v>2.7</v>
       </c>
       <c r="AB45">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AC45">
         <v>5.8</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="O48">
         <v>3.7</v>
       </c>
       <c r="P48">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q48">
         <v>2.3</v>
@@ -8190,7 +8190,7 @@
         <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8335,10 +8335,10 @@
         <v>6.8</v>
       </c>
       <c r="AA49">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB49">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AC49">
         <v>1.86</v>
@@ -9117,7 +9117,7 @@
         <v>3.6</v>
       </c>
       <c r="P54">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -9639,7 +9639,7 @@
         <v>4</v>
       </c>
       <c r="AA57">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB57">
         <v>2.15</v>
@@ -10916,7 +10916,7 @@
         <v>3.04</v>
       </c>
       <c r="R65">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="S65">
         <v>1.3</v>
@@ -11598,7 +11598,7 @@
         <v>1.85</v>
       </c>
       <c r="AB69">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC69">
         <v>2.59</v>
@@ -11725,7 +11725,7 @@
         <v>3.3</v>
       </c>
       <c r="P70">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="Q70">
         <v>2.84</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="O71">
         <v>3.84</v>
@@ -11897,13 +11897,13 @@
         <v>2.25</v>
       </c>
       <c r="S71">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T71">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="U71">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="V71">
         <v>1.44</v>
@@ -11927,10 +11927,10 @@
         <v>2</v>
       </c>
       <c r="AC71">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AD71">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE71">
         <v>1.13</v>
@@ -12060,16 +12060,16 @@
         <v>2.1</v>
       </c>
       <c r="S72">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T72">
         <v>2.9</v>
       </c>
       <c r="U72">
-        <v>2.67</v>
+        <v>2.91</v>
       </c>
       <c r="V72">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W72">
         <v>1.08</v>
@@ -12081,16 +12081,16 @@
         <v>1.24</v>
       </c>
       <c r="Z72">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="AA72">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AB72">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AC72">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="AD72">
         <v>1.27</v>
@@ -12253,7 +12253,7 @@
         <v>2.13</v>
       </c>
       <c r="AC73">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AD73">
         <v>1.47</v>
@@ -12281,7 +12281,7 @@
         <v>1.17</v>
       </c>
       <c r="AK73">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12579,10 +12579,10 @@
         <v>1.86</v>
       </c>
       <c r="AC75">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AD75">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE75">
         <v>1.07</v>
@@ -12607,7 +12607,7 @@
         <v>1.07</v>
       </c>
       <c r="AK75">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>1.2</v>
       </c>
       <c r="O77">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="P77">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q77">
         <v>1.47</v>
@@ -13225,7 +13225,7 @@
         <v>2.91</v>
       </c>
       <c r="AA79">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB79">
         <v>1.7</v>
@@ -13234,7 +13234,7 @@
         <v>3.72</v>
       </c>
       <c r="AD79">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AE79">
         <v>1.05</v>
@@ -13349,7 +13349,7 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O80">
         <v>3.6</v>
@@ -13400,7 +13400,7 @@
         <v>1.48</v>
       </c>
       <c r="AE80">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AF80">
         <v>1.53</v>
@@ -14074,7 +14074,7 @@
         <v>1.5</v>
       </c>
       <c r="AK84">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AL84">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2280,16 +2280,16 @@
         <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T12">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="U12">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="V12">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W12">
         <v>1.08</v>
@@ -2304,7 +2304,7 @@
         <v>3.28</v>
       </c>
       <c r="AA12">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AB12">
         <v>2</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK12">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>3.9</v>
       </c>
       <c r="AA13">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AB13">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC13">
         <v>2.74</v>
@@ -2485,7 +2485,7 @@
         <v>1.56</v>
       </c>
       <c r="AG13">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O14">
         <v>4.25</v>
@@ -2630,10 +2630,10 @@
         <v>4.51</v>
       </c>
       <c r="AA14">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB14">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AC14">
         <v>2.52</v>
@@ -2757,10 +2757,10 @@
         <v>1.91</v>
       </c>
       <c r="O15">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q15">
         <v>2.61</v>
@@ -2793,7 +2793,7 @@
         <v>2.7</v>
       </c>
       <c r="AA15">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AB15">
         <v>1.65</v>
@@ -2802,13 +2802,13 @@
         <v>4.14</v>
       </c>
       <c r="AD15">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE15">
         <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG15">
         <v>1.8</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
         <v>1.73</v>
@@ -3110,7 +3110,7 @@
         <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y17">
         <v>1.29</v>
@@ -3119,16 +3119,16 @@
         <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AC17">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="AD17">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE17">
         <v>1.07</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AK17">
         <v>2</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O18">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
         <v>2.25</v>
@@ -3276,16 +3276,16 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
         <v>3.9</v>
       </c>
       <c r="AA18">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AB18">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AC18">
         <v>2.74</v>
@@ -3294,7 +3294,7 @@
         <v>1.35</v>
       </c>
       <c r="AE18">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF18">
         <v>1.62</v>
@@ -3415,7 +3415,7 @@
         <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R19">
         <v>1.8</v>
@@ -3445,16 +3445,16 @@
         <v>1.98</v>
       </c>
       <c r="AA19">
-        <v>3.37</v>
+        <v>3.2</v>
       </c>
       <c r="AB19">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC19">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AD19">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AE19">
         <v>1.02</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.15</v>
@@ -3771,7 +3771,7 @@
         <v>3.14</v>
       </c>
       <c r="AA21">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB21">
         <v>1.83</v>
@@ -3968,7 +3968,7 @@
         <v>1.23</v>
       </c>
       <c r="AK22">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="U24">
         <v>2.45</v>
@@ -4257,22 +4257,22 @@
         <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="AA24">
         <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE24">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF24">
         <v>1.62</v>
@@ -4396,7 +4396,7 @@
         <v>3.34</v>
       </c>
       <c r="R25">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S25">
         <v>1.43</v>
@@ -4417,10 +4417,10 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="Z25">
-        <v>3.43</v>
+        <v>3.08</v>
       </c>
       <c r="AA25">
         <v>2.07</v>
@@ -5202,10 +5202,10 @@
         <v>5.63</v>
       </c>
       <c r="O30">
-        <v>3.97</v>
+        <v>3.65</v>
       </c>
       <c r="P30">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="Q30">
         <v>5</v>
@@ -5220,7 +5220,7 @@
         <v>2.9</v>
       </c>
       <c r="U30">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="V30">
         <v>1.36</v>
@@ -5232,7 +5232,7 @@
         <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z30">
         <v>3.76</v>
@@ -5407,7 +5407,7 @@
         <v>1.65</v>
       </c>
       <c r="AC31">
-        <v>3.68</v>
+        <v>4.28</v>
       </c>
       <c r="AD31">
         <v>1.2</v>
@@ -5694,7 +5694,7 @@
         <v>3.35</v>
       </c>
       <c r="P33">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q33">
         <v>3.1</v>
@@ -5736,7 +5736,7 @@
         <v>3.32</v>
       </c>
       <c r="AD33">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AE33">
         <v>1.12</v>
@@ -5761,7 +5761,7 @@
         <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5884,7 +5884,7 @@
         <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z34">
         <v>5.11</v>
@@ -5893,10 +5893,10 @@
         <v>1.54</v>
       </c>
       <c r="AB34">
+        <v>2.27</v>
+      </c>
+      <c r="AC34">
         <v>2.28</v>
-      </c>
-      <c r="AC34">
-        <v>2.27</v>
       </c>
       <c r="AD34">
         <v>1.54</v>
@@ -6358,16 +6358,16 @@
         <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="V37">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W37">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X37">
         <v>1.03</v>
@@ -6672,13 +6672,13 @@
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="Q39">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R39">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="S39">
         <v>1.36</v>
@@ -7194,19 +7194,19 @@
         <v>4.82</v>
       </c>
       <c r="AA42">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB42">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AC42">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AD42">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AE42">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF42">
         <v>1.44</v>
@@ -7369,13 +7369,13 @@
         <v>1.25</v>
       </c>
       <c r="AE43">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         <v>1.57</v>
       </c>
       <c r="T44">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U44">
         <v>3.6</v>
@@ -7523,7 +7523,7 @@
         <v>2.87</v>
       </c>
       <c r="AB44">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC44">
         <v>5.45</v>
@@ -7674,13 +7674,13 @@
         <v>1.01</v>
       </c>
       <c r="X45">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y45">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z45">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="AA45">
         <v>2.7</v>
@@ -7698,10 +7698,10 @@
         <v>1.03</v>
       </c>
       <c r="AF45">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AG45">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>2.28</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
         <v>3.5</v>
@@ -7861,7 +7861,7 @@
         <v>1.16</v>
       </c>
       <c r="AF46">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG46">
         <v>2.5</v>
@@ -8015,10 +8015,10 @@
         <v>1.82</v>
       </c>
       <c r="AC47">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AD47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE47">
         <v>1.07</v>
@@ -8148,10 +8148,10 @@
         <v>2.38</v>
       </c>
       <c r="S48">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U48">
         <v>2.3</v>
@@ -8166,10 +8166,10 @@
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA48">
         <v>1.66</v>
@@ -8181,16 +8181,16 @@
         <v>2.56</v>
       </c>
       <c r="AD48">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
         <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="O49">
         <v>6</v>
@@ -8341,13 +8341,13 @@
         <v>3.1</v>
       </c>
       <c r="AC49">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AD49">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="AE49">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AF49">
         <v>1.6</v>
@@ -8858,7 +8858,7 @@
         <v>1.18</v>
       </c>
       <c r="AK52">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8951,16 +8951,16 @@
         <v>1.95</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
         <v>3.1</v>
       </c>
       <c r="Q53">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R53">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="S53">
         <v>1.23</v>
@@ -8990,13 +8990,13 @@
         <v>1.57</v>
       </c>
       <c r="AB53">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AC53">
         <v>2.28</v>
       </c>
       <c r="AD53">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE53">
         <v>1.18</v>
@@ -9021,7 +9021,7 @@
         <v>1.23</v>
       </c>
       <c r="AK53">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>3.6</v>
       </c>
       <c r="P54">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -9162,13 +9162,13 @@
         <v>1.43</v>
       </c>
       <c r="AE54">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF54">
         <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>4.33</v>
       </c>
       <c r="AA55">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB55">
         <v>2.25</v>
@@ -9609,16 +9609,16 @@
         <v>3</v>
       </c>
       <c r="Q57">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S57">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T57">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="U57">
         <v>2.4</v>
@@ -9639,7 +9639,7 @@
         <v>4</v>
       </c>
       <c r="AA57">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AB57">
         <v>2.15</v>
@@ -9654,7 +9654,7 @@
         <v>1.14</v>
       </c>
       <c r="AF57">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG57">
         <v>2.3</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK57">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -10753,19 +10753,19 @@
         <v>2.65</v>
       </c>
       <c r="R64">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S64">
         <v>1.3</v>
       </c>
       <c r="T64">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U64">
-        <v>2.51</v>
+        <v>2.34</v>
       </c>
       <c r="V64">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W64">
         <v>1.1</v>
@@ -10774,10 +10774,10 @@
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z64">
-        <v>4.21</v>
+        <v>4.1</v>
       </c>
       <c r="AA64">
         <v>1.67</v>
@@ -10786,19 +10786,19 @@
         <v>2.04</v>
       </c>
       <c r="AC64">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AD64">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AE64">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF64">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG64">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>2.5</v>
       </c>
       <c r="Q65">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="R65">
         <v>2.13</v>
@@ -10934,13 +10934,13 @@
         <v>1.09</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
         <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA65">
         <v>1.73</v>
@@ -10949,16 +10949,16 @@
         <v>1.95</v>
       </c>
       <c r="AC65">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="AD65">
         <v>1.33</v>
       </c>
       <c r="AE65">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF65">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG65">
         <v>2.2</v>
@@ -11070,7 +11070,7 @@
         <v>2.27</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
         <v>2.75</v>
@@ -11106,7 +11106,7 @@
         <v>5</v>
       </c>
       <c r="AA66">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB66">
         <v>2.43</v>
@@ -11124,7 +11124,7 @@
         <v>1.44</v>
       </c>
       <c r="AG66">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,80 +11393,80 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="O68">
+        <v>3.5</v>
+      </c>
+      <c r="P68">
+        <v>4.1</v>
+      </c>
+      <c r="Q68">
+        <v>2.22</v>
+      </c>
+      <c r="R68">
+        <v>2.21</v>
+      </c>
+      <c r="S68">
+        <v>1.3</v>
+      </c>
+      <c r="T68">
         <v>3.2</v>
       </c>
-      <c r="P68">
-        <v>3.43</v>
-      </c>
-      <c r="Q68">
-        <v>2.68</v>
-      </c>
-      <c r="R68">
+      <c r="U68">
+        <v>2.32</v>
+      </c>
+      <c r="V68">
+        <v>1.51</v>
+      </c>
+      <c r="W68">
+        <v>1.11</v>
+      </c>
+      <c r="X68">
+        <v>1</v>
+      </c>
+      <c r="Y68">
+        <v>1.18</v>
+      </c>
+      <c r="Z68">
+        <v>3.85</v>
+      </c>
+      <c r="AA68">
+        <v>1.85</v>
+      </c>
+      <c r="AB68">
+        <v>2.05</v>
+      </c>
+      <c r="AC68">
+        <v>2.59</v>
+      </c>
+      <c r="AD68">
+        <v>1.39</v>
+      </c>
+      <c r="AE68">
+        <v>1.13</v>
+      </c>
+      <c r="AF68">
+        <v>1.65</v>
+      </c>
+      <c r="AG68">
+        <v>2.1</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ68">
+        <v>1.25</v>
+      </c>
+      <c r="AK68">
         <v>1.95</v>
-      </c>
-      <c r="S68">
-        <v>1.4</v>
-      </c>
-      <c r="T68">
-        <v>2.75</v>
-      </c>
-      <c r="U68">
-        <v>2.88</v>
-      </c>
-      <c r="V68">
-        <v>1.36</v>
-      </c>
-      <c r="W68">
-        <v>1.06</v>
-      </c>
-      <c r="X68">
-        <v>1.01</v>
-      </c>
-      <c r="Y68">
-        <v>1.26</v>
-      </c>
-      <c r="Z68">
-        <v>3.2</v>
-      </c>
-      <c r="AA68">
-        <v>2.05</v>
-      </c>
-      <c r="AB68">
-        <v>1.75</v>
-      </c>
-      <c r="AC68">
-        <v>3.2</v>
-      </c>
-      <c r="AD68">
-        <v>1.26</v>
-      </c>
-      <c r="AE68">
-        <v>1.05</v>
-      </c>
-      <c r="AF68">
-        <v>1.73</v>
-      </c>
-      <c r="AG68">
-        <v>1.92</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ68">
-        <v>1.26</v>
-      </c>
-      <c r="AK68">
-        <v>1.63</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="O69">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P69">
-        <v>4.2</v>
+        <v>3.43</v>
       </c>
       <c r="Q69">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="R69">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="S69">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T69">
+        <v>2.88</v>
+      </c>
+      <c r="U69">
+        <v>2.7</v>
+      </c>
+      <c r="V69">
+        <v>1.4</v>
+      </c>
+      <c r="W69">
+        <v>1.06</v>
+      </c>
+      <c r="X69">
+        <v>1.01</v>
+      </c>
+      <c r="Y69">
+        <v>1.26</v>
+      </c>
+      <c r="Z69">
         <v>3.2</v>
       </c>
-      <c r="U69">
-        <v>2.32</v>
-      </c>
-      <c r="V69">
-        <v>1.49</v>
-      </c>
-      <c r="W69">
-        <v>1.11</v>
-      </c>
-      <c r="X69">
-        <v>1</v>
-      </c>
-      <c r="Y69">
-        <v>1.18</v>
-      </c>
-      <c r="Z69">
-        <v>3.85</v>
-      </c>
       <c r="AA69">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB69">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AC69">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AD69">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE69">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AG69">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
-        <v>1.97</v>
+        <v>1.63</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11776,7 +11776,7 @@
         <v>1.74</v>
       </c>
       <c r="AG70">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11921,7 +11921,7 @@
         <v>4</v>
       </c>
       <c r="AA71">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AB71">
         <v>2</v>
@@ -12051,7 +12051,7 @@
         <v>3.4</v>
       </c>
       <c r="P72">
-        <v>2.8</v>
+        <v>2.93</v>
       </c>
       <c r="Q72">
         <v>2.9</v>
@@ -12060,7 +12060,7 @@
         <v>2.1</v>
       </c>
       <c r="S72">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T72">
         <v>2.9</v>
@@ -12087,7 +12087,7 @@
         <v>1.98</v>
       </c>
       <c r="AB72">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC72">
         <v>3.43</v>
@@ -12099,10 +12099,10 @@
         <v>1.06</v>
       </c>
       <c r="AF72">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AG72">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>4.6</v>
       </c>
       <c r="P73">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="Q73">
         <v>1.94</v>
@@ -12241,16 +12241,16 @@
         <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z73">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AA73">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB73">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AC73">
         <v>2.44</v>
@@ -12374,25 +12374,25 @@
         <v>2.18</v>
       </c>
       <c r="O74">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="P74">
         <v>2.9</v>
       </c>
       <c r="Q74">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="R74">
         <v>2.25</v>
       </c>
       <c r="S74">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T74">
         <v>3.4</v>
       </c>
       <c r="U74">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V74">
         <v>1.53</v>
@@ -12401,7 +12401,7 @@
         <v>1.11</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y74">
         <v>1.21</v>
@@ -12416,13 +12416,13 @@
         <v>2.2</v>
       </c>
       <c r="AC74">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="AD74">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE74">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF74">
         <v>1.53</v>
@@ -12537,7 +12537,7 @@
         <v>1.47</v>
       </c>
       <c r="O75">
-        <v>3.9</v>
+        <v>4.22</v>
       </c>
       <c r="P75">
         <v>6.8</v>
@@ -12863,16 +12863,16 @@
         <v>1.2</v>
       </c>
       <c r="O77">
-        <v>7.7</v>
+        <v>7.25</v>
       </c>
       <c r="P77">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q77">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="R77">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="S77">
         <v>1.22</v>
@@ -12881,10 +12881,10 @@
         <v>4</v>
       </c>
       <c r="U77">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V77">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W77">
         <v>1.2</v>
@@ -12896,7 +12896,7 @@
         <v>1.11</v>
       </c>
       <c r="Z77">
-        <v>4.84</v>
+        <v>4.91</v>
       </c>
       <c r="AA77">
         <v>1.34</v>
@@ -12905,10 +12905,10 @@
         <v>2.87</v>
       </c>
       <c r="AC77">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="AD77">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AE77">
         <v>1.34</v>
@@ -13029,7 +13029,7 @@
         <v>3.14</v>
       </c>
       <c r="P78">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q78">
         <v>3.5</v>
@@ -13204,7 +13204,7 @@
         <v>1.4</v>
       </c>
       <c r="T79">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U79">
         <v>2.8</v>
@@ -13222,10 +13222,10 @@
         <v>1.33</v>
       </c>
       <c r="Z79">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="AA79">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB79">
         <v>1.7</v>
@@ -13243,7 +13243,7 @@
         <v>1.85</v>
       </c>
       <c r="AG79">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P80">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK80">
         <v>1.65</v>
@@ -13838,16 +13838,16 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="O83">
-        <v>3.71</v>
+        <v>3.63</v>
       </c>
       <c r="P83">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="Q83">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="R83">
         <v>2.46</v>
@@ -13886,16 +13886,16 @@
         <v>2.63</v>
       </c>
       <c r="AD83">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE83">
         <v>1.14</v>
       </c>
       <c r="AF83">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG83">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.3</v>
       </c>
       <c r="AK83">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14052,7 +14052,7 @@
         <v>1.3</v>
       </c>
       <c r="AE84">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF84">
         <v>1.7</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="Q13">
         <v>2.85</v>
@@ -2757,7 +2757,7 @@
         <v>1.91</v>
       </c>
       <c r="O15">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="P15">
         <v>3.6</v>
@@ -2793,7 +2793,7 @@
         <v>2.7</v>
       </c>
       <c r="AA15">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AB15">
         <v>1.65</v>
@@ -2802,7 +2802,7 @@
         <v>4.14</v>
       </c>
       <c r="AD15">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE15">
         <v>1.03</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="O18">
         <v>3.3</v>
@@ -3934,10 +3934,10 @@
         <v>4.1</v>
       </c>
       <c r="AA22">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AB22">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC22">
         <v>2.46</v>
@@ -4239,7 +4239,7 @@
         <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U24">
         <v>2.45</v>
@@ -4257,7 +4257,7 @@
         <v>1.22</v>
       </c>
       <c r="Z24">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="AA24">
         <v>1.75</v>
@@ -4266,13 +4266,13 @@
         <v>2.05</v>
       </c>
       <c r="AC24">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD24">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
         <v>1.62</v>
@@ -7001,16 +7001,16 @@
         <v>5</v>
       </c>
       <c r="Q41">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R41">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="S41">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T41">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="U41">
         <v>3.2</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O42">
         <v>3.6</v>
@@ -7206,7 +7206,7 @@
         <v>1.55</v>
       </c>
       <c r="AE42">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AF42">
         <v>1.44</v>
@@ -9117,7 +9117,7 @@
         <v>3.6</v>
       </c>
       <c r="P54">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -9159,7 +9159,7 @@
         <v>2.39</v>
       </c>
       <c r="AD54">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AE54">
         <v>1.2</v>
@@ -9295,10 +9295,10 @@
         <v>3.46</v>
       </c>
       <c r="U55">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="V55">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W55">
         <v>1.13</v>
@@ -10753,22 +10753,22 @@
         <v>2.65</v>
       </c>
       <c r="R64">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S64">
         <v>1.3</v>
       </c>
       <c r="T64">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U64">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="V64">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
         <v>1.03</v>
@@ -10786,19 +10786,19 @@
         <v>2.04</v>
       </c>
       <c r="AC64">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="AD64">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE64">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AF64">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG64">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>2.5</v>
       </c>
       <c r="Q65">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="R65">
         <v>2.13</v>
@@ -10934,28 +10934,28 @@
         <v>1.09</v>
       </c>
       <c r="X65">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y65">
         <v>1.22</v>
       </c>
       <c r="Z65">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="AA65">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB65">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC65">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="AD65">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE65">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF65">
         <v>1.62</v>
@@ -11230,25 +11230,25 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="O67">
         <v>3.1</v>
       </c>
       <c r="P67">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="Q67">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="R67">
         <v>2.15</v>
       </c>
       <c r="S67">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="U67">
         <v>2.62</v>
@@ -11260,34 +11260,34 @@
         <v>1.08</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y67">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z67">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="AA67">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AB67">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AC67">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="AD67">
         <v>1.28</v>
       </c>
       <c r="AE67">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF67">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG67">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK67">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="O68">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P68">
         <v>4.1</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK68">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11571,10 +11571,10 @@
         <v>1.95</v>
       </c>
       <c r="S69">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T69">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U69">
         <v>2.7</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK69">
         <v>1.63</v>
@@ -12214,7 +12214,7 @@
         <v>4.6</v>
       </c>
       <c r="P73">
-        <v>5.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q73">
         <v>1.94</v>
@@ -12253,13 +12253,13 @@
         <v>2.15</v>
       </c>
       <c r="AC73">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="AD73">
         <v>1.47</v>
       </c>
       <c r="AE73">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF73">
         <v>1.75</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2458,7 +2458,7 @@
         <v>1.09</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
         <v>1.18</v>
@@ -2594,10 +2594,10 @@
         <v>5.1</v>
       </c>
       <c r="O14">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P14">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q14">
         <v>5.75</v>
@@ -2642,7 +2642,7 @@
         <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF14">
         <v>1.7</v>
@@ -3083,10 +3083,10 @@
         <v>1.7</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -3122,7 +3122,7 @@
         <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC17">
         <v>3.44</v>
@@ -3131,7 +3131,7 @@
         <v>1.31</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
         <v>1.83</v>
@@ -3415,7 +3415,7 @@
         <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R19">
         <v>1.8</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK19">
         <v>1.49</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O20">
         <v>3.5</v>
       </c>
       <c r="P20">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Q20">
         <v>4.06</v>
@@ -3599,16 +3599,16 @@
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z20">
         <v>4.62</v>
       </c>
       <c r="AA20">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AB20">
         <v>2.28</v>
@@ -3617,7 +3617,7 @@
         <v>2.5</v>
       </c>
       <c r="AD20">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE20">
         <v>1.19</v>
@@ -3759,16 +3759,16 @@
         <v>1.37</v>
       </c>
       <c r="W21">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X21">
         <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="Z21">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="AA21">
         <v>2</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O22">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -4396,7 +4396,7 @@
         <v>3.34</v>
       </c>
       <c r="R25">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
         <v>1.43</v>
@@ -4417,10 +4417,10 @@
         <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z25">
-        <v>3.08</v>
+        <v>3.43</v>
       </c>
       <c r="AA25">
         <v>2.07</v>
@@ -4435,7 +4435,7 @@
         <v>1.25</v>
       </c>
       <c r="AE25">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
         <v>1.8</v>
@@ -5407,7 +5407,7 @@
         <v>1.65</v>
       </c>
       <c r="AC31">
-        <v>4.28</v>
+        <v>3.68</v>
       </c>
       <c r="AD31">
         <v>1.2</v>
@@ -5745,7 +5745,7 @@
         <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -6355,31 +6355,31 @@
         <v>2.45</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U37">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V37">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W37">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X37">
         <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z37">
         <v>3.98</v>
       </c>
       <c r="AA37">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB37">
         <v>2.15</v>
@@ -6391,7 +6391,7 @@
         <v>1.4</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF37">
         <v>1.85</v>
@@ -6672,7 +6672,7 @@
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="Q39">
         <v>2.4</v>
@@ -6708,7 +6708,7 @@
         <v>2.05</v>
       </c>
       <c r="AB39">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC39">
         <v>3.5</v>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6832,10 +6832,10 @@
         <v>2.27</v>
       </c>
       <c r="O40">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P40">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -7499,7 +7499,7 @@
         <v>1.57</v>
       </c>
       <c r="T44">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U44">
         <v>3.6</v>
@@ -7520,7 +7520,7 @@
         <v>2.27</v>
       </c>
       <c r="AA44">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="AB44">
         <v>1.4</v>
@@ -7668,7 +7668,7 @@
         <v>3.5</v>
       </c>
       <c r="V45">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W45">
         <v>1.01</v>
@@ -7683,7 +7683,7 @@
         <v>2.31</v>
       </c>
       <c r="AA45">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB45">
         <v>1.36</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK45">
         <v>1.53</v>
@@ -7822,7 +7822,7 @@
         <v>2.28</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
         <v>3.5</v>
@@ -7864,7 +7864,7 @@
         <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -8166,10 +8166,10 @@
         <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA48">
         <v>1.66</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
         <v>1.91</v>
@@ -8308,7 +8308,7 @@
         <v>7.03</v>
       </c>
       <c r="R49">
-        <v>2.84</v>
+        <v>3.06</v>
       </c>
       <c r="S49">
         <v>1.22</v>
@@ -8341,13 +8341,13 @@
         <v>3.1</v>
       </c>
       <c r="AC49">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="AD49">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="AE49">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AF49">
         <v>1.6</v>
@@ -8471,7 +8471,7 @@
         <v>4.73</v>
       </c>
       <c r="R50">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="S50">
         <v>1.22</v>
@@ -8480,13 +8480,13 @@
         <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="V50">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W50">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X50">
         <v>1.02</v>
@@ -8504,7 +8504,7 @@
         <v>2.55</v>
       </c>
       <c r="AC50">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AD50">
         <v>1.63</v>
@@ -8625,16 +8625,16 @@
         <v>1.96</v>
       </c>
       <c r="O51">
-        <v>3.97</v>
+        <v>3.9</v>
       </c>
       <c r="P51">
-        <v>2.41</v>
+        <v>2.83</v>
       </c>
       <c r="Q51">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="R51">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="S51">
         <v>1.06</v>
@@ -8661,7 +8661,7 @@
         <v>9.6</v>
       </c>
       <c r="AA51">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="AB51">
         <v>4.03</v>
@@ -8670,7 +8670,7 @@
         <v>1.58</v>
       </c>
       <c r="AD51">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AE51">
         <v>1.64</v>
@@ -8951,7 +8951,7 @@
         <v>1.95</v>
       </c>
       <c r="O53">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P53">
         <v>3.1</v>
@@ -8969,7 +8969,7 @@
         <v>3.48</v>
       </c>
       <c r="U53">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="V53">
         <v>1.57</v>
@@ -8990,7 +8990,7 @@
         <v>1.57</v>
       </c>
       <c r="AB53">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="AC53">
         <v>2.28</v>
@@ -9609,16 +9609,16 @@
         <v>3</v>
       </c>
       <c r="Q57">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R57">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T57">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U57">
         <v>2.4</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK57">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9932,7 +9932,7 @@
         <v>6.5</v>
       </c>
       <c r="P59">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q59">
         <v>1.5</v>
@@ -9947,10 +9947,10 @@
         <v>4.45</v>
       </c>
       <c r="U59">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="V59">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="W59">
         <v>1.24</v>
@@ -9971,13 +9971,13 @@
         <v>3.6</v>
       </c>
       <c r="AC59">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AD59">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AE59">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AF59">
         <v>1.73</v>
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="O60">
-        <v>3.64</v>
+        <v>3.46</v>
       </c>
       <c r="P60">
-        <v>2.48</v>
+        <v>2.43</v>
       </c>
       <c r="Q60">
         <v>2.8</v>
@@ -10125,22 +10125,22 @@
         <v>1.11</v>
       </c>
       <c r="Z60">
-        <v>5.75</v>
+        <v>5.39</v>
       </c>
       <c r="AA60">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AB60">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AC60">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AD60">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE60">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AF60">
         <v>1.41</v>
@@ -10258,10 +10258,10 @@
         <v>4.05</v>
       </c>
       <c r="P61">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Q61">
-        <v>4.79</v>
+        <v>4.2</v>
       </c>
       <c r="R61">
         <v>2.82</v>
@@ -10270,7 +10270,7 @@
         <v>1.18</v>
       </c>
       <c r="T61">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="U61">
         <v>1.91</v>
@@ -10421,13 +10421,13 @@
         <v>3.98</v>
       </c>
       <c r="P62">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
       </c>
       <c r="R62">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="S62">
         <v>1.2</v>
@@ -10584,7 +10584,7 @@
         <v>3.3</v>
       </c>
       <c r="P63">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q63">
         <v>2.6</v>
@@ -10599,7 +10599,7 @@
         <v>2.75</v>
       </c>
       <c r="U63">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="V63">
         <v>1.37</v>
@@ -11070,7 +11070,7 @@
         <v>2.27</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
         <v>2.75</v>
@@ -11106,7 +11106,7 @@
         <v>5</v>
       </c>
       <c r="AA66">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AB66">
         <v>2.43</v>
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O70">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P70">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="Q70">
         <v>2.84</v>
@@ -11752,28 +11752,28 @@
         <v>1.02</v>
       </c>
       <c r="Y70">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z70">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="AA70">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB70">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC70">
         <v>3.67</v>
       </c>
       <c r="AD70">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE70">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF70">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AG70">
         <v>1.95</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="O71">
         <v>3.84</v>
       </c>
       <c r="P71">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="Q71">
         <v>2.2</v>
@@ -11921,7 +11921,7 @@
         <v>4</v>
       </c>
       <c r="AA71">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB71">
         <v>2</v>
@@ -11936,7 +11936,7 @@
         <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG71">
         <v>2</v>
@@ -12087,7 +12087,7 @@
         <v>1.98</v>
       </c>
       <c r="AB72">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC72">
         <v>3.43</v>
@@ -12374,10 +12374,10 @@
         <v>2.18</v>
       </c>
       <c r="O74">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P74">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="Q74">
         <v>2.8</v>
@@ -12537,7 +12537,7 @@
         <v>1.47</v>
       </c>
       <c r="O75">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="P75">
         <v>6.8</v>
@@ -12573,7 +12573,7 @@
         <v>3.5</v>
       </c>
       <c r="AA75">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="AB75">
         <v>1.86</v>
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="O77">
-        <v>7.25</v>
+        <v>7.9</v>
       </c>
       <c r="P77">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q77">
         <v>1.45</v>
@@ -12911,7 +12911,7 @@
         <v>1.81</v>
       </c>
       <c r="AE77">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AF77">
         <v>2</v>
@@ -13029,7 +13029,7 @@
         <v>3.14</v>
       </c>
       <c r="P78">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="Q78">
         <v>3.5</v>
@@ -13201,7 +13201,7 @@
         <v>1.99</v>
       </c>
       <c r="S79">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T79">
         <v>2.48</v>
@@ -13222,10 +13222,10 @@
         <v>1.33</v>
       </c>
       <c r="Z79">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AA79">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB79">
         <v>1.7</v>
@@ -13234,7 +13234,7 @@
         <v>3.72</v>
       </c>
       <c r="AD79">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE79">
         <v>1.05</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O80">
         <v>3.5</v>
       </c>
       <c r="P80">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -13370,10 +13370,10 @@
         <v>3.25</v>
       </c>
       <c r="U80">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="V80">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W80">
         <v>1.13</v>
@@ -13400,7 +13400,7 @@
         <v>1.48</v>
       </c>
       <c r="AE80">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF80">
         <v>1.53</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O81">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P81">
         <v>2.87</v>
       </c>
       <c r="Q81">
-        <v>3.17</v>
+        <v>2.99</v>
       </c>
       <c r="R81">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="S81">
         <v>1.41</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="O83">
-        <v>3.63</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>2.83</v>
+        <v>3.7</v>
       </c>
       <c r="Q83">
         <v>2.57</v>
@@ -13865,7 +13865,7 @@
         <v>1.55</v>
       </c>
       <c r="W83">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X83">
         <v>1</v>
@@ -13877,19 +13877,19 @@
         <v>4.2</v>
       </c>
       <c r="AA83">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AB83">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AC83">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="AD83">
         <v>1.5</v>
       </c>
       <c r="AE83">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF83">
         <v>1.57</v>
@@ -14052,7 +14052,7 @@
         <v>1.3</v>
       </c>
       <c r="AE84">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF84">
         <v>1.7</v>
@@ -14173,7 +14173,7 @@
         <v>2.6</v>
       </c>
       <c r="Q85">
-        <v>3.11</v>
+        <v>2.95</v>
       </c>
       <c r="R85">
         <v>2.33</v>
@@ -14221,7 +14221,7 @@
         <v>1.65</v>
       </c>
       <c r="AG85">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2277,7 +2277,7 @@
         <v>2.2</v>
       </c>
       <c r="R12">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S12">
         <v>1.35</v>
@@ -2796,7 +2796,7 @@
         <v>2.28</v>
       </c>
       <c r="AB15">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC15">
         <v>4.14</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="O18">
         <v>3.3</v>
@@ -3252,7 +3252,7 @@
         <v>2.25</v>
       </c>
       <c r="Q18">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R18">
         <v>2.2</v>
@@ -3442,22 +3442,22 @@
         <v>1.71</v>
       </c>
       <c r="Z19">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AA19">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AB19">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AD19">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AE19">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
         <v>2.5</v>
@@ -4263,7 +4263,7 @@
         <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AC24">
         <v>2.88</v>
@@ -5202,7 +5202,7 @@
         <v>5.63</v>
       </c>
       <c r="O30">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P30">
         <v>1.6</v>
@@ -5214,16 +5214,16 @@
         <v>2.19</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T30">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="U30">
         <v>2.67</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W30">
         <v>1.08</v>
@@ -6687,7 +6687,7 @@
         <v>2.9</v>
       </c>
       <c r="U39">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="V39">
         <v>1.4</v>
@@ -6705,7 +6705,7 @@
         <v>3.4</v>
       </c>
       <c r="AA39">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AB39">
         <v>1.8</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="O40">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P40">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -7209,7 +7209,7 @@
         <v>1.23</v>
       </c>
       <c r="AF42">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG42">
         <v>2.5</v>
@@ -7499,7 +7499,7 @@
         <v>1.57</v>
       </c>
       <c r="T44">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="U44">
         <v>3.6</v>
@@ -7976,7 +7976,7 @@
         <v>3.35</v>
       </c>
       <c r="P47">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="Q47">
         <v>2.9</v>
@@ -8015,10 +8015,10 @@
         <v>1.82</v>
       </c>
       <c r="AC47">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD47">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE47">
         <v>1.07</v>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="O48">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
         <v>3.9</v>
@@ -8172,7 +8172,7 @@
         <v>4.4</v>
       </c>
       <c r="AA48">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB48">
         <v>2.14</v>
@@ -8480,10 +8480,10 @@
         <v>3.75</v>
       </c>
       <c r="U50">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="V50">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W50">
         <v>1.17</v>
@@ -9117,7 +9117,7 @@
         <v>3.6</v>
       </c>
       <c r="P54">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>1.1</v>
+        <v>4.66</v>
       </c>
       <c r="O59">
-        <v>6.5</v>
+        <v>4.05</v>
       </c>
       <c r="P59">
-        <v>9.699999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="Q59">
-        <v>1.5</v>
+        <v>4.79</v>
       </c>
       <c r="R59">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="S59">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T59">
-        <v>4.45</v>
+        <v>4.8</v>
       </c>
       <c r="U59">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="V59">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="W59">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="Z59">
-        <v>8</v>
+        <v>5.63</v>
       </c>
       <c r="AA59">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AB59">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AC59">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="AD59">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AE59">
+        <v>1.33</v>
+      </c>
+      <c r="AF59">
         <v>1.4</v>
       </c>
-      <c r="AF59">
-        <v>1.73</v>
-      </c>
       <c r="AG59">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK59">
-        <v>4.55</v>
+        <v>1.17</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.22</v>
+        <v>1.1</v>
       </c>
       <c r="O60">
-        <v>3.46</v>
+        <v>6.5</v>
       </c>
       <c r="P60">
-        <v>2.43</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q60">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="R60">
-        <v>2.53</v>
+        <v>3.1</v>
       </c>
       <c r="S60">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T60">
-        <v>3.65</v>
+        <v>4.45</v>
       </c>
       <c r="U60">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="V60">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="W60">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Z60">
-        <v>5.39</v>
+        <v>8</v>
       </c>
       <c r="AA60">
-        <v>1.48</v>
+        <v>1.25</v>
       </c>
       <c r="AB60">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC60">
-        <v>2.17</v>
+        <v>1.72</v>
       </c>
       <c r="AD60">
-        <v>1.67</v>
+        <v>1.97</v>
       </c>
       <c r="AE60">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AF60">
-        <v>1.41</v>
+        <v>1.73</v>
       </c>
       <c r="AG60">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="AK60">
-        <v>1.57</v>
+        <v>4.55</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>4.66</v>
+        <v>2.15</v>
       </c>
       <c r="O61">
-        <v>4.05</v>
+        <v>3.46</v>
       </c>
       <c r="P61">
-        <v>1.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q61">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="R61">
-        <v>2.82</v>
+        <v>2.53</v>
       </c>
       <c r="S61">
+        <v>1.22</v>
+      </c>
+      <c r="T61">
+        <v>3.65</v>
+      </c>
+      <c r="U61">
+        <v>2.1</v>
+      </c>
+      <c r="V61">
+        <v>1.67</v>
+      </c>
+      <c r="W61">
         <v>1.18</v>
       </c>
-      <c r="T61">
-        <v>4.8</v>
-      </c>
-      <c r="U61">
-        <v>1.91</v>
-      </c>
-      <c r="V61">
-        <v>1.84</v>
-      </c>
-      <c r="W61">
-        <v>1.22</v>
-      </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y61">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Z61">
-        <v>5.63</v>
+        <v>5</v>
       </c>
       <c r="AA61">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AB61">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AC61">
-        <v>1.84</v>
+        <v>2.17</v>
       </c>
       <c r="AD61">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="AE61">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AF61">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG61">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK61">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10753,7 +10753,7 @@
         <v>2.65</v>
       </c>
       <c r="R64">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S64">
         <v>1.3</v>
@@ -11396,16 +11396,16 @@
         <v>1.68</v>
       </c>
       <c r="O68">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P68">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Q68">
         <v>2.22</v>
       </c>
       <c r="R68">
-        <v>2.21</v>
+        <v>2.39</v>
       </c>
       <c r="S68">
         <v>1.3</v>
@@ -11758,10 +11758,10 @@
         <v>2.87</v>
       </c>
       <c r="AA70">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB70">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AC70">
         <v>3.67</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="O71">
         <v>3.84</v>
@@ -12066,10 +12066,10 @@
         <v>2.9</v>
       </c>
       <c r="U72">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="V72">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W72">
         <v>1.08</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O73">
         <v>4.6</v>
@@ -12229,10 +12229,10 @@
         <v>3.25</v>
       </c>
       <c r="U73">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V73">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W73">
         <v>1.11</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O74">
         <v>3.55</v>
       </c>
       <c r="P74">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="Q74">
         <v>2.8</v>
@@ -12866,7 +12866,7 @@
         <v>7.9</v>
       </c>
       <c r="P77">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Q77">
         <v>1.45</v>
@@ -13029,7 +13029,7 @@
         <v>3.14</v>
       </c>
       <c r="P78">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q78">
         <v>3.5</v>
@@ -13355,7 +13355,7 @@
         <v>3.5</v>
       </c>
       <c r="P80">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -13880,10 +13880,10 @@
         <v>1.6</v>
       </c>
       <c r="AB83">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AC83">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="AD83">
         <v>1.5</v>
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O84">
         <v>3.2</v>
       </c>
       <c r="P84">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q84">
         <v>2.89</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2437,7 +2437,7 @@
         <v>2.63</v>
       </c>
       <c r="Q13">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="R13">
         <v>2.16</v>
@@ -2501,7 +2501,7 @@
         <v>1.22</v>
       </c>
       <c r="AK13">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,7 +2600,7 @@
         <v>1.54</v>
       </c>
       <c r="Q14">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="R14">
         <v>2.41</v>
@@ -2630,10 +2630,10 @@
         <v>4.51</v>
       </c>
       <c r="AA14">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AB14">
-        <v>2.26</v>
+        <v>2.17</v>
       </c>
       <c r="AC14">
         <v>2.52</v>
@@ -2642,7 +2642,7 @@
         <v>1.44</v>
       </c>
       <c r="AE14">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
         <v>1.7</v>
@@ -3086,7 +3086,7 @@
         <v>3.6</v>
       </c>
       <c r="P17">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -3252,7 +3252,7 @@
         <v>2.25</v>
       </c>
       <c r="Q18">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R18">
         <v>2.2</v>
@@ -3460,10 +3460,10 @@
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="AG19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>4.62</v>
       </c>
       <c r="AA20">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB20">
         <v>2.28</v>
@@ -3762,22 +3762,22 @@
         <v>1.06</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
         <v>1.31</v>
       </c>
       <c r="Z21">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AB21">
         <v>1.83</v>
       </c>
       <c r="AC21">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="AD21">
         <v>1.3</v>
@@ -3907,13 +3907,13 @@
         <v>2.88</v>
       </c>
       <c r="R22">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
         <v>2.25</v>
@@ -3922,34 +3922,34 @@
         <v>1.57</v>
       </c>
       <c r="W22">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA22">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AB22">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AC22">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AD22">
+        <v>1.53</v>
+      </c>
+      <c r="AE22">
+        <v>1.17</v>
+      </c>
+      <c r="AF22">
         <v>1.46</v>
-      </c>
-      <c r="AE22">
-        <v>1.15</v>
-      </c>
-      <c r="AF22">
-        <v>1.5</v>
       </c>
       <c r="AG22">
         <v>2.75</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
         <v>1.5</v>
@@ -4263,7 +4263,7 @@
         <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC24">
         <v>2.88</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>5.63</v>
+        <v>6.16</v>
       </c>
       <c r="O30">
         <v>3.7</v>
       </c>
       <c r="P30">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Q30">
         <v>5</v>
@@ -5220,7 +5220,7 @@
         <v>3</v>
       </c>
       <c r="U30">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="V30">
         <v>1.39</v>
@@ -5733,10 +5733,10 @@
         <v>1.85</v>
       </c>
       <c r="AC33">
-        <v>3.32</v>
+        <v>3.22</v>
       </c>
       <c r="AD33">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE33">
         <v>1.12</v>
@@ -5745,7 +5745,7 @@
         <v>1.7</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.28</v>
       </c>
       <c r="AK33">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5893,10 +5893,10 @@
         <v>1.54</v>
       </c>
       <c r="AB34">
+        <v>2.28</v>
+      </c>
+      <c r="AC34">
         <v>2.27</v>
-      </c>
-      <c r="AC34">
-        <v>2.28</v>
       </c>
       <c r="AD34">
         <v>1.54</v>
@@ -6355,19 +6355,19 @@
         <v>2.45</v>
       </c>
       <c r="S37">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V37">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W37">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X37">
         <v>1.03</v>
@@ -6379,7 +6379,7 @@
         <v>3.98</v>
       </c>
       <c r="AA37">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB37">
         <v>2.15</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
         <v>1.91</v>
@@ -6835,7 +6835,7 @@
         <v>3</v>
       </c>
       <c r="P40">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -7677,10 +7677,10 @@
         <v>1.05</v>
       </c>
       <c r="Y45">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Z45">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AA45">
         <v>2.87</v>
@@ -7695,7 +7695,7 @@
         <v>1.07</v>
       </c>
       <c r="AE45">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF45">
         <v>2.25</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK45">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="O46">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P46">
         <v>2.71</v>
@@ -7846,7 +7846,7 @@
         <v>4.5</v>
       </c>
       <c r="AA46">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AB46">
         <v>2.35</v>
@@ -7991,7 +7991,7 @@
         <v>2.73</v>
       </c>
       <c r="U47">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="V47">
         <v>1.36</v>
@@ -8009,16 +8009,16 @@
         <v>3.34</v>
       </c>
       <c r="AA47">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AB47">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC47">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE47">
         <v>1.07</v>
@@ -8148,10 +8148,10 @@
         <v>2.38</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U48">
         <v>2.3</v>
@@ -8169,28 +8169,28 @@
         <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA48">
         <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE48">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>1.95</v>
       </c>
       <c r="O53">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P53">
         <v>3.1</v>
@@ -8969,7 +8969,7 @@
         <v>3.48</v>
       </c>
       <c r="U53">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V53">
         <v>1.57</v>
@@ -9117,7 +9117,7 @@
         <v>3.6</v>
       </c>
       <c r="P54">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="Q54">
         <v>3</v>
@@ -9612,7 +9612,7 @@
         <v>2.62</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S57">
         <v>1.29</v>
@@ -9639,7 +9639,7 @@
         <v>4</v>
       </c>
       <c r="AA57">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB57">
         <v>2.15</v>
@@ -9657,7 +9657,7 @@
         <v>1.54</v>
       </c>
       <c r="AG57">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.3</v>
       </c>
       <c r="AK65">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11070,7 +11070,7 @@
         <v>2.27</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
         <v>2.75</v>
@@ -11405,13 +11405,13 @@
         <v>2.22</v>
       </c>
       <c r="R68">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="S68">
         <v>1.3</v>
       </c>
       <c r="T68">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U68">
         <v>2.32</v>
@@ -11734,10 +11734,10 @@
         <v>2.04</v>
       </c>
       <c r="S70">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T70">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="U70">
         <v>2.9</v>
@@ -11764,7 +11764,7 @@
         <v>1.72</v>
       </c>
       <c r="AC70">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="AD70">
         <v>1.29</v>
@@ -11900,10 +11900,10 @@
         <v>1.33</v>
       </c>
       <c r="T71">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="U71">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="V71">
         <v>1.44</v>
@@ -11912,28 +11912,28 @@
         <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA71">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB71">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC71">
-        <v>3.01</v>
+        <v>2.97</v>
       </c>
       <c r="AD71">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE71">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF71">
         <v>1.73</v>
@@ -12051,7 +12051,7 @@
         <v>3.4</v>
       </c>
       <c r="P72">
-        <v>2.93</v>
+        <v>2.8</v>
       </c>
       <c r="Q72">
         <v>2.9</v>
@@ -12066,10 +12066,10 @@
         <v>2.9</v>
       </c>
       <c r="U72">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="V72">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W72">
         <v>1.08</v>
@@ -12081,16 +12081,16 @@
         <v>1.24</v>
       </c>
       <c r="Z72">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="AA72">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB72">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AC72">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="AD72">
         <v>1.27</v>
@@ -12118,7 +12118,7 @@
         <v>1.28</v>
       </c>
       <c r="AK72">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12244,19 +12244,19 @@
         <v>1.17</v>
       </c>
       <c r="Z73">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA73">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB73">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC73">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="AD73">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE73">
         <v>1.18</v>
@@ -12377,7 +12377,7 @@
         <v>3.55</v>
       </c>
       <c r="P74">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="Q74">
         <v>2.8</v>
@@ -12407,7 +12407,7 @@
         <v>1.21</v>
       </c>
       <c r="Z74">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AA74">
         <v>1.69</v>
@@ -12733,7 +12733,7 @@
         <v>1.38</v>
       </c>
       <c r="Z76">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AA76">
         <v>2.28</v>
@@ -12863,7 +12863,7 @@
         <v>1.15</v>
       </c>
       <c r="O77">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="P77">
         <v>15</v>
@@ -13023,10 +13023,10 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="O78">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="P78">
         <v>2.5</v>
@@ -13234,7 +13234,7 @@
         <v>3.72</v>
       </c>
       <c r="AD79">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE79">
         <v>1.05</v>
@@ -13349,10 +13349,10 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="O80">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
         <v>3</v>
@@ -13838,19 +13838,19 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="O83">
         <v>3.6</v>
       </c>
       <c r="P83">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="Q83">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="R83">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
         <v>1.25</v>
@@ -13865,7 +13865,7 @@
         <v>1.55</v>
       </c>
       <c r="W83">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X83">
         <v>1</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2760,7 +2760,7 @@
         <v>2.88</v>
       </c>
       <c r="P15">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
         <v>2.61</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
         <v>2.25</v>
@@ -3261,7 +3261,7 @@
         <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="U18">
         <v>2.5</v>
@@ -3925,7 +3925,7 @@
         <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y22">
         <v>1.14</v>
@@ -4239,7 +4239,7 @@
         <v>1.3</v>
       </c>
       <c r="T24">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U24">
         <v>2.45</v>
@@ -4248,7 +4248,7 @@
         <v>1.44</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
         <v>1.03</v>
@@ -4263,7 +4263,7 @@
         <v>1.75</v>
       </c>
       <c r="AB24">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC24">
         <v>2.88</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>6.16</v>
+        <v>2.67</v>
       </c>
       <c r="O30">
-        <v>3.7</v>
+        <v>3.27</v>
       </c>
       <c r="P30">
-        <v>1.54</v>
+        <v>2.67</v>
       </c>
       <c r="Q30">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="R30">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="U30">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="V30">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z30">
-        <v>3.76</v>
+        <v>2.83</v>
       </c>
       <c r="AA30">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB30">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AC30">
-        <v>2.88</v>
+        <v>3.68</v>
       </c>
       <c r="AD30">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AE30">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG30">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AK30">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.67</v>
+        <v>6.16</v>
       </c>
       <c r="O31">
-        <v>3.27</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>2.67</v>
+        <v>1.54</v>
       </c>
       <c r="Q31">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="S31">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="U31">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="Z31">
-        <v>2.83</v>
+        <v>3.76</v>
       </c>
       <c r="AA31">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AC31">
-        <v>3.68</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF31">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG31">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AK31">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -9168,7 +9168,7 @@
         <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>2.62</v>
       </c>
       <c r="R57">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="S57">
         <v>1.29</v>
@@ -9630,7 +9630,7 @@
         <v>1.12</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
         <v>1.17</v>
@@ -9639,7 +9639,7 @@
         <v>4</v>
       </c>
       <c r="AA57">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB57">
         <v>2.15</v>
@@ -9657,7 +9657,7 @@
         <v>1.54</v>
       </c>
       <c r="AG57">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P63">
         <v>3.1</v>
@@ -10617,7 +10617,7 @@
         <v>2.97</v>
       </c>
       <c r="AA63">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AB63">
         <v>1.72</v>
@@ -10919,7 +10919,7 @@
         <v>2.13</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T65">
         <v>2.89</v>
@@ -10943,10 +10943,10 @@
         <v>3.83</v>
       </c>
       <c r="AA65">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB65">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC65">
         <v>2.94</v>
@@ -11233,7 +11233,7 @@
         <v>2.37</v>
       </c>
       <c r="O67">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
         <v>2.62</v>
@@ -11245,10 +11245,10 @@
         <v>2.15</v>
       </c>
       <c r="S67">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T67">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="U67">
         <v>2.62</v>
@@ -11269,10 +11269,10 @@
         <v>3.2</v>
       </c>
       <c r="AA67">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="AB67">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AC67">
         <v>3.08</v>
@@ -11287,7 +11287,7 @@
         <v>1.67</v>
       </c>
       <c r="AG67">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="O68">
         <v>3.7</v>
@@ -11402,7 +11402,7 @@
         <v>4</v>
       </c>
       <c r="Q68">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R68">
         <v>2.21</v>
@@ -11414,7 +11414,7 @@
         <v>3.12</v>
       </c>
       <c r="U68">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V68">
         <v>1.51</v>
@@ -11429,10 +11429,10 @@
         <v>1.18</v>
       </c>
       <c r="Z68">
-        <v>3.85</v>
+        <v>3.84</v>
       </c>
       <c r="AA68">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AB68">
         <v>2.05</v>
@@ -11444,10 +11444,10 @@
         <v>1.39</v>
       </c>
       <c r="AE68">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AG68">
         <v>2.1</v>
@@ -13527,10 +13527,10 @@
         <v>1.97</v>
       </c>
       <c r="S81">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="T81">
-        <v>2.64</v>
+        <v>2.59</v>
       </c>
       <c r="U81">
         <v>3.02</v>
@@ -14167,10 +14167,10 @@
         <v>2.37</v>
       </c>
       <c r="O85">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P85">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q85">
         <v>2.95</v>
@@ -14191,7 +14191,7 @@
         <v>1.44</v>
       </c>
       <c r="W85">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X85">
         <v>1.02</v>
@@ -14212,10 +14212,10 @@
         <v>2.89</v>
       </c>
       <c r="AD85">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE85">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF85">
         <v>1.65</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2304,10 +2304,10 @@
         <v>3.28</v>
       </c>
       <c r="AA12">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
         <v>2.97</v>
@@ -3119,7 +3119,7 @@
         <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB17">
         <v>1.86</v>
@@ -3445,10 +3445,10 @@
         <v>2.15</v>
       </c>
       <c r="AA19">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="AB19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC19">
         <v>6.5</v>
@@ -3599,7 +3599,7 @@
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
         <v>1.17</v>
@@ -3611,7 +3611,7 @@
         <v>1.65</v>
       </c>
       <c r="AB20">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AC20">
         <v>2.5</v>
@@ -3623,7 +3623,7 @@
         <v>1.19</v>
       </c>
       <c r="AF20">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AG20">
         <v>2.34</v>
@@ -4402,16 +4402,16 @@
         <v>1.43</v>
       </c>
       <c r="T25">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U25">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
         <v>1.01</v>
@@ -5226,7 +5226,7 @@
         <v>1.3</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
         <v>1.03</v>
@@ -5241,7 +5241,7 @@
         <v>2.2</v>
       </c>
       <c r="AB30">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC30">
         <v>3.68</v>
@@ -5256,7 +5256,7 @@
         <v>1.83</v>
       </c>
       <c r="AG30">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>5</v>
       </c>
       <c r="R31">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="S31">
         <v>1.35</v>
@@ -5386,7 +5386,7 @@
         <v>2.66</v>
       </c>
       <c r="V31">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W31">
         <v>1.08</v>
@@ -5404,13 +5404,13 @@
         <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AC31">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD31">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE31">
         <v>1.09</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK31">
         <v>1.14</v>
@@ -5857,7 +5857,7 @@
         <v>3.6</v>
       </c>
       <c r="P34">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="Q34">
         <v>2.44</v>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6379,7 +6379,7 @@
         <v>3.98</v>
       </c>
       <c r="AA37">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB37">
         <v>2.15</v>
@@ -6672,7 +6672,7 @@
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>4</v>
+        <v>4.08</v>
       </c>
       <c r="Q39">
         <v>2.4</v>
@@ -7487,13 +7487,13 @@
         <v>2.97</v>
       </c>
       <c r="P44">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="Q44">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="R44">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="S44">
         <v>1.57</v>
@@ -7514,13 +7514,13 @@
         <v>1.1</v>
       </c>
       <c r="Y44">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Z44">
-        <v>2.27</v>
+        <v>2.22</v>
       </c>
       <c r="AA44">
-        <v>2.73</v>
+        <v>2.87</v>
       </c>
       <c r="AB44">
         <v>1.4</v>
@@ -7535,7 +7535,7 @@
         <v>1.03</v>
       </c>
       <c r="AF44">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG44">
         <v>1.62</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK44">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7659,22 +7659,22 @@
         <v>1.85</v>
       </c>
       <c r="S45">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T45">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U45">
         <v>3.5</v>
       </c>
       <c r="V45">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W45">
         <v>1.01</v>
       </c>
       <c r="X45">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y45">
         <v>1.59</v>
@@ -7686,7 +7686,7 @@
         <v>2.87</v>
       </c>
       <c r="AB45">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC45">
         <v>5.8</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK45">
         <v>1.57</v>
@@ -7822,7 +7822,7 @@
         <v>2.28</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
         <v>3.5</v>
@@ -7834,10 +7834,10 @@
         <v>1.57</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
         <v>1.13</v>
@@ -7849,7 +7849,7 @@
         <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AC46">
         <v>2.33</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="O47">
         <v>3.35</v>
       </c>
       <c r="P47">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="Q47">
         <v>2.9</v>
@@ -7985,7 +7985,7 @@
         <v>2.15</v>
       </c>
       <c r="S47">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T47">
         <v>2.73</v>
@@ -7994,10 +7994,10 @@
         <v>2.7</v>
       </c>
       <c r="V47">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X47">
         <v>1.03</v>
@@ -8148,7 +8148,7 @@
         <v>2.38</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T48">
         <v>3.6</v>
@@ -8163,7 +8163,7 @@
         <v>1.14</v>
       </c>
       <c r="X48">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
         <v>1.17</v>
@@ -8172,7 +8172,7 @@
         <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB48">
         <v>2.25</v>
@@ -8338,7 +8338,7 @@
         <v>1.36</v>
       </c>
       <c r="AB49">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="AC49">
         <v>1.86</v>
@@ -8637,13 +8637,13 @@
         <v>2.8</v>
       </c>
       <c r="S51">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="T51">
         <v>6.4</v>
       </c>
       <c r="U51">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="V51">
         <v>2.2</v>
@@ -8676,7 +8676,7 @@
         <v>1.64</v>
       </c>
       <c r="AF51">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AG51">
         <v>3.9</v>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="O52">
         <v>3.47</v>
@@ -8803,7 +8803,7 @@
         <v>1.25</v>
       </c>
       <c r="T52">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="U52">
         <v>2.3</v>
@@ -8815,7 +8815,7 @@
         <v>1.12</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
         <v>1.18</v>
@@ -8824,10 +8824,10 @@
         <v>4.3</v>
       </c>
       <c r="AA52">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AB52">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="AC52">
         <v>2.38</v>
@@ -8966,7 +8966,7 @@
         <v>1.23</v>
       </c>
       <c r="T53">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="U53">
         <v>2.3</v>
@@ -8975,7 +8975,7 @@
         <v>1.57</v>
       </c>
       <c r="W53">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X53">
         <v>1.02</v>
@@ -9002,7 +9002,7 @@
         <v>1.18</v>
       </c>
       <c r="AF53">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG53">
         <v>2.5</v>
@@ -9941,7 +9941,7 @@
         <v>2.82</v>
       </c>
       <c r="S59">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="T59">
         <v>4.8</v>
@@ -9950,10 +9950,10 @@
         <v>1.91</v>
       </c>
       <c r="V59">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W59">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X59">
         <v>1.01</v>
@@ -9980,10 +9980,10 @@
         <v>1.33</v>
       </c>
       <c r="AF59">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG59">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         <v>1.5</v>
       </c>
       <c r="R60">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="S60">
         <v>1.14</v>
@@ -10113,7 +10113,7 @@
         <v>1.75</v>
       </c>
       <c r="V60">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="W60">
         <v>1.24</v>
@@ -10146,7 +10146,7 @@
         <v>1.73</v>
       </c>
       <c r="AG60">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10261,13 +10261,13 @@
         <v>2.5</v>
       </c>
       <c r="Q61">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="R61">
         <v>2.53</v>
       </c>
       <c r="S61">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T61">
         <v>3.65</v>
@@ -10294,7 +10294,7 @@
         <v>1.43</v>
       </c>
       <c r="AB61">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AC61">
         <v>2.17</v>
@@ -10303,10 +10303,10 @@
         <v>1.67</v>
       </c>
       <c r="AE61">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF61">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG61">
         <v>2.64</v>
@@ -10421,7 +10421,7 @@
         <v>3.98</v>
       </c>
       <c r="P62">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q62">
         <v>3.4</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
         <v>2.75</v>
@@ -11085,7 +11085,7 @@
         <v>1.25</v>
       </c>
       <c r="T66">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="U66">
         <v>2.25</v>
@@ -11758,10 +11758,10 @@
         <v>2.87</v>
       </c>
       <c r="AA70">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB70">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC70">
         <v>3.75</v>
@@ -12386,7 +12386,7 @@
         <v>2.25</v>
       </c>
       <c r="S74">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T74">
         <v>3.4</v>
@@ -12588,10 +12588,10 @@
         <v>1.07</v>
       </c>
       <c r="AF75">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AG75">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12736,7 +12736,7 @@
         <v>2.73</v>
       </c>
       <c r="AA76">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="AB76">
         <v>1.62</v>
@@ -12751,7 +12751,7 @@
         <v>1.05</v>
       </c>
       <c r="AF76">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AG76">
         <v>1.8</v>
@@ -12899,7 +12899,7 @@
         <v>4.91</v>
       </c>
       <c r="AA77">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB77">
         <v>2.87</v>
@@ -13029,7 +13029,7 @@
         <v>3.18</v>
       </c>
       <c r="P78">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q78">
         <v>3.5</v>
@@ -13056,28 +13056,28 @@
         <v>1.05</v>
       </c>
       <c r="Y78">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z78">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AA78">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AB78">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC78">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD78">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE78">
         <v>1.04</v>
       </c>
       <c r="AF78">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG78">
         <v>1.83</v>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK78">
         <v>1.4</v>
@@ -13225,13 +13225,13 @@
         <v>2.88</v>
       </c>
       <c r="AA79">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AB79">
         <v>1.7</v>
       </c>
       <c r="AC79">
-        <v>3.72</v>
+        <v>3.54</v>
       </c>
       <c r="AD79">
         <v>1.25</v>
@@ -13352,7 +13352,7 @@
         <v>1.99</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P80">
         <v>3</v>
@@ -13364,10 +13364,10 @@
         <v>2.45</v>
       </c>
       <c r="S80">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U80">
         <v>2.5</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="O83">
         <v>3.6</v>
       </c>
       <c r="P83">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q83">
         <v>2.5</v>
@@ -13880,7 +13880,7 @@
         <v>1.6</v>
       </c>
       <c r="AB83">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AC83">
         <v>2.37</v>
@@ -13892,10 +13892,10 @@
         <v>1.17</v>
       </c>
       <c r="AF83">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG83">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -14200,16 +14200,16 @@
         <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>4.14</v>
+        <v>4.16</v>
       </c>
       <c r="AA85">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB85">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AC85">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AD85">
         <v>1.36</v>
@@ -14237,7 +14237,7 @@
         <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL85">
         <v>0</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2307,7 +2307,7 @@
         <v>1.9</v>
       </c>
       <c r="AB12">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC12">
         <v>2.97</v>
@@ -2757,10 +2757,10 @@
         <v>1.91</v>
       </c>
       <c r="O15">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q15">
         <v>2.61</v>
@@ -3083,7 +3083,7 @@
         <v>1.7</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.47</v>
       </c>
       <c r="P17">
         <v>4.45</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
         <v>2.25</v>
@@ -3415,16 +3415,16 @@
         <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="R19">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="S19">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="T19">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="U19">
         <v>3.95</v>
@@ -3439,13 +3439,13 @@
         <v>1.16</v>
       </c>
       <c r="Y19">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Z19">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AA19">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AB19">
         <v>1.3</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
         <v>1.17</v>
@@ -3608,10 +3608,10 @@
         <v>4.62</v>
       </c>
       <c r="AA20">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB20">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC20">
         <v>2.5</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
         <v>1.91</v>
@@ -3925,7 +3925,7 @@
         <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
         <v>1.14</v>
@@ -4230,10 +4230,10 @@
         <v>3.2</v>
       </c>
       <c r="Q24">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S24">
         <v>1.3</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="O25">
         <v>3.25</v>
       </c>
       <c r="P25">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="Q25">
         <v>3.34</v>
@@ -4405,10 +4405,10 @@
         <v>2.88</v>
       </c>
       <c r="U25">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V25">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
         <v>1.05</v>
@@ -5238,10 +5238,10 @@
         <v>2.83</v>
       </c>
       <c r="AA30">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB30">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC30">
         <v>3.68</v>
@@ -5365,10 +5365,10 @@
         <v>6.16</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Q31">
         <v>5</v>
@@ -5404,7 +5404,7 @@
         <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC31">
         <v>2.83</v>
@@ -5435,7 +5435,7 @@
         <v>1.16</v>
       </c>
       <c r="AK31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="O33">
         <v>3.35</v>
@@ -5857,7 +5857,7 @@
         <v>3.6</v>
       </c>
       <c r="P34">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="Q34">
         <v>2.44</v>
@@ -6355,7 +6355,7 @@
         <v>2.45</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
         <v>3.3</v>
@@ -6379,10 +6379,10 @@
         <v>3.98</v>
       </c>
       <c r="AA37">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB37">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC37">
         <v>2.7</v>
@@ -6672,7 +6672,7 @@
         <v>3.4</v>
       </c>
       <c r="P39">
-        <v>4.08</v>
+        <v>3.9</v>
       </c>
       <c r="Q39">
         <v>2.4</v>
@@ -6829,7 +6829,7 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O40">
         <v>3</v>
@@ -7158,7 +7158,7 @@
         <v>2.85</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="P42">
         <v>2.3</v>
@@ -7487,7 +7487,7 @@
         <v>2.97</v>
       </c>
       <c r="P44">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="Q44">
         <v>3.7</v>
@@ -7502,10 +7502,10 @@
         <v>2.2</v>
       </c>
       <c r="U44">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V44">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="W44">
         <v>1.03</v>
@@ -7520,10 +7520,10 @@
         <v>2.22</v>
       </c>
       <c r="AA44">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="AB44">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC44">
         <v>5.45</v>
@@ -7665,10 +7665,10 @@
         <v>2.29</v>
       </c>
       <c r="U45">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V45">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W45">
         <v>1.01</v>
@@ -7683,7 +7683,7 @@
         <v>2.32</v>
       </c>
       <c r="AA45">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AB45">
         <v>1.4</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK45">
         <v>1.57</v>
@@ -7810,7 +7810,7 @@
         <v>2.3</v>
       </c>
       <c r="O46">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="P46">
         <v>2.71</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="O47">
         <v>3.35</v>
       </c>
       <c r="P47">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q47">
         <v>2.9</v>
@@ -8172,7 +8172,7 @@
         <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB48">
         <v>2.25</v>
@@ -9168,7 +9168,7 @@
         <v>1.5</v>
       </c>
       <c r="AG54">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>4.33</v>
       </c>
       <c r="AA55">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AB55">
         <v>2.25</v>
@@ -9615,7 +9615,7 @@
         <v>2.3</v>
       </c>
       <c r="S57">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T57">
         <v>3.3</v>
@@ -9630,7 +9630,7 @@
         <v>1.12</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
         <v>1.17</v>
@@ -11067,7 +11067,7 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="O66">
         <v>3.7</v>
@@ -11094,7 +11094,7 @@
         <v>1.6</v>
       </c>
       <c r="W66">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X66">
         <v>1.03</v>
@@ -11402,7 +11402,7 @@
         <v>4</v>
       </c>
       <c r="Q68">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="R68">
         <v>2.21</v>
@@ -11414,7 +11414,7 @@
         <v>3.12</v>
       </c>
       <c r="U68">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V68">
         <v>1.51</v>
@@ -11429,13 +11429,13 @@
         <v>1.18</v>
       </c>
       <c r="Z68">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="AA68">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AB68">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC68">
         <v>2.59</v>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK68">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>3.2</v>
       </c>
       <c r="AA69">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB69">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC69">
         <v>3.2</v>
@@ -11773,7 +11773,7 @@
         <v>1.09</v>
       </c>
       <c r="AF70">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG70">
         <v>1.95</v>
@@ -11888,7 +11888,7 @@
         <v>3.84</v>
       </c>
       <c r="P71">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="Q71">
         <v>2.2</v>
@@ -12045,7 +12045,7 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="O72">
         <v>3.4</v>
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="O75">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="P75">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q75">
         <v>2.02</v>
@@ -12736,7 +12736,7 @@
         <v>2.73</v>
       </c>
       <c r="AA76">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AB76">
         <v>1.62</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,80 +12860,80 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.15</v>
+        <v>2.9</v>
       </c>
       <c r="O77">
-        <v>7.5</v>
+        <v>3.18</v>
       </c>
       <c r="P77">
-        <v>15</v>
+        <v>2.35</v>
       </c>
       <c r="Q77">
-        <v>1.45</v>
+        <v>3.5</v>
       </c>
       <c r="R77">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="S77">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T77">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="U77">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="V77">
-        <v>1.73</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
+        <v>1.06</v>
+      </c>
+      <c r="X77">
+        <v>1.05</v>
+      </c>
+      <c r="Y77">
+        <v>1.39</v>
+      </c>
+      <c r="Z77">
+        <v>2.69</v>
+      </c>
+      <c r="AA77">
+        <v>2.12</v>
+      </c>
+      <c r="AB77">
+        <v>1.62</v>
+      </c>
+      <c r="AC77">
+        <v>4.1</v>
+      </c>
+      <c r="AD77">
         <v>1.2</v>
       </c>
-      <c r="X77">
-        <v>1</v>
-      </c>
-      <c r="Y77">
-        <v>1.11</v>
-      </c>
-      <c r="Z77">
-        <v>4.91</v>
-      </c>
-      <c r="AA77">
+      <c r="AE77">
+        <v>1.04</v>
+      </c>
+      <c r="AF77">
+        <v>1.85</v>
+      </c>
+      <c r="AG77">
+        <v>1.83</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
+        <v>1.3</v>
+      </c>
+      <c r="AK77">
         <v>1.4</v>
-      </c>
-      <c r="AB77">
-        <v>2.87</v>
-      </c>
-      <c r="AC77">
-        <v>2.03</v>
-      </c>
-      <c r="AD77">
-        <v>1.81</v>
-      </c>
-      <c r="AE77">
-        <v>1.31</v>
-      </c>
-      <c r="AF77">
-        <v>2</v>
-      </c>
-      <c r="AG77">
-        <v>1.75</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.1</v>
-      </c>
-      <c r="AK77">
-        <v>4.8</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.9</v>
+        <v>1.15</v>
       </c>
       <c r="O78">
-        <v>3.18</v>
+        <v>7.5</v>
       </c>
       <c r="P78">
-        <v>2.45</v>
+        <v>15</v>
       </c>
       <c r="Q78">
-        <v>3.5</v>
+        <v>1.45</v>
       </c>
       <c r="R78">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="S78">
+        <v>1.22</v>
+      </c>
+      <c r="T78">
+        <v>4</v>
+      </c>
+      <c r="U78">
+        <v>1.95</v>
+      </c>
+      <c r="V78">
+        <v>1.73</v>
+      </c>
+      <c r="W78">
+        <v>1.2</v>
+      </c>
+      <c r="X78">
+        <v>1</v>
+      </c>
+      <c r="Y78">
+        <v>1.11</v>
+      </c>
+      <c r="Z78">
+        <v>4.91</v>
+      </c>
+      <c r="AA78">
         <v>1.4</v>
       </c>
-      <c r="T78">
-        <v>2.7</v>
-      </c>
-      <c r="U78">
-        <v>3.1</v>
-      </c>
-      <c r="V78">
-        <v>1.33</v>
-      </c>
-      <c r="W78">
-        <v>1.06</v>
-      </c>
-      <c r="X78">
-        <v>1.05</v>
-      </c>
-      <c r="Y78">
-        <v>1.39</v>
-      </c>
-      <c r="Z78">
-        <v>2.69</v>
-      </c>
-      <c r="AA78">
-        <v>2.12</v>
-      </c>
       <c r="AB78">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="AC78">
-        <v>4.1</v>
+        <v>2.03</v>
       </c>
       <c r="AD78">
-        <v>1.2</v>
+        <v>1.81</v>
       </c>
       <c r="AE78">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="AF78">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG78">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK78">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13231,7 +13231,7 @@
         <v>1.7</v>
       </c>
       <c r="AC79">
-        <v>3.54</v>
+        <v>3.72</v>
       </c>
       <c r="AD79">
         <v>1.25</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="O80">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P80">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="Q80">
         <v>2.5</v>
@@ -13419,7 +13419,7 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK80">
         <v>1.65</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="O83">
         <v>3.6</v>
       </c>
       <c r="P83">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q83">
         <v>2.5</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -2286,7 +2286,7 @@
         <v>2.77</v>
       </c>
       <c r="U12">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="V12">
         <v>1.41</v>
@@ -2597,7 +2597,7 @@
         <v>4.2</v>
       </c>
       <c r="P14">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q14">
         <v>5.88</v>
@@ -2760,7 +2760,7 @@
         <v>3.2</v>
       </c>
       <c r="P15">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="Q15">
         <v>2.61</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O17">
-        <v>3.47</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="Q17">
         <v>2.3</v>
@@ -3119,7 +3119,7 @@
         <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
         <v>1.86</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="O18">
         <v>3.3</v>
@@ -3415,7 +3415,7 @@
         <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="R19">
         <v>1.75</v>
@@ -3427,7 +3427,7 @@
         <v>2.11</v>
       </c>
       <c r="U19">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="V19">
         <v>1.17</v>
@@ -3436,13 +3436,13 @@
         <v>1.02</v>
       </c>
       <c r="X19">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Y19">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Z19">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AA19">
         <v>3.25</v>
@@ -3451,19 +3451,19 @@
         <v>1.3</v>
       </c>
       <c r="AC19">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AD19">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AE19">
         <v>1.01</v>
       </c>
       <c r="AF19">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AG19">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK19">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3602,13 +3602,13 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z20">
         <v>4.62</v>
       </c>
       <c r="AA20">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB20">
         <v>2.28</v>
@@ -3617,7 +3617,7 @@
         <v>2.5</v>
       </c>
       <c r="AD20">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AE20">
         <v>1.19</v>
@@ -4230,7 +4230,7 @@
         <v>3.2</v>
       </c>
       <c r="Q24">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R24">
         <v>2.2</v>
@@ -4390,7 +4390,7 @@
         <v>3.25</v>
       </c>
       <c r="P25">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="Q25">
         <v>3.34</v>
@@ -4429,7 +4429,7 @@
         <v>1.75</v>
       </c>
       <c r="AC25">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD25">
         <v>1.25</v>
@@ -5214,7 +5214,7 @@
         <v>2</v>
       </c>
       <c r="S30">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
         <v>2.75</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="N31">
-        <v>6.16</v>
+        <v>5.79</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Q31">
         <v>5</v>
       </c>
       <c r="R31">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T31">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U31">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="V31">
         <v>1.4</v>
@@ -5392,28 +5392,28 @@
         <v>1.08</v>
       </c>
       <c r="X31">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y31">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z31">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="AA31">
         <v>1.85</v>
       </c>
       <c r="AB31">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC31">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD31">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE31">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF31">
         <v>1.85</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK31">
         <v>1.13</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="O33">
         <v>3.35</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="O34">
         <v>3.6</v>
       </c>
       <c r="P34">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="Q34">
         <v>2.44</v>
@@ -5893,13 +5893,13 @@
         <v>1.54</v>
       </c>
       <c r="AB34">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="AC34">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD34">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE34">
         <v>1.18</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="O37">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="P37">
         <v>6</v>
@@ -6379,10 +6379,10 @@
         <v>3.98</v>
       </c>
       <c r="AA37">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB37">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AC37">
         <v>2.7</v>
@@ -6669,7 +6669,7 @@
         <v>1.84</v>
       </c>
       <c r="O39">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="P39">
         <v>3.9</v>
@@ -6705,16 +6705,16 @@
         <v>3.4</v>
       </c>
       <c r="AA39">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AB39">
         <v>1.8</v>
       </c>
       <c r="AC39">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD39">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE39">
         <v>1.06</v>
@@ -7813,7 +7813,7 @@
         <v>3.58</v>
       </c>
       <c r="P46">
-        <v>2.71</v>
+        <v>2.69</v>
       </c>
       <c r="Q46">
         <v>2.62</v>
@@ -7849,7 +7849,7 @@
         <v>1.57</v>
       </c>
       <c r="AB46">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AC46">
         <v>2.33</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O47">
         <v>3.35</v>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
         <v>3.9</v>
@@ -8160,10 +8160,10 @@
         <v>1.53</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
         <v>1.17</v>
@@ -8172,7 +8172,7 @@
         <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB48">
         <v>2.25</v>
@@ -8181,13 +8181,13 @@
         <v>2.42</v>
       </c>
       <c r="AD48">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE48">
         <v>1.15</v>
       </c>
       <c r="AF48">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
         <v>2.3</v>
@@ -8317,13 +8317,13 @@
         <v>4</v>
       </c>
       <c r="U49">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V49">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="W49">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="O52">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="P52">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="Q52">
         <v>2.31</v>
@@ -9156,10 +9156,10 @@
         <v>2.21</v>
       </c>
       <c r="AC54">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="AD54">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AE54">
         <v>1.2</v>
@@ -9313,7 +9313,7 @@
         <v>4.33</v>
       </c>
       <c r="AA55">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AB55">
         <v>2.25</v>
@@ -9558,22 +9558,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Real Tomayapo</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blooming</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q57">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R57">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S57">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T57">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U57">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V57">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W57">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y57">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA57">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB57">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC57">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AD57">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE57">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF57">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG57">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK57">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9721,7 +9721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>5.63</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>4.66</v>
+        <v>1.1</v>
       </c>
       <c r="O59">
-        <v>4.05</v>
+        <v>6.5</v>
       </c>
       <c r="P59">
-        <v>1.55</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q59">
-        <v>4.79</v>
+        <v>1.5</v>
       </c>
       <c r="R59">
-        <v>2.82</v>
+        <v>3.14</v>
       </c>
       <c r="S59">
         <v>1.14</v>
       </c>
       <c r="T59">
-        <v>4.8</v>
+        <v>4.45</v>
       </c>
       <c r="U59">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="V59">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="W59">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X59">
         <v>1.01</v>
       </c>
       <c r="Y59">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="Z59">
-        <v>5.63</v>
+        <v>8</v>
       </c>
       <c r="AA59">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AB59">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AC59">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="AD59">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AE59">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF59">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="AG59">
-        <v>2.72</v>
+        <v>1.97</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AK59">
-        <v>1.17</v>
+        <v>4.55</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
+        <v>2.15</v>
+      </c>
+      <c r="O60">
+        <v>3.46</v>
+      </c>
+      <c r="P60">
+        <v>2.5</v>
+      </c>
+      <c r="Q60">
+        <v>2.68</v>
+      </c>
+      <c r="R60">
+        <v>2.53</v>
+      </c>
+      <c r="S60">
+        <v>1.21</v>
+      </c>
+      <c r="T60">
+        <v>3.65</v>
+      </c>
+      <c r="U60">
+        <v>2.1</v>
+      </c>
+      <c r="V60">
+        <v>1.67</v>
+      </c>
+      <c r="W60">
+        <v>1.18</v>
+      </c>
+      <c r="X60">
+        <v>1.02</v>
+      </c>
+      <c r="Y60">
         <v>1.1</v>
       </c>
-      <c r="O60">
-        <v>6.5</v>
-      </c>
-      <c r="P60">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="Q60">
-        <v>1.5</v>
-      </c>
-      <c r="R60">
-        <v>3.14</v>
-      </c>
-      <c r="S60">
-        <v>1.14</v>
-      </c>
-      <c r="T60">
-        <v>4.45</v>
-      </c>
-      <c r="U60">
-        <v>1.75</v>
-      </c>
-      <c r="V60">
-        <v>1.88</v>
-      </c>
-      <c r="W60">
-        <v>1.24</v>
-      </c>
-      <c r="X60">
-        <v>1.01</v>
-      </c>
-      <c r="Y60">
-        <v>1.05</v>
-      </c>
       <c r="Z60">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AA60">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AB60">
-        <v>3.6</v>
+        <v>2.46</v>
       </c>
       <c r="AC60">
-        <v>1.72</v>
+        <v>2.17</v>
       </c>
       <c r="AD60">
-        <v>1.97</v>
+        <v>1.67</v>
       </c>
       <c r="AE60">
+        <v>1.28</v>
+      </c>
+      <c r="AF60">
         <v>1.4</v>
       </c>
-      <c r="AF60">
-        <v>1.73</v>
-      </c>
       <c r="AG60">
-        <v>1.97</v>
+        <v>2.64</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.06</v>
+        <v>1.29</v>
       </c>
       <c r="AK60">
-        <v>4.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="O61">
-        <v>3.46</v>
+        <v>3.98</v>
       </c>
       <c r="P61">
+        <v>2.05</v>
+      </c>
+      <c r="Q61">
+        <v>3.4</v>
+      </c>
+      <c r="R61">
         <v>2.5</v>
       </c>
-      <c r="Q61">
-        <v>2.68</v>
-      </c>
-      <c r="R61">
-        <v>2.53</v>
-      </c>
       <c r="S61">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="U61">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W61">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA61">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AB61">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="AC61">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AD61">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AE61">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF61">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AG61">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10373,22 +10373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.62</v>
+        <v>2.05</v>
       </c>
       <c r="O62">
-        <v>3.98</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q62">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="R62">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="T62">
-        <v>4.2</v>
+        <v>2.75</v>
       </c>
       <c r="U62">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="V62">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="W62">
+        <v>1.06</v>
+      </c>
+      <c r="X62">
+        <v>1.02</v>
+      </c>
+      <c r="Y62">
+        <v>1.33</v>
+      </c>
+      <c r="Z62">
+        <v>2.97</v>
+      </c>
+      <c r="AA62">
+        <v>1.97</v>
+      </c>
+      <c r="AB62">
+        <v>1.72</v>
+      </c>
+      <c r="AC62">
+        <v>3.5</v>
+      </c>
+      <c r="AD62">
         <v>1.22</v>
       </c>
-      <c r="X62">
-        <v>1.01</v>
-      </c>
-      <c r="Y62">
-        <v>1.07</v>
-      </c>
-      <c r="Z62">
-        <v>7</v>
-      </c>
-      <c r="AA62">
-        <v>1.33</v>
-      </c>
-      <c r="AB62">
-        <v>3.1</v>
-      </c>
-      <c r="AC62">
-        <v>1.87</v>
-      </c>
-      <c r="AD62">
+      <c r="AE62">
+        <v>1.04</v>
+      </c>
+      <c r="AF62">
         <v>1.83</v>
       </c>
-      <c r="AE62">
-        <v>1.33</v>
-      </c>
-      <c r="AF62">
-        <v>1.3</v>
-      </c>
       <c r="AG62">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK62">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10531,27 +10531,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q63">
-        <v>2.6</v>
+        <v>3.04</v>
       </c>
       <c r="R63">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S63">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T63">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="U63">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="V63">
+        <v>1.44</v>
+      </c>
+      <c r="W63">
+        <v>1.09</v>
+      </c>
+      <c r="X63">
+        <v>1.03</v>
+      </c>
+      <c r="Y63">
+        <v>1.22</v>
+      </c>
+      <c r="Z63">
+        <v>3.83</v>
+      </c>
+      <c r="AA63">
+        <v>1.8</v>
+      </c>
+      <c r="AB63">
+        <v>1.95</v>
+      </c>
+      <c r="AC63">
+        <v>2.94</v>
+      </c>
+      <c r="AD63">
         <v>1.37</v>
       </c>
-      <c r="W63">
-        <v>1.06</v>
-      </c>
-      <c r="X63">
-        <v>1.02</v>
-      </c>
-      <c r="Y63">
-        <v>1.33</v>
-      </c>
-      <c r="Z63">
-        <v>2.97</v>
-      </c>
-      <c r="AA63">
-        <v>1.97</v>
-      </c>
-      <c r="AB63">
-        <v>1.72</v>
-      </c>
-      <c r="AC63">
-        <v>3.5</v>
-      </c>
-      <c r="AD63">
-        <v>1.22</v>
-      </c>
       <c r="AE63">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF63">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-11-02 16:00:00</t>
+          <t>2026-11-02 16:30:00</t>
         </is>
       </c>
     </row>
@@ -10780,10 +10780,10 @@
         <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB64">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC64">
         <v>2.68</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Szczecin</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
+        <v>2.27</v>
+      </c>
+      <c r="O65">
+        <v>3.65</v>
+      </c>
+      <c r="P65">
+        <v>2.62</v>
+      </c>
+      <c r="Q65">
+        <v>2.46</v>
+      </c>
+      <c r="R65">
         <v>2.4</v>
       </c>
-      <c r="O65">
-        <v>3.3</v>
-      </c>
-      <c r="P65">
-        <v>2.5</v>
-      </c>
-      <c r="Q65">
-        <v>3.04</v>
-      </c>
-      <c r="R65">
-        <v>2.13</v>
-      </c>
       <c r="S65">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T65">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="U65">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="V65">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="W65">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X65">
         <v>1.03</v>
       </c>
       <c r="Y65">
+        <v>1.11</v>
+      </c>
+      <c r="Z65">
+        <v>5</v>
+      </c>
+      <c r="AA65">
+        <v>1.48</v>
+      </c>
+      <c r="AB65">
+        <v>2.43</v>
+      </c>
+      <c r="AC65">
+        <v>2.42</v>
+      </c>
+      <c r="AD65">
+        <v>1.56</v>
+      </c>
+      <c r="AE65">
         <v>1.22</v>
       </c>
-      <c r="Z65">
-        <v>3.83</v>
-      </c>
-      <c r="AA65">
-        <v>1.8</v>
-      </c>
-      <c r="AB65">
-        <v>2</v>
-      </c>
-      <c r="AC65">
-        <v>2.94</v>
-      </c>
-      <c r="AD65">
-        <v>1.37</v>
-      </c>
-      <c r="AE65">
-        <v>1.09</v>
-      </c>
       <c r="AF65">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG65">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AK65">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pogoń Szczecin</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.27</v>
+        <v>2.37</v>
       </c>
       <c r="O66">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Q66">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="R66">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="S66">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T66">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="U66">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="V66">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="W66">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="Z66">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AA66">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AB66">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="AC66">
-        <v>2.42</v>
+        <v>3.08</v>
       </c>
       <c r="AD66">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AE66">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AF66">
+        <v>1.67</v>
+      </c>
+      <c r="AG66">
+        <v>2</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
+        <v>1.3</v>
+      </c>
+      <c r="AK66">
         <v>1.44</v>
-      </c>
-      <c r="AG66">
-        <v>2.53</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.23</v>
-      </c>
-      <c r="AK66">
-        <v>1.57</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.37</v>
+        <v>1.67</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P67">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="Q67">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="R67">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S67">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="U67">
-        <v>2.62</v>
+        <v>2.32</v>
       </c>
       <c r="V67">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="W67">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="Z67">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="AA67">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AB67">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC67">
-        <v>3.08</v>
+        <v>2.59</v>
       </c>
       <c r="AD67">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AE67">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="AF67">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AK67">
-        <v>1.44</v>
+        <v>1.99</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Desenzano Calvina</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="O68">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="P68">
-        <v>4</v>
+        <v>3.43</v>
       </c>
       <c r="Q68">
-        <v>2.19</v>
+        <v>2.68</v>
       </c>
       <c r="R68">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="T68">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="U68">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="V68">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="W68">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z68">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="AA68">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB68">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AC68">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AD68">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AE68">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF68">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG68">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AK68">
-        <v>1.99</v>
+        <v>1.63</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Desenzano Calvina</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.98</v>
+        <v>2.45</v>
       </c>
       <c r="O69">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
-        <v>3.43</v>
+        <v>2.92</v>
       </c>
       <c r="Q69">
-        <v>2.68</v>
+        <v>2.84</v>
       </c>
       <c r="R69">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="S69">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T69">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="U69">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="V69">
         <v>1.4</v>
       </c>
       <c r="W69">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y69">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="Z69">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="AA69">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="AB69">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AC69">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AD69">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE69">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AF69">
         <v>1.75</v>
       </c>
       <c r="AG69">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK69">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-11-02 16:30:00</t>
+          <t>2026-11-02 16:45:00</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.45</v>
+        <v>1.45</v>
       </c>
       <c r="O70">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="P70">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="Q70">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="R70">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="S70">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="T70">
-        <v>2.86</v>
+        <v>3.19</v>
       </c>
       <c r="U70">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="V70">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W70">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y70">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>2.87</v>
+        <v>4.1</v>
       </c>
       <c r="AA70">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="AB70">
-        <v>1.78</v>
+        <v>2.02</v>
       </c>
       <c r="AC70">
-        <v>3.75</v>
+        <v>2.97</v>
       </c>
       <c r="AD70">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AE70">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF70">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG70">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK70">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,58 +11882,58 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="O71">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="P71">
-        <v>4.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q71">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="R71">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S71">
         <v>1.33</v>
       </c>
       <c r="T71">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="U71">
-        <v>2.67</v>
+        <v>2.93</v>
       </c>
       <c r="V71">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="W71">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X71">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y71">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z71">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA71">
+        <v>2</v>
+      </c>
+      <c r="AB71">
         <v>1.8</v>
       </c>
-      <c r="AB71">
-        <v>2.02</v>
-      </c>
       <c r="AC71">
-        <v>2.97</v>
+        <v>3.44</v>
       </c>
       <c r="AD71">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AE71">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF71">
         <v>1.73</v>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK71">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,61 +12045,61 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.28</v>
+        <v>1.47</v>
       </c>
       <c r="O72">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="P72">
-        <v>2.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q72">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="R72">
-        <v>2.1</v>
+        <v>2.31</v>
       </c>
       <c r="S72">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="U72">
-        <v>2.93</v>
+        <v>2.4</v>
       </c>
       <c r="V72">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="W72">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X72">
         <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="Z72">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA72">
-        <v>2</v>
+        <v>1.59</v>
       </c>
       <c r="AB72">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AC72">
-        <v>3.44</v>
+        <v>2.41</v>
       </c>
       <c r="AD72">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AE72">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AF72">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG72">
         <v>2</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.28</v>
+        <v>1.17</v>
       </c>
       <c r="AK72">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="O73">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>5.75</v>
+        <v>2.77</v>
       </c>
       <c r="Q73">
-        <v>1.94</v>
+        <v>2.8</v>
       </c>
       <c r="R73">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T73">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U73">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="V73">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W73">
         <v>1.11</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y73">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z73">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA73">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="AB73">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AC73">
-        <v>2.41</v>
+        <v>2.78</v>
       </c>
       <c r="AD73">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE73">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF73">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG73">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AK73">
-        <v>2.45</v>
+        <v>1.64</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-11-02 16:45:00</t>
+          <t>2026-11-02 17:00:00</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.3</v>
+        <v>1.47</v>
       </c>
       <c r="O74">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="P74">
-        <v>2.77</v>
+        <v>6.8</v>
       </c>
       <c r="Q74">
-        <v>2.8</v>
+        <v>2.02</v>
       </c>
       <c r="R74">
         <v>2.25</v>
       </c>
       <c r="S74">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="T74">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="U74">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V74">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W74">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y74">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z74">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA74">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AB74">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="AC74">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
       <c r="AD74">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="AE74">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AF74">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AG74">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="AK74">
-        <v>1.64</v>
+        <v>2.42</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,80 +12534,80 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="O75">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P75">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="Q75">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="R75">
-        <v>2.25</v>
+        <v>1.98</v>
       </c>
       <c r="S75">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="T75">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="U75">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="V75">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W75">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
         <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z75">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="AA75">
+        <v>2.28</v>
+      </c>
+      <c r="AB75">
+        <v>1.62</v>
+      </c>
+      <c r="AC75">
+        <v>4.08</v>
+      </c>
+      <c r="AD75">
+        <v>1.24</v>
+      </c>
+      <c r="AE75">
+        <v>1.05</v>
+      </c>
+      <c r="AF75">
         <v>1.95</v>
       </c>
-      <c r="AB75">
-        <v>1.86</v>
-      </c>
-      <c r="AC75">
-        <v>3.08</v>
-      </c>
-      <c r="AD75">
+      <c r="AG75">
+        <v>1.8</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
         <v>1.35</v>
       </c>
-      <c r="AE75">
-        <v>1.07</v>
-      </c>
-      <c r="AF75">
-        <v>2.05</v>
-      </c>
-      <c r="AG75">
-        <v>1.73</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.07</v>
-      </c>
       <c r="AK75">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q76">
-        <v>2.7</v>
+        <v>1.45</v>
       </c>
       <c r="R76">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="S76">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="T76">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="U76">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="V76">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="W76">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y76">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="Z76">
-        <v>2.73</v>
+        <v>4.91</v>
       </c>
       <c r="AA76">
-        <v>2.28</v>
+        <v>1.4</v>
       </c>
       <c r="AB76">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="AC76">
-        <v>4.08</v>
+        <v>2.03</v>
       </c>
       <c r="AD76">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="AE76">
-        <v>1.05</v>
+        <v>1.31</v>
       </c>
       <c r="AF76">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG76">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="AK76">
-        <v>1.67</v>
+        <v>4.8</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-11-02 17:00:00</t>
+          <t>2026-11-02 17:15:00</t>
         </is>
       </c>
     </row>
@@ -12866,7 +12866,7 @@
         <v>3.18</v>
       </c>
       <c r="P77">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q77">
         <v>3.5</v>
@@ -12893,13 +12893,13 @@
         <v>1.05</v>
       </c>
       <c r="Y77">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="Z77">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="AA77">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="AB77">
         <v>1.62</v>
@@ -12976,27 +12976,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,81 +13023,81 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.15</v>
+        <v>1.79</v>
       </c>
       <c r="O78">
-        <v>7.5</v>
+        <v>3.45</v>
       </c>
       <c r="P78">
-        <v>15</v>
+        <v>3.7</v>
       </c>
       <c r="Q78">
-        <v>1.45</v>
+        <v>2.3</v>
       </c>
       <c r="R78">
+        <v>1.99</v>
+      </c>
+      <c r="S78">
+        <v>1.43</v>
+      </c>
+      <c r="T78">
+        <v>2.48</v>
+      </c>
+      <c r="U78">
+        <v>2.8</v>
+      </c>
+      <c r="V78">
+        <v>1.36</v>
+      </c>
+      <c r="W78">
+        <v>1.07</v>
+      </c>
+      <c r="X78">
+        <v>1.03</v>
+      </c>
+      <c r="Y78">
+        <v>1.33</v>
+      </c>
+      <c r="Z78">
         <v>2.88</v>
       </c>
-      <c r="S78">
-        <v>1.22</v>
-      </c>
-      <c r="T78">
-        <v>4</v>
-      </c>
-      <c r="U78">
+      <c r="AA78">
+        <v>2.07</v>
+      </c>
+      <c r="AB78">
+        <v>1.7</v>
+      </c>
+      <c r="AC78">
+        <v>3.72</v>
+      </c>
+      <c r="AD78">
+        <v>1.25</v>
+      </c>
+      <c r="AE78">
+        <v>1.05</v>
+      </c>
+      <c r="AF78">
+        <v>1.85</v>
+      </c>
+      <c r="AG78">
+        <v>1.8</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>1.18</v>
+      </c>
+      <c r="AK78">
         <v>1.95</v>
       </c>
-      <c r="V78">
-        <v>1.73</v>
-      </c>
-      <c r="W78">
-        <v>1.2</v>
-      </c>
-      <c r="X78">
-        <v>1</v>
-      </c>
-      <c r="Y78">
-        <v>1.11</v>
-      </c>
-      <c r="Z78">
-        <v>4.91</v>
-      </c>
-      <c r="AA78">
-        <v>1.4</v>
-      </c>
-      <c r="AB78">
-        <v>2.87</v>
-      </c>
-      <c r="AC78">
-        <v>2.03</v>
-      </c>
-      <c r="AD78">
-        <v>1.81</v>
-      </c>
-      <c r="AE78">
-        <v>1.31</v>
-      </c>
-      <c r="AF78">
-        <v>2</v>
-      </c>
-      <c r="AG78">
-        <v>1.75</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.1</v>
-      </c>
-      <c r="AK78">
-        <v>4.8</v>
-      </c>
       <c r="AL78">
         <v>0</v>
       </c>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-11-02 17:15:00</t>
+          <t>2026-11-02 17:30:00</t>
         </is>
       </c>
     </row>
@@ -13139,12 +13139,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="O79">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P79">
-        <v>3.7</v>
+        <v>3.11</v>
       </c>
       <c r="Q79">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R79">
-        <v>1.99</v>
+        <v>2.45</v>
       </c>
       <c r="S79">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T79">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="U79">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="V79">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="W79">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="Z79">
-        <v>2.88</v>
+        <v>4.15</v>
       </c>
       <c r="AA79">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="AB79">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AC79">
-        <v>3.72</v>
+        <v>2.47</v>
       </c>
       <c r="AD79">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="AE79">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AF79">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG79">
-        <v>1.8</v>
+        <v>2.31</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK79">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-11-02 17:30:00</t>
+          <t>2026-11-02 18:00:00</t>
         </is>
       </c>
     </row>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="O80">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="P80">
-        <v>3.11</v>
+        <v>2.87</v>
       </c>
       <c r="Q80">
-        <v>2.5</v>
+        <v>2.99</v>
       </c>
       <c r="R80">
-        <v>2.45</v>
+        <v>1.97</v>
       </c>
       <c r="S80">
-        <v>1.25</v>
+        <v>1.47</v>
       </c>
       <c r="T80">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="U80">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="V80">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="W80">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X80">
+        <v>1.02</v>
+      </c>
+      <c r="Y80">
+        <v>1.41</v>
+      </c>
+      <c r="Z80">
+        <v>2.85</v>
+      </c>
+      <c r="AA80">
+        <v>2.23</v>
+      </c>
+      <c r="AB80">
+        <v>1.6</v>
+      </c>
+      <c r="AC80">
+        <v>4.15</v>
+      </c>
+      <c r="AD80">
+        <v>1.16</v>
+      </c>
+      <c r="AE80">
         <v>1.01</v>
       </c>
-      <c r="Y80">
-        <v>1.16</v>
-      </c>
-      <c r="Z80">
-        <v>4.15</v>
-      </c>
-      <c r="AA80">
-        <v>1.6</v>
-      </c>
-      <c r="AB80">
-        <v>2.2</v>
-      </c>
-      <c r="AC80">
-        <v>2.47</v>
-      </c>
-      <c r="AD80">
-        <v>1.48</v>
-      </c>
-      <c r="AE80">
-        <v>1.16</v>
-      </c>
       <c r="AF80">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AG80">
-        <v>2.31</v>
+        <v>1.78</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AK80">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Real Tomayapo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Blooming</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
+        <v>2</v>
+      </c>
+      <c r="O81">
+        <v>3.6</v>
+      </c>
+      <c r="P81">
+        <v>3</v>
+      </c>
+      <c r="Q81">
+        <v>2.62</v>
+      </c>
+      <c r="R81">
         <v>2.3</v>
       </c>
-      <c r="O81">
-        <v>3.1</v>
-      </c>
-      <c r="P81">
-        <v>2.87</v>
-      </c>
-      <c r="Q81">
-        <v>2.99</v>
-      </c>
-      <c r="R81">
-        <v>1.97</v>
-      </c>
       <c r="S81">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="T81">
-        <v>2.59</v>
+        <v>3.3</v>
       </c>
       <c r="U81">
-        <v>3.02</v>
+        <v>2.4</v>
       </c>
       <c r="V81">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="W81">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="X81">
         <v>1.02</v>
       </c>
       <c r="Y81">
+        <v>1.17</v>
+      </c>
+      <c r="Z81">
+        <v>4</v>
+      </c>
+      <c r="AA81">
+        <v>1.66</v>
+      </c>
+      <c r="AB81">
+        <v>2.15</v>
+      </c>
+      <c r="AC81">
+        <v>2.52</v>
+      </c>
+      <c r="AD81">
         <v>1.41</v>
       </c>
-      <c r="Z81">
-        <v>2.85</v>
-      </c>
-      <c r="AA81">
-        <v>2.23</v>
-      </c>
-      <c r="AB81">
-        <v>1.6</v>
-      </c>
-      <c r="AC81">
-        <v>4.15</v>
-      </c>
-      <c r="AD81">
-        <v>1.16</v>
-      </c>
       <c r="AE81">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AF81">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="AG81">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK81">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-11-02 18:00:00</t>
+          <t>2026-11-02 18:15:00</t>
         </is>
       </c>
     </row>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O83">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q83">
         <v>2.5</v>
@@ -13883,7 +13883,7 @@
         <v>2.3</v>
       </c>
       <c r="AC83">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="AD83">
         <v>1.5</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>3.28</v>
       </c>
       <c r="AA12">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB12">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
         <v>2.97</v>
@@ -2757,10 +2757,10 @@
         <v>1.91</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="P15">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="Q15">
         <v>2.61</v>
@@ -3098,7 +3098,7 @@
         <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="U17">
         <v>2.7</v>
@@ -3246,7 +3246,7 @@
         <v>2.83</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="P18">
         <v>2.25</v>
@@ -3415,13 +3415,13 @@
         <v>3.5</v>
       </c>
       <c r="Q19">
-        <v>3.02</v>
+        <v>3.25</v>
       </c>
       <c r="R19">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="S19">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="T19">
         <v>2.11</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AK19">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4384,7 +4384,7 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="O25">
         <v>3.25</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="O30">
         <v>3.27</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>5.79</v>
+        <v>5.2</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>4.01</v>
       </c>
       <c r="P31">
         <v>1.52</v>
@@ -5383,7 +5383,7 @@
         <v>2.9</v>
       </c>
       <c r="U31">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="V31">
         <v>1.4</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="O33">
         <v>3.35</v>
@@ -6669,7 +6669,7 @@
         <v>1.84</v>
       </c>
       <c r="O39">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
         <v>3.9</v>
@@ -6705,7 +6705,7 @@
         <v>3.4</v>
       </c>
       <c r="AA39">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AB39">
         <v>1.8</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="O40">
         <v>3</v>
       </c>
       <c r="P40">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="O41">
         <v>3.7</v>
@@ -7647,7 +7647,7 @@
         <v>2.6</v>
       </c>
       <c r="O45">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="P45">
         <v>2.6</v>
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.3</v>
+        <v>2.01</v>
       </c>
       <c r="O46">
         <v>3.58</v>
@@ -8139,7 +8139,7 @@
         <v>3.8</v>
       </c>
       <c r="P48">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q48">
         <v>2.3</v>
@@ -8160,7 +8160,7 @@
         <v>1.53</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1.02</v>
@@ -8462,7 +8462,7 @@
         <v>6.51</v>
       </c>
       <c r="O50">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="P50">
         <v>1.43</v>
@@ -8486,13 +8486,13 @@
         <v>1.65</v>
       </c>
       <c r="W50">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
         <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
         <v>5.2</v>
@@ -9781,7 +9781,7 @@
         <v>1.14</v>
       </c>
       <c r="T58">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="U58">
         <v>1.91</v>
@@ -9802,7 +9802,7 @@
         <v>5.63</v>
       </c>
       <c r="AA58">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AB58">
         <v>3.4</v>
@@ -9938,10 +9938,10 @@
         <v>1.5</v>
       </c>
       <c r="R59">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="S59">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T59">
         <v>4.45</v>
@@ -9968,7 +9968,7 @@
         <v>1.25</v>
       </c>
       <c r="AB59">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC59">
         <v>1.72</v>
@@ -10089,25 +10089,25 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="O60">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="P60">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="Q60">
         <v>2.68</v>
       </c>
       <c r="R60">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="S60">
         <v>1.21</v>
       </c>
       <c r="T60">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="U60">
         <v>2.1</v>
@@ -10146,7 +10146,7 @@
         <v>1.4</v>
       </c>
       <c r="AG60">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.29</v>
       </c>
       <c r="AK60">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10255,10 +10255,10 @@
         <v>2.62</v>
       </c>
       <c r="O61">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="Q61">
         <v>3.4</v>
@@ -10300,7 +10300,7 @@
         <v>1.87</v>
       </c>
       <c r="AD61">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AE61">
         <v>1.33</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="O63">
+        <v>3.4</v>
+      </c>
+      <c r="P63">
+        <v>2.64</v>
+      </c>
+      <c r="Q63">
+        <v>2.65</v>
+      </c>
+      <c r="R63">
+        <v>2.35</v>
+      </c>
+      <c r="S63">
+        <v>1.3</v>
+      </c>
+      <c r="T63">
         <v>3.3</v>
       </c>
-      <c r="P63">
-        <v>2.5</v>
-      </c>
-      <c r="Q63">
-        <v>3.04</v>
-      </c>
-      <c r="R63">
-        <v>2.13</v>
-      </c>
-      <c r="S63">
-        <v>1.28</v>
-      </c>
-      <c r="T63">
-        <v>2.89</v>
-      </c>
       <c r="U63">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="V63">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W63">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X63">
         <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z63">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="AA63">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB63">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC63">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AD63">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE63">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF63">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG63">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="O64">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P64">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="Q64">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="R64">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="S64">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T64">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U64">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V64">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W64">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X64">
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z64">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="AA64">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB64">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC64">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="AD64">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE64">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AF64">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG64">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10934,28 +10934,28 @@
         <v>1.11</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y65">
         <v>1.11</v>
       </c>
       <c r="Z65">
-        <v>5</v>
+        <v>4.91</v>
       </c>
       <c r="AA65">
         <v>1.48</v>
       </c>
       <c r="AB65">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="AC65">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="AD65">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE65">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF65">
         <v>1.44</v>
@@ -11106,10 +11106,10 @@
         <v>3.2</v>
       </c>
       <c r="AA66">
+        <v>1.95</v>
+      </c>
+      <c r="AB66">
         <v>1.85</v>
-      </c>
-      <c r="AB66">
-        <v>1.95</v>
       </c>
       <c r="AC66">
         <v>3.08</v>
@@ -11236,7 +11236,7 @@
         <v>3.7</v>
       </c>
       <c r="P67">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q67">
         <v>2.19</v>
@@ -11432,10 +11432,10 @@
         <v>3.2</v>
       </c>
       <c r="AA68">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AB68">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AC68">
         <v>3.2</v>
@@ -11562,7 +11562,7 @@
         <v>3.25</v>
       </c>
       <c r="P69">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Q69">
         <v>2.84</v>
@@ -11722,7 +11722,7 @@
         <v>1.45</v>
       </c>
       <c r="O70">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P70">
         <v>4.2</v>
@@ -11761,7 +11761,7 @@
         <v>1.8</v>
       </c>
       <c r="AB70">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC70">
         <v>2.97</v>
@@ -11776,7 +11776,7 @@
         <v>1.73</v>
       </c>
       <c r="AG70">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -12217,13 +12217,13 @@
         <v>2.77</v>
       </c>
       <c r="Q73">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R73">
         <v>2.25</v>
       </c>
       <c r="S73">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T73">
         <v>3.4</v>
@@ -12253,7 +12253,7 @@
         <v>2.2</v>
       </c>
       <c r="AC73">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="AD73">
         <v>1.45</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O74">
         <v>3.9</v>
       </c>
       <c r="P74">
-        <v>6.8</v>
+        <v>5.75</v>
       </c>
       <c r="Q74">
         <v>2.02</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,80 +12697,80 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.15</v>
+        <v>2.9</v>
       </c>
       <c r="O76">
-        <v>7.5</v>
+        <v>3.18</v>
       </c>
       <c r="P76">
-        <v>15</v>
+        <v>2.35</v>
       </c>
       <c r="Q76">
-        <v>1.45</v>
+        <v>3.5</v>
       </c>
       <c r="R76">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="S76">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T76">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="U76">
-        <v>1.96</v>
+        <v>3.1</v>
       </c>
       <c r="V76">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W76">
+        <v>1.06</v>
+      </c>
+      <c r="X76">
+        <v>1.05</v>
+      </c>
+      <c r="Y76">
+        <v>1.39</v>
+      </c>
+      <c r="Z76">
+        <v>2.68</v>
+      </c>
+      <c r="AA76">
+        <v>2.24</v>
+      </c>
+      <c r="AB76">
+        <v>1.62</v>
+      </c>
+      <c r="AC76">
+        <v>4.1</v>
+      </c>
+      <c r="AD76">
         <v>1.2</v>
       </c>
-      <c r="X76">
-        <v>1</v>
-      </c>
-      <c r="Y76">
-        <v>1.11</v>
-      </c>
-      <c r="Z76">
-        <v>4.91</v>
-      </c>
-      <c r="AA76">
+      <c r="AE76">
+        <v>1.04</v>
+      </c>
+      <c r="AF76">
+        <v>1.85</v>
+      </c>
+      <c r="AG76">
+        <v>1.83</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ76">
+        <v>1.3</v>
+      </c>
+      <c r="AK76">
         <v>1.4</v>
-      </c>
-      <c r="AB76">
-        <v>2.87</v>
-      </c>
-      <c r="AC76">
-        <v>2.03</v>
-      </c>
-      <c r="AD76">
-        <v>1.81</v>
-      </c>
-      <c r="AE76">
-        <v>1.31</v>
-      </c>
-      <c r="AF76">
-        <v>2</v>
-      </c>
-      <c r="AG76">
-        <v>1.7</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ76">
-        <v>1.1</v>
-      </c>
-      <c r="AK76">
-        <v>4.8</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.9</v>
+        <v>1.15</v>
       </c>
       <c r="O77">
-        <v>3.18</v>
+        <v>7.5</v>
       </c>
       <c r="P77">
-        <v>2.45</v>
+        <v>12</v>
       </c>
       <c r="Q77">
-        <v>3.5</v>
+        <v>1.45</v>
       </c>
       <c r="R77">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="S77">
+        <v>1.22</v>
+      </c>
+      <c r="T77">
+        <v>4</v>
+      </c>
+      <c r="U77">
+        <v>1.96</v>
+      </c>
+      <c r="V77">
+        <v>1.72</v>
+      </c>
+      <c r="W77">
+        <v>1.2</v>
+      </c>
+      <c r="X77">
+        <v>1</v>
+      </c>
+      <c r="Y77">
+        <v>1.11</v>
+      </c>
+      <c r="Z77">
+        <v>4.91</v>
+      </c>
+      <c r="AA77">
         <v>1.4</v>
       </c>
-      <c r="T77">
-        <v>2.7</v>
-      </c>
-      <c r="U77">
-        <v>3.1</v>
-      </c>
-      <c r="V77">
-        <v>1.33</v>
-      </c>
-      <c r="W77">
-        <v>1.06</v>
-      </c>
-      <c r="X77">
-        <v>1.05</v>
-      </c>
-      <c r="Y77">
-        <v>1.4</v>
-      </c>
-      <c r="Z77">
-        <v>2.67</v>
-      </c>
-      <c r="AA77">
-        <v>2.24</v>
-      </c>
       <c r="AB77">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="AC77">
-        <v>4.1</v>
+        <v>2.03</v>
       </c>
       <c r="AD77">
-        <v>1.2</v>
+        <v>1.81</v>
       </c>
       <c r="AE77">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="AF77">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG77">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK77">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="O79">
         <v>3.6</v>
@@ -13195,7 +13195,7 @@
         <v>3.11</v>
       </c>
       <c r="Q79">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="R79">
         <v>2.45</v>
@@ -13219,10 +13219,10 @@
         <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z79">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="AA79">
         <v>1.6</v>
@@ -13231,19 +13231,19 @@
         <v>2.2</v>
       </c>
       <c r="AC79">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="AD79">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE79">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AF79">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG79">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13355,7 +13355,7 @@
         <v>3.1</v>
       </c>
       <c r="P80">
-        <v>2.87</v>
+        <v>2.58</v>
       </c>
       <c r="Q80">
         <v>2.99</v>
@@ -13838,7 +13838,7 @@
         </is>
       </c>
       <c r="N83">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O83">
         <v>3.7</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -1133,10 +1133,10 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1145,34 +1145,34 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X5">
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1296,10 +1296,10 @@
         <v>2.46</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1308,34 +1308,34 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE6">
         <v>0</v>
@@ -1344,7 +1344,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -2757,7 +2757,7 @@
         <v>1.91</v>
       </c>
       <c r="O15">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
         <v>3.5</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O17">
         <v>3.6</v>
@@ -3246,7 +3246,7 @@
         <v>2.83</v>
       </c>
       <c r="O18">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
         <v>2.25</v>
@@ -3901,7 +3901,7 @@
         <v>3.4</v>
       </c>
       <c r="P22">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="Q22">
         <v>2.88</v>
@@ -5368,7 +5368,7 @@
         <v>4.01</v>
       </c>
       <c r="P31">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="Q31">
         <v>5</v>
@@ -7810,10 +7810,10 @@
         <v>2.01</v>
       </c>
       <c r="O46">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P46">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="Q46">
         <v>2.62</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK46">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8622,16 +8622,16 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="O51">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P51">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="Q51">
-        <v>2.38</v>
+        <v>2.61</v>
       </c>
       <c r="R51">
         <v>2.8</v>
@@ -8640,7 +8640,7 @@
         <v>1.12</v>
       </c>
       <c r="T51">
-        <v>6.4</v>
+        <v>6.15</v>
       </c>
       <c r="U51">
         <v>1.7</v>
@@ -8649,37 +8649,37 @@
         <v>2.2</v>
       </c>
       <c r="W51">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X51">
         <v>1</v>
       </c>
       <c r="Y51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z51">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA51">
         <v>1.23</v>
       </c>
       <c r="AB51">
-        <v>4.03</v>
+        <v>3.99</v>
       </c>
       <c r="AC51">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AD51">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AE51">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AF51">
         <v>1.22</v>
       </c>
       <c r="AG51">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.17</v>
       </c>
       <c r="AK51">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -9929,7 +9929,7 @@
         <v>1.1</v>
       </c>
       <c r="O59">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="P59">
         <v>9.699999999999999</v>
@@ -10255,7 +10255,7 @@
         <v>2.62</v>
       </c>
       <c r="O61">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="P61">
         <v>2.03</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="O63">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="Q63">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="R63">
-        <v>2.35</v>
+        <v>2.13</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T63">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="U63">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="V63">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W63">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X63">
         <v>1.03</v>
       </c>
       <c r="Y63">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="Z63">
-        <v>4.1</v>
+        <v>3.83</v>
       </c>
       <c r="AA63">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AB63">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AC63">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="AD63">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AE63">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="AF63">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG63">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK63">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="O64">
+        <v>3.4</v>
+      </c>
+      <c r="P64">
+        <v>2.64</v>
+      </c>
+      <c r="Q64">
+        <v>2.65</v>
+      </c>
+      <c r="R64">
+        <v>2.35</v>
+      </c>
+      <c r="S64">
+        <v>1.3</v>
+      </c>
+      <c r="T64">
         <v>3.3</v>
       </c>
-      <c r="P64">
-        <v>2.5</v>
-      </c>
-      <c r="Q64">
-        <v>3.04</v>
-      </c>
-      <c r="R64">
-        <v>2.13</v>
-      </c>
-      <c r="S64">
-        <v>1.28</v>
-      </c>
-      <c r="T64">
-        <v>2.89</v>
-      </c>
       <c r="U64">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="V64">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W64">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X64">
         <v>1.03</v>
       </c>
       <c r="Y64">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z64">
-        <v>3.83</v>
+        <v>4.1</v>
       </c>
       <c r="AA64">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AB64">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC64">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AD64">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AE64">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF64">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG64">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK64">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -11236,7 +11236,7 @@
         <v>3.7</v>
       </c>
       <c r="P67">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q67">
         <v>2.19</v>
@@ -12211,7 +12211,7 @@
         <v>2.3</v>
       </c>
       <c r="O73">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
         <v>2.77</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="O74">
         <v>3.9</v>
       </c>
       <c r="P74">
-        <v>5.75</v>
+        <v>6.8</v>
       </c>
       <c r="Q74">
         <v>2.02</v>
@@ -12703,7 +12703,7 @@
         <v>3.18</v>
       </c>
       <c r="P76">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q76">
         <v>3.5</v>

--- a/jogos_2026-11-02.xlsx
+++ b/jogos_2026-11-02.xlsx
@@ -3753,7 +3753,7 @@
         <v>2.9</v>
       </c>
       <c r="U21">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="V21">
         <v>1.37</v>
@@ -3768,19 +3768,19 @@
         <v>1.31</v>
       </c>
       <c r="Z21">
-        <v>3.36</v>
+        <v>3.14</v>
       </c>
       <c r="AA21">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="AB21">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC21">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="AD21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE21">
         <v>1.1</v>
@@ -4221,10 +4221,10 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="O24">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P24">
         <v>3.2</v>
@@ -4251,7 +4251,7 @@
         <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
         <v>1.22</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O40">
         <v>3</v>
       </c>
       <c r="P40">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -7490,22 +7490,22 @@
         <v>2.27</v>
       </c>
       <c r="Q44">
-        <v>3.7</v>
+        <v>4.14</v>
       </c>
       <c r="R44">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="S44">
         <v>1.57</v>
       </c>
       <c r="T44">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="U44">
         <v>3.8</v>
       </c>
       <c r="V44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W44">
         <v>1.03</v>
@@ -7514,28 +7514,28 @@
         <v>1.1</v>
       </c>
       <c r="Y44">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Z44">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AA44">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="AB44">
         <v>1.38</v>
       </c>
       <c r="AC44">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="AD44">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE44">
         <v>1.03</v>
       </c>
       <c r="AF44">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG44">
         <v>1.62</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
+        <v>1.27</v>
+      </c>
+      <c r="AK44">
         <v>1.28</v>
-      </c>
-      <c r="AK44">
-        <v>1.32</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8012,7 +8012,7 @@
         <v>1.84</v>
       </c>
       <c r="AB47">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AC47">
         <v>3.2</v>
@@ -9781,7 +9781,7 @@
         <v>1.14</v>
       </c>
       <c r="T58">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U58">
         <v>1.91</v>
@@ -9808,19 +9808,19 @@
         <v>3.4</v>
       </c>
       <c r="AC58">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AD58">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AE58">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AF58">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG58">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>1.73</v>
       </c>
       <c r="AG59">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10119,28 +10119,28 @@
         <v>1.18</v>
       </c>
       <c r="X60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y60">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z60">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA60">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB60">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AC60">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AD60">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE60">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AF60">
         <v>1.4</v>
@@ -11607,7 +11607,7 @@
         <v>1.29</v>
       </c>
       <c r="AE69">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF69">
         <v>1.75</v>
@@ -11761,7 +11761,7 @@
         <v>1.8</v>
       </c>
       <c r="AB70">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AC70">
         <v>2.97</v>
@@ -11891,7 +11891,7 @@
         <v>2.8</v>
       </c>
       <c r="Q71">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R71">
         <v>2.1</v>
@@ -11924,7 +11924,7 @@
         <v>2</v>
       </c>
       <c r="AB71">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC71">
         <v>3.44</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>2.9</v>
+        <v>1.15</v>
       </c>
       <c r="O76">
-        <v>3.18</v>
+        <v>7.5</v>
       </c>
       <c r="P76">
-        <v>2.45</v>
+        <v>12</v>
       </c>
       <c r="Q76">
-        <v>3.5</v>
+        <v>1.45</v>
       </c>
       <c r="R76">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="S76">
+        <v>1.22</v>
+      </c>
+      <c r="T76">
+        <v>4</v>
+      </c>
+      <c r="U76">
+        <v>1.96</v>
+      </c>
+      <c r="V76">
+        <v>1.72</v>
+      </c>
+      <c r="W76">
+        <v>1.2</v>
+      </c>
+      <c r="X76">
+        <v>1</v>
+      </c>
+      <c r="Y76">
+        <v>1.11</v>
+      </c>
+      <c r="Z76">
+        <v>4.91</v>
+      </c>
+      <c r="AA76">
         <v>1.4</v>
       </c>
-      <c r="T76">
-        <v>2.7</v>
-      </c>
-      <c r="U76">
-        <v>3.1</v>
-      </c>
-      <c r="V76">
-        <v>1.33</v>
-      </c>
-      <c r="W76">
-        <v>1.06</v>
-      </c>
-      <c r="X76">
-        <v>1.05</v>
-      </c>
-      <c r="Y76">
-        <v>1.39</v>
-      </c>
-      <c r="Z76">
-        <v>2.68</v>
-      </c>
-      <c r="AA76">
-        <v>2.24</v>
-      </c>
       <c r="AB76">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="AC76">
-        <v>4.1</v>
+        <v>2.03</v>
       </c>
       <c r="AD76">
-        <v>1.2</v>
+        <v>1.81</v>
       </c>
       <c r="AE76">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="AF76">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG76">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK76">
-        <v>1.4</v>
+        <v>4.8</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,80 +12860,80 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.15</v>
+        <v>2.9</v>
       </c>
       <c r="O77">
-        <v>7.5</v>
+        <v>3.18</v>
       </c>
       <c r="P77">
-        <v>12</v>
+        <v>2.45</v>
       </c>
       <c r="Q77">
-        <v>1.45</v>
+        <v>3.5</v>
       </c>
       <c r="R77">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="S77">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="T77">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="U77">
-        <v>1.96</v>
+        <v>3.1</v>
       </c>
       <c r="V77">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="W77">
+        <v>1.06</v>
+      </c>
+      <c r="X77">
+        <v>1.05</v>
+      </c>
+      <c r="Y77">
+        <v>1.39</v>
+      </c>
+      <c r="Z77">
+        <v>2.68</v>
+      </c>
+      <c r="AA77">
+        <v>2.24</v>
+      </c>
+      <c r="AB77">
+        <v>1.62</v>
+      </c>
+      <c r="AC77">
+        <v>4.1</v>
+      </c>
+      <c r="AD77">
         <v>1.2</v>
       </c>
-      <c r="X77">
-        <v>1</v>
-      </c>
-      <c r="Y77">
-        <v>1.11</v>
-      </c>
-      <c r="Z77">
-        <v>4.91</v>
-      </c>
-      <c r="AA77">
+      <c r="AE77">
+        <v>1.04</v>
+      </c>
+      <c r="AF77">
+        <v>1.85</v>
+      </c>
+      <c r="AG77">
+        <v>1.83</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
+        <v>1.3</v>
+      </c>
+      <c r="AK77">
         <v>1.4</v>
-      </c>
-      <c r="AB77">
-        <v>2.87</v>
-      </c>
-      <c r="AC77">
-        <v>2.03</v>
-      </c>
-      <c r="AD77">
-        <v>1.81</v>
-      </c>
-      <c r="AE77">
-        <v>1.31</v>
-      </c>
-      <c r="AF77">
-        <v>2</v>
-      </c>
-      <c r="AG77">
-        <v>1.7</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.1</v>
-      </c>
-      <c r="AK77">
-        <v>4.8</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13068,7 +13068,7 @@
         <v>1.7</v>
       </c>
       <c r="AC78">
-        <v>3.72</v>
+        <v>3.54</v>
       </c>
       <c r="AD78">
         <v>1.25</v>
@@ -13358,10 +13358,10 @@
         <v>2.58</v>
       </c>
       <c r="Q80">
-        <v>2.99</v>
+        <v>3.17</v>
       </c>
       <c r="R80">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="S80">
         <v>1.47</v>
@@ -13370,16 +13370,16 @@
         <v>2.59</v>
       </c>
       <c r="U80">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="V80">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W80">
         <v>1.03</v>
       </c>
       <c r="X80">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y80">
         <v>1.41</v>
@@ -13388,25 +13388,25 @@
         <v>2.85</v>
       </c>
       <c r="AA80">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AB80">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC80">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AD80">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE80">
         <v>1.01</v>
       </c>
       <c r="AF80">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG80">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK80">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O83">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q83">
         <v>2.5</v>
